--- a/NRM1_Cost_Estimate_Tool_v4_5.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v4_5.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A4A74B1-DB8C-4DB7-B523-50AA59B93F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBA7215-3F23-4322-836E-C3ED81F6A740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="660">
   <si>
     <t>MASTER COST TABLE | v4.5 June 2026</t>
   </si>
@@ -184,9 +184,6 @@
     <t>Basement excavation &amp; structure</t>
   </si>
   <si>
-    <t>High uncertainty; specialist estimate</t>
-  </si>
-  <si>
     <t>GROUP 2 - Superstructure &amp; envelope</t>
   </si>
   <si>
@@ -2003,6 +2000,12 @@
   </si>
   <si>
     <t>Education</t>
+  </si>
+  <si>
+    <t>Applied to basment foot print High uncertainty; specialist estimate</t>
+  </si>
+  <si>
+    <t>GIFA (automatic, m2)/number of stories</t>
   </si>
 </sst>
 </file>
@@ -2372,13 +2375,13 @@
     <xf numFmtId="164" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2665,12 +2668,12 @@
   <sheetData>
     <row r="1" spans="2:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="2" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2678,22 +2681,22 @@
     </row>
     <row r="5" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2701,37 +2704,37 @@
     </row>
     <row r="10" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2739,42 +2742,42 @@
     </row>
     <row r="18" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2782,187 +2785,187 @@
     </row>
     <row r="27" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="38" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="39" x14ac:dyDescent="0.25">
       <c r="B35" s="39" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="39" x14ac:dyDescent="0.25">
       <c r="B36" s="39" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B37" s="39" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B38" s="39" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B39" s="39" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="40" spans="2:2" ht="39" x14ac:dyDescent="0.25">
       <c r="B40" s="39" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="41" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B41" s="39" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="43" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B43" s="38" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="44" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B44" s="39" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="45" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B45" s="39" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="46" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B46" s="39" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B47" s="39" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B48" s="39" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="49" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B49" s="39" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" s="38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="52" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B52" s="39" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="53" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B53" s="39" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="54" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B54" s="39" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="55" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B55" s="39" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B56" s="39" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" s="39" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" s="38" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="60" spans="2:2" ht="39" x14ac:dyDescent="0.25">
       <c r="B60" s="39" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="61" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B61" s="39" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="62" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B62" s="39" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" s="39" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B65" s="38" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="66" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B66" s="39" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="67" spans="2:2" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B67" s="39" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B68" s="39" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -2998,27 +3001,27 @@
       </c>
     </row>
     <row r="2" spans="1:19" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55"/>
     </row>
     <row r="4" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="46" t="s">
@@ -3079,30 +3082,30 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="54" t="s">
+    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
-      <c r="L5" s="55"/>
-      <c r="M5" s="55"/>
-      <c r="N5" s="55"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="56"/>
-    </row>
-    <row r="6" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="58"/>
+    </row>
+    <row r="6" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
         <v>22</v>
       </c>
@@ -3139,11 +3142,11 @@
       <c r="L6" s="49">
         <v>90</v>
       </c>
-      <c r="M6" s="49">
-        <v>10</v>
-      </c>
-      <c r="N6" s="49">
-        <v>20</v>
+      <c r="M6" s="53">
+        <v>0</v>
+      </c>
+      <c r="N6" s="53">
+        <v>0</v>
       </c>
       <c r="O6" s="49">
         <v>10</v>
@@ -3161,7 +3164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
         <v>30</v>
       </c>
@@ -3190,19 +3193,19 @@
         <v>32</v>
       </c>
       <c r="J7" s="53">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K7" s="53">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L7" s="53">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="M7" s="53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N7" s="53">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O7" s="53">
         <v>20</v>
@@ -3220,7 +3223,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
         <v>34</v>
       </c>
@@ -3252,25 +3255,25 @@
         <v>15</v>
       </c>
       <c r="K8" s="49">
+        <v>35</v>
+      </c>
+      <c r="L8" s="49">
+        <v>60</v>
+      </c>
+      <c r="M8" s="49">
+        <v>35</v>
+      </c>
+      <c r="N8" s="49">
+        <v>60</v>
+      </c>
+      <c r="O8" s="49">
+        <v>35</v>
+      </c>
+      <c r="P8" s="49">
+        <v>60</v>
+      </c>
+      <c r="Q8" s="49">
         <v>30</v>
-      </c>
-      <c r="L8" s="49">
-        <v>40</v>
-      </c>
-      <c r="M8" s="49">
-        <v>10</v>
-      </c>
-      <c r="N8" s="49">
-        <v>20</v>
-      </c>
-      <c r="O8" s="49">
-        <v>5</v>
-      </c>
-      <c r="P8" s="49">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="49">
-        <v>10</v>
       </c>
       <c r="R8" s="48" t="s">
         <v>27</v>
@@ -3279,7 +3282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
         <v>37</v>
       </c>
@@ -3308,28 +3311,28 @@
         <v>32</v>
       </c>
       <c r="J9" s="53">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K9" s="53">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L9" s="53">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M9" s="53">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="N9" s="53">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="O9" s="53">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="P9" s="53">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="Q9" s="53">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R9" s="52" t="s">
         <v>27</v>
@@ -3338,30 +3341,30 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
-      <c r="L10" s="55"/>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-      <c r="S10" s="56"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="57"/>
+      <c r="M10" s="57"/>
+      <c r="N10" s="57"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="57"/>
+      <c r="R10" s="57"/>
+      <c r="S10" s="58"/>
+    </row>
+    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
         <v>41</v>
       </c>
@@ -3399,16 +3402,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="49">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="N11" s="49">
+        <v>120</v>
+      </c>
+      <c r="O11" s="49">
         <v>80</v>
       </c>
-      <c r="O11" s="49">
-        <v>55</v>
-      </c>
       <c r="P11" s="49">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="Q11" s="49">
         <v>0</v>
@@ -3420,7 +3423,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
         <v>44</v>
       </c>
@@ -3458,16 +3461,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="53">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="N12" s="53">
+        <v>220</v>
+      </c>
+      <c r="O12" s="53">
         <v>160</v>
       </c>
-      <c r="O12" s="53">
-        <v>110</v>
-      </c>
       <c r="P12" s="53">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="Q12" s="53">
         <v>0</v>
@@ -3479,7 +3482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
         <v>47</v>
       </c>
@@ -3517,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="49">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="N13" s="49">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="O13" s="49">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="P13" s="49">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="Q13" s="49">
         <v>0</v>
@@ -3538,7 +3541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
         <v>50</v>
       </c>
@@ -3564,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="51" t="s">
-        <v>28</v>
+        <v>659</v>
       </c>
       <c r="J14" s="53">
         <v>0</v>
@@ -3576,16 +3579,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="53">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="N14" s="53">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="O14" s="53">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="P14" s="53">
-        <v>200</v>
+        <v>1600</v>
       </c>
       <c r="Q14" s="53">
         <v>0</v>
@@ -3594,38 +3597,38 @@
         <v>27</v>
       </c>
       <c r="S14" s="51" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="56" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="54" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="57"/>
+      <c r="L15" s="57"/>
+      <c r="M15" s="57"/>
+      <c r="N15" s="57"/>
+      <c r="O15" s="57"/>
+      <c r="P15" s="57"/>
+      <c r="Q15" s="57"/>
+      <c r="R15" s="57"/>
+      <c r="S15" s="58"/>
+    </row>
+    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="55"/>
-      <c r="P15" s="55"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="56"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>54</v>
-      </c>
       <c r="B16" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="48">
         <v>2</v>
@@ -3634,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="E16" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="48" t="s">
         <v>25</v>
@@ -3658,10 +3661,10 @@
         <v>40</v>
       </c>
       <c r="M16" s="49">
-        <v>165</v>
+        <v>350</v>
       </c>
       <c r="N16" s="49">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="O16" s="49">
         <v>130</v>
@@ -3676,15 +3679,15 @@
         <v>27</v>
       </c>
       <c r="S16" s="40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="50" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="50" t="s">
-        <v>57</v>
-      </c>
       <c r="B17" s="51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="52">
         <v>2</v>
@@ -3693,7 +3696,7 @@
         <v>23</v>
       </c>
       <c r="E17" s="51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F17" s="52" t="s">
         <v>25</v>
@@ -3735,15 +3738,15 @@
         <v>27</v>
       </c>
       <c r="S17" s="51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="47" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
-        <v>60</v>
-      </c>
       <c r="B18" s="40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="48">
         <v>2</v>
@@ -3752,7 +3755,7 @@
         <v>23</v>
       </c>
       <c r="E18" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F18" s="48" t="s">
         <v>25</v>
@@ -3776,10 +3779,10 @@
         <v>90</v>
       </c>
       <c r="M18" s="49">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="N18" s="49">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="O18" s="49">
         <v>75</v>
@@ -3794,15 +3797,15 @@
         <v>27</v>
       </c>
       <c r="S18" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="50" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
-        <v>63</v>
-      </c>
       <c r="B19" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="52">
         <v>2</v>
@@ -3811,7 +3814,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F19" s="52" t="s">
         <v>25</v>
@@ -3853,15 +3856,15 @@
         <v>27</v>
       </c>
       <c r="S19" s="51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="47" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>66</v>
-      </c>
       <c r="B20" s="40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="48">
         <v>2</v>
@@ -3870,7 +3873,7 @@
         <v>23</v>
       </c>
       <c r="E20" s="40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20" s="48" t="s">
         <v>25</v>
@@ -3894,16 +3897,16 @@
         <v>110</v>
       </c>
       <c r="M20" s="49">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="N20" s="49">
+        <v>650</v>
+      </c>
+      <c r="O20" s="49">
         <v>450</v>
       </c>
-      <c r="O20" s="49">
-        <v>350</v>
-      </c>
       <c r="P20" s="49">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="Q20" s="49">
         <v>0</v>
@@ -3912,15 +3915,15 @@
         <v>27</v>
       </c>
       <c r="S20" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="50" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
-        <v>69</v>
-      </c>
       <c r="B21" s="51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="52">
         <v>2</v>
@@ -3929,7 +3932,7 @@
         <v>23</v>
       </c>
       <c r="E21" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F21" s="52" t="s">
         <v>25</v>
@@ -3953,16 +3956,16 @@
         <v>200</v>
       </c>
       <c r="M21" s="53">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="N21" s="53">
-        <v>240</v>
+        <v>350</v>
       </c>
       <c r="O21" s="53">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="P21" s="53">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="Q21" s="53">
         <v>0</v>
@@ -3971,15 +3974,15 @@
         <v>27</v>
       </c>
       <c r="S21" s="51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="47" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
-        <v>72</v>
-      </c>
       <c r="B22" s="40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="48">
         <v>2</v>
@@ -3988,7 +3991,7 @@
         <v>23</v>
       </c>
       <c r="E22" s="40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F22" s="48" t="s">
         <v>25</v>
@@ -4003,25 +4006,25 @@
         <v>32</v>
       </c>
       <c r="J22" s="49">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K22" s="49">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="L22" s="49">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="M22" s="49">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="N22" s="49">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="O22" s="49">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="P22" s="49">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="Q22" s="49">
         <v>0</v>
@@ -4030,15 +4033,15 @@
         <v>27</v>
       </c>
       <c r="S22" s="40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
-        <v>75</v>
-      </c>
       <c r="B23" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="52">
         <v>2</v>
@@ -4047,7 +4050,7 @@
         <v>23</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F23" s="52" t="s">
         <v>25</v>
@@ -4071,10 +4074,10 @@
         <v>60</v>
       </c>
       <c r="M23" s="53">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="N23" s="53">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="O23" s="53">
         <v>35</v>
@@ -4089,15 +4092,15 @@
         <v>27</v>
       </c>
       <c r="S23" s="51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="47" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>78</v>
-      </c>
       <c r="B24" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" s="48">
         <v>2</v>
@@ -4106,7 +4109,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F24" s="48" t="s">
         <v>25</v>
@@ -4148,38 +4151,38 @@
         <v>27</v>
       </c>
       <c r="S24" s="40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A25" s="56" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="54" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="55"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="55"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="55"/>
-      <c r="S25" s="56"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="57"/>
+      <c r="K25" s="57"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="57"/>
+      <c r="O25" s="57"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="57"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="58"/>
     </row>
     <row r="26" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" s="47" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="40" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="48">
         <v>3</v>
@@ -4188,7 +4191,7 @@
         <v>23</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F26" s="48" t="s">
         <v>25</v>
@@ -4212,13 +4215,13 @@
         <v>180</v>
       </c>
       <c r="M26" s="49">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="N26" s="49">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="O26" s="49">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="P26" s="49">
         <v>140</v>
@@ -4230,15 +4233,15 @@
         <v>27</v>
       </c>
       <c r="S26" s="40" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" s="50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" s="52">
         <v>3</v>
@@ -4247,7 +4250,7 @@
         <v>23</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F27" s="52" t="s">
         <v>25</v>
@@ -4271,13 +4274,13 @@
         <v>280</v>
       </c>
       <c r="M27" s="53">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="N27" s="53">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="O27" s="53">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="P27" s="53">
         <v>200</v>
@@ -4289,15 +4292,15 @@
         <v>27</v>
       </c>
       <c r="S27" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" s="47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C28" s="48">
         <v>3</v>
@@ -4306,7 +4309,7 @@
         <v>23</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F28" s="48" t="s">
         <v>25</v>
@@ -4330,13 +4333,13 @@
         <v>140</v>
       </c>
       <c r="M28" s="49">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="N28" s="49">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="O28" s="49">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="P28" s="49">
         <v>100</v>
@@ -4348,38 +4351,38 @@
         <v>27</v>
       </c>
       <c r="S28" s="40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A29" s="56" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="55"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="55"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="55"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="55"/>
-      <c r="M29" s="55"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="55"/>
-      <c r="P29" s="55"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="55"/>
-      <c r="S29" s="56"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="57"/>
+      <c r="K29" s="57"/>
+      <c r="L29" s="57"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="57"/>
+      <c r="R29" s="57"/>
+      <c r="S29" s="58"/>
     </row>
     <row r="30" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A30" s="47" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="48">
         <v>4</v>
@@ -4388,7 +4391,7 @@
         <v>23</v>
       </c>
       <c r="E30" s="40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F30" s="48" t="s">
         <v>25</v>
@@ -4430,36 +4433,36 @@
         <v>27</v>
       </c>
       <c r="S30" s="40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="40" t="s">
         <v>95</v>
-      </c>
-      <c r="B31" s="40" t="s">
-        <v>96</v>
       </c>
       <c r="C31" s="48">
         <v>4</v>
       </c>
       <c r="D31" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="40" t="s">
+      <c r="F31" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="48" t="s">
+      <c r="G31" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G31" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H31" s="48">
         <v>2</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J31" s="49">
         <v>900</v>
@@ -4489,36 +4492,36 @@
         <v>27</v>
       </c>
       <c r="S31" s="40" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C32" s="48">
         <v>4</v>
       </c>
       <c r="D32" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="E32" s="40" t="s">
-        <v>106</v>
-      </c>
       <c r="F32" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G32" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H32" s="48">
         <v>2</v>
       </c>
       <c r="I32" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J32" s="49">
         <v>1200</v>
@@ -4548,36 +4551,36 @@
         <v>27</v>
       </c>
       <c r="S32" s="40" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C33" s="48">
         <v>4</v>
       </c>
       <c r="D33" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="40" t="s">
-        <v>110</v>
-      </c>
       <c r="F33" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H33" s="48">
         <v>2</v>
       </c>
       <c r="I33" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J33" s="49">
         <v>3500</v>
@@ -4607,36 +4610,36 @@
         <v>27</v>
       </c>
       <c r="S33" s="40" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B34" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="48">
         <v>4</v>
       </c>
       <c r="D34" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="40" t="s">
-        <v>114</v>
-      </c>
       <c r="F34" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G34" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H34" s="48">
         <v>2</v>
       </c>
       <c r="I34" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J34" s="49">
         <v>2000</v>
@@ -4666,36 +4669,36 @@
         <v>27</v>
       </c>
       <c r="S34" s="40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B35" s="40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="48">
         <v>4</v>
       </c>
       <c r="D35" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="40" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="40" t="s">
-        <v>118</v>
-      </c>
       <c r="F35" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G35" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H35" s="48">
         <v>2</v>
       </c>
       <c r="I35" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J35" s="49">
         <v>2800</v>
@@ -4725,15 +4728,15 @@
         <v>27</v>
       </c>
       <c r="S35" s="40" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C36" s="48">
         <v>4</v>
@@ -4742,19 +4745,19 @@
         <v>23</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F36" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G36" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G36" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H36" s="48">
         <v>2</v>
       </c>
       <c r="I36" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J36" s="49">
         <v>3500</v>
@@ -4784,36 +4787,36 @@
         <v>27</v>
       </c>
       <c r="S36" s="40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C37" s="48">
         <v>4</v>
       </c>
       <c r="D37" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="F37" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="48" t="s">
+      <c r="G37" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H37" s="48">
         <v>3</v>
       </c>
       <c r="I37" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J37" s="49">
         <v>5000</v>
@@ -4840,18 +4843,18 @@
         <v>0</v>
       </c>
       <c r="R37" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S37" s="40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" s="48">
         <v>4</v>
@@ -4860,7 +4863,7 @@
         <v>23</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F38" s="48" t="s">
         <v>25</v>
@@ -4902,36 +4905,36 @@
         <v>27</v>
       </c>
       <c r="S38" s="40" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C39" s="48">
         <v>4</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G39" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G39" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H39" s="48">
         <v>1</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J39" s="49">
         <v>1200</v>
@@ -4959,36 +4962,36 @@
         <v>27</v>
       </c>
       <c r="S39" s="40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C40" s="48">
         <v>4</v>
       </c>
       <c r="D40" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="E40" s="40" t="s">
-        <v>140</v>
-      </c>
       <c r="F40" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G40" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G40" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H40" s="48">
         <v>1</v>
       </c>
       <c r="I40" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J40" s="49">
         <v>550</v>
@@ -5016,36 +5019,36 @@
         <v>27</v>
       </c>
       <c r="S40" s="40" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C41" s="48">
         <v>4</v>
       </c>
       <c r="D41" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" s="40" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="40" t="s">
-        <v>144</v>
-      </c>
       <c r="F41" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G41" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H41" s="48">
         <v>1</v>
       </c>
       <c r="I41" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J41" s="49">
         <v>2500</v>
@@ -5073,36 +5076,36 @@
         <v>27</v>
       </c>
       <c r="S41" s="40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C42" s="48">
         <v>4</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F42" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G42" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G42" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H42" s="48">
         <v>1</v>
       </c>
       <c r="I42" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J42" s="49">
         <v>750</v>
@@ -5126,36 +5129,36 @@
         <v>27</v>
       </c>
       <c r="S42" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A43" s="47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C43" s="48">
         <v>4</v>
       </c>
       <c r="D43" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="E43" s="40" t="s">
-        <v>151</v>
-      </c>
       <c r="F43" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G43" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H43" s="48">
         <v>3</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J43" s="49">
         <v>10000</v>
@@ -5176,39 +5179,39 @@
       <c r="P43" s="49"/>
       <c r="Q43" s="49"/>
       <c r="R43" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S43" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C44" s="48">
         <v>4</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F44" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G44" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H44" s="48">
         <v>3</v>
       </c>
       <c r="I44" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J44" s="49">
         <v>7000</v>
@@ -5229,39 +5232,39 @@
       <c r="P44" s="49"/>
       <c r="Q44" s="49"/>
       <c r="R44" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S44" s="40" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="47" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C45" s="48">
         <v>4</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F45" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G45" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H45" s="48">
         <v>1</v>
       </c>
       <c r="I45" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J45" s="49">
         <v>9500</v>
@@ -5282,39 +5285,39 @@
       <c r="P45" s="49"/>
       <c r="Q45" s="49"/>
       <c r="R45" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S45" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C46" s="48">
         <v>4</v>
       </c>
       <c r="D46" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="E46" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="E46" s="40" t="s">
-        <v>162</v>
-      </c>
       <c r="F46" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G46" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H46" s="48">
         <v>1</v>
       </c>
       <c r="I46" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J46" s="49">
         <v>28000</v>
@@ -5335,39 +5338,39 @@
       <c r="P46" s="49"/>
       <c r="Q46" s="49"/>
       <c r="R46" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S46" s="40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C47" s="48">
         <v>4</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F47" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G47" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H47" s="48">
         <v>4</v>
       </c>
       <c r="I47" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J47" s="49">
         <v>5200</v>
@@ -5391,36 +5394,36 @@
         <v>27</v>
       </c>
       <c r="S47" s="40" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="47" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C48" s="48">
         <v>4</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F48" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G48" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G48" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H48" s="48">
         <v>1</v>
       </c>
       <c r="I48" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J48" s="49">
         <v>2800</v>
@@ -5448,24 +5451,24 @@
         <v>27</v>
       </c>
       <c r="S48" s="40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C49" s="48">
         <v>4</v>
       </c>
       <c r="D49" s="41" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="40" t="s">
         <v>171</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>172</v>
       </c>
       <c r="F49" s="48" t="s">
         <v>25</v>
@@ -5477,7 +5480,7 @@
         <v>3</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J49" s="49">
         <v>440</v>
@@ -5501,36 +5504,36 @@
         <v>27</v>
       </c>
       <c r="S49" s="40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C50" s="48">
         <v>4</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F50" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G50" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H50" s="48">
         <v>4</v>
       </c>
       <c r="I50" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J50" s="49">
         <v>34000</v>
@@ -5551,39 +5554,39 @@
       <c r="P50" s="49"/>
       <c r="Q50" s="49"/>
       <c r="R50" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S50" s="40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A51" s="47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C51" s="48">
         <v>4</v>
       </c>
       <c r="D51" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G51" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G51" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H51" s="48">
         <v>3</v>
       </c>
       <c r="I51" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J51" s="49">
         <v>1000</v>
@@ -5607,24 +5610,24 @@
         <v>27</v>
       </c>
       <c r="S51" s="40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C52" s="48">
         <v>4</v>
       </c>
       <c r="D52" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F52" s="48" t="s">
         <v>25</v>
@@ -5636,7 +5639,7 @@
         <v>1</v>
       </c>
       <c r="I52" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J52" s="49">
         <v>65</v>
@@ -5660,24 +5663,24 @@
         <v>27</v>
       </c>
       <c r="S52" s="40" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A53" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C53" s="48">
         <v>4</v>
       </c>
       <c r="D53" s="41" t="s">
+        <v>184</v>
+      </c>
+      <c r="E53" s="40" t="s">
         <v>185</v>
-      </c>
-      <c r="E53" s="40" t="s">
-        <v>186</v>
       </c>
       <c r="F53" s="48" t="s">
         <v>25</v>
@@ -5689,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="I53" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J53" s="49">
         <v>200</v>
@@ -5713,36 +5716,36 @@
         <v>27</v>
       </c>
       <c r="S53" s="40" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C54" s="48">
         <v>4</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G54" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G54" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H54" s="48">
         <v>3</v>
       </c>
       <c r="I54" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J54" s="49">
         <v>5500</v>
@@ -5766,36 +5769,36 @@
         <v>27</v>
       </c>
       <c r="S54" s="40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C55" s="48">
         <v>4</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F55" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G55" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G55" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H55" s="48">
         <v>2</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J55" s="49">
         <v>6000</v>
@@ -5819,24 +5822,24 @@
         <v>27</v>
       </c>
       <c r="S55" s="40" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C56" s="48">
         <v>4</v>
       </c>
       <c r="D56" s="41" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" s="40" t="s">
         <v>195</v>
-      </c>
-      <c r="E56" s="40" t="s">
-        <v>196</v>
       </c>
       <c r="F56" s="48" t="s">
         <v>25</v>
@@ -5872,36 +5875,36 @@
         <v>27</v>
       </c>
       <c r="S56" s="40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="47" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C57" s="48">
         <v>4</v>
       </c>
       <c r="D57" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F57" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G57" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G57" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H57" s="48">
         <v>1</v>
       </c>
       <c r="I57" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J57" s="49">
         <v>3500</v>
@@ -5925,36 +5928,36 @@
         <v>27</v>
       </c>
       <c r="S57" s="40" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A58" s="47" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C58" s="48">
         <v>4</v>
       </c>
       <c r="D58" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G58" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G58" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H58" s="48">
         <v>2</v>
       </c>
       <c r="I58" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J58" s="49">
         <v>3200</v>
@@ -5978,36 +5981,36 @@
         <v>27</v>
       </c>
       <c r="S58" s="40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="47" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C59" s="48">
         <v>4</v>
       </c>
       <c r="D59" s="41" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F59" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G59" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G59" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H59" s="48">
         <v>2</v>
       </c>
       <c r="I59" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J59" s="49">
         <v>5500</v>
@@ -6028,27 +6031,27 @@
       <c r="P59" s="49"/>
       <c r="Q59" s="49"/>
       <c r="R59" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S59" s="40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A60" s="47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C60" s="48">
         <v>4</v>
       </c>
       <c r="D60" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="E60" s="40" t="s">
         <v>208</v>
-      </c>
-      <c r="E60" s="40" t="s">
-        <v>209</v>
       </c>
       <c r="F60" s="48" t="s">
         <v>25</v>
@@ -6060,7 +6063,7 @@
         <v>1</v>
       </c>
       <c r="I60" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J60" s="49">
         <v>120</v>
@@ -6084,36 +6087,36 @@
         <v>27</v>
       </c>
       <c r="S60" s="40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C61" s="48">
         <v>4</v>
       </c>
       <c r="D61" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G61" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G61" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H61" s="48">
         <v>4</v>
       </c>
       <c r="I61" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J61" s="49">
         <v>280</v>
@@ -6137,24 +6140,24 @@
         <v>27</v>
       </c>
       <c r="S61" s="40" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="47" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C62" s="48">
         <v>4</v>
       </c>
       <c r="D62" s="41" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F62" s="48" t="s">
         <v>25</v>
@@ -6166,7 +6169,7 @@
         <v>1</v>
       </c>
       <c r="I62" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J62" s="49">
         <v>160</v>
@@ -6190,36 +6193,36 @@
         <v>27</v>
       </c>
       <c r="S62" s="40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="40" t="s">
         <v>217</v>
-      </c>
-      <c r="B63" s="40" t="s">
-        <v>218</v>
       </c>
       <c r="C63" s="48">
         <v>4</v>
       </c>
       <c r="D63" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F63" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G63" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G63" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H63" s="48">
         <v>2</v>
       </c>
       <c r="I63" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J63" s="49">
         <v>600</v>
@@ -6249,36 +6252,36 @@
         <v>27</v>
       </c>
       <c r="S63" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="B64" s="40" t="s">
         <v>221</v>
-      </c>
-      <c r="B64" s="40" t="s">
-        <v>222</v>
       </c>
       <c r="C64" s="48">
         <v>4</v>
       </c>
       <c r="D64" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E64" s="40" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="40" t="s">
-        <v>224</v>
-      </c>
       <c r="F64" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G64" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G64" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H64" s="48">
         <v>2</v>
       </c>
       <c r="I64" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J64" s="49">
         <v>3000</v>
@@ -6305,41 +6308,41 @@
         <v>0</v>
       </c>
       <c r="R64" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S64" s="40" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A65" s="56" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="54" t="s">
-        <v>226</v>
-      </c>
-      <c r="B65" s="55"/>
-      <c r="C65" s="55"/>
-      <c r="D65" s="55"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="55"/>
-      <c r="G65" s="55"/>
-      <c r="H65" s="55"/>
-      <c r="I65" s="55"/>
-      <c r="J65" s="55"/>
-      <c r="K65" s="55"/>
-      <c r="L65" s="55"/>
-      <c r="M65" s="55"/>
-      <c r="N65" s="55"/>
-      <c r="O65" s="55"/>
-      <c r="P65" s="55"/>
-      <c r="Q65" s="55"/>
-      <c r="R65" s="55"/>
-      <c r="S65" s="56"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
+      <c r="J65" s="57"/>
+      <c r="K65" s="57"/>
+      <c r="L65" s="57"/>
+      <c r="M65" s="57"/>
+      <c r="N65" s="57"/>
+      <c r="O65" s="57"/>
+      <c r="P65" s="57"/>
+      <c r="Q65" s="57"/>
+      <c r="R65" s="57"/>
+      <c r="S65" s="58"/>
     </row>
     <row r="66" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A66" s="47" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B66" s="40" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C66" s="48">
         <v>5</v>
@@ -6348,7 +6351,7 @@
         <v>23</v>
       </c>
       <c r="E66" s="40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F66" s="48" t="s">
         <v>25</v>
@@ -6360,7 +6363,7 @@
         <v>2</v>
       </c>
       <c r="I66" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J66" s="49">
         <v>30</v>
@@ -6390,15 +6393,15 @@
         <v>27</v>
       </c>
       <c r="S66" s="40" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B67" s="51" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C67" s="52">
         <v>5</v>
@@ -6407,7 +6410,7 @@
         <v>23</v>
       </c>
       <c r="E67" s="51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F67" s="52" t="s">
         <v>25</v>
@@ -6436,10 +6439,10 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B68" s="40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C68" s="48">
         <v>5</v>
@@ -6448,7 +6451,7 @@
         <v>23</v>
       </c>
       <c r="E68" s="40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F68" s="48" t="s">
         <v>25</v>
@@ -6490,15 +6493,15 @@
         <v>27</v>
       </c>
       <c r="S68" s="40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A69" s="50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B69" s="51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C69" s="52">
         <v>5</v>
@@ -6507,19 +6510,19 @@
         <v>23</v>
       </c>
       <c r="E69" s="51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F69" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G69" s="51" t="s">
         <v>127</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>128</v>
       </c>
       <c r="H69" s="52">
         <v>2</v>
       </c>
       <c r="I69" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J69" s="53">
         <v>2500</v>
@@ -6546,18 +6549,18 @@
         <v>0</v>
       </c>
       <c r="R69" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S69" s="51" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A70" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B70" s="40" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C70" s="48">
         <v>5</v>
@@ -6566,7 +6569,7 @@
         <v>23</v>
       </c>
       <c r="E70" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F70" s="48" t="s">
         <v>25</v>
@@ -6578,7 +6581,7 @@
         <v>3</v>
       </c>
       <c r="I70" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J70" s="49">
         <v>20</v>
@@ -6608,15 +6611,15 @@
         <v>27</v>
       </c>
       <c r="S70" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A71" s="50" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B71" s="51" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C71" s="52">
         <v>5</v>
@@ -6625,7 +6628,7 @@
         <v>23</v>
       </c>
       <c r="E71" s="51" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F71" s="52" t="s">
         <v>25</v>
@@ -6637,7 +6640,7 @@
         <v>3</v>
       </c>
       <c r="I71" s="51" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J71" s="53">
         <v>30</v>
@@ -6646,13 +6649,13 @@
         <v>55</v>
       </c>
       <c r="L71" s="53">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="M71" s="53">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="N71" s="53">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="O71" s="53">
         <v>10</v>
@@ -6667,15 +6670,15 @@
         <v>27</v>
       </c>
       <c r="S71" s="51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A72" s="47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B72" s="40" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C72" s="48">
         <v>5</v>
@@ -6684,7 +6687,7 @@
         <v>23</v>
       </c>
       <c r="E72" s="40" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F72" s="48" t="s">
         <v>25</v>
@@ -6726,15 +6729,15 @@
         <v>27</v>
       </c>
       <c r="S72" s="40" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="50" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B73" s="51" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C73" s="52">
         <v>5</v>
@@ -6743,7 +6746,7 @@
         <v>23</v>
       </c>
       <c r="E73" s="51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F73" s="52" t="s">
         <v>25</v>
@@ -6785,15 +6788,15 @@
         <v>27</v>
       </c>
       <c r="S73" s="51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="47" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B74" s="40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C74" s="48">
         <v>5</v>
@@ -6802,7 +6805,7 @@
         <v>23</v>
       </c>
       <c r="E74" s="40" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F74" s="48" t="s">
         <v>25</v>
@@ -6844,24 +6847,24 @@
         <v>27</v>
       </c>
       <c r="S74" s="40" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A75" s="47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B75" s="40" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C75" s="48">
         <v>5</v>
       </c>
       <c r="D75" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F75" s="48" t="s">
         <v>25</v>
@@ -6903,15 +6906,15 @@
         <v>27</v>
       </c>
       <c r="S75" s="40" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B76" s="40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C76" s="48">
         <v>5</v>
@@ -6920,7 +6923,7 @@
         <v>23</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F76" s="48" t="s">
         <v>25</v>
@@ -6962,15 +6965,15 @@
         <v>27</v>
       </c>
       <c r="S76" s="40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A77" s="50" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B77" s="51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C77" s="52">
         <v>5</v>
@@ -6979,7 +6982,7 @@
         <v>23</v>
       </c>
       <c r="E77" s="51" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F77" s="52" t="s">
         <v>25</v>
@@ -7021,15 +7024,15 @@
         <v>27</v>
       </c>
       <c r="S77" s="51" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A78" s="47" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B78" s="40" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C78" s="48">
         <v>5</v>
@@ -7038,7 +7041,7 @@
         <v>23</v>
       </c>
       <c r="E78" s="40" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F78" s="48" t="s">
         <v>25</v>
@@ -7080,15 +7083,15 @@
         <v>27</v>
       </c>
       <c r="S78" s="40" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A79" s="50" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B79" s="51" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C79" s="52">
         <v>5</v>
@@ -7097,7 +7100,7 @@
         <v>23</v>
       </c>
       <c r="E79" s="51" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F79" s="52" t="s">
         <v>25</v>
@@ -7139,15 +7142,15 @@
         <v>27</v>
       </c>
       <c r="S79" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A80" s="47" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B80" s="40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C80" s="48">
         <v>5</v>
@@ -7156,7 +7159,7 @@
         <v>23</v>
       </c>
       <c r="E80" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F80" s="48" t="s">
         <v>25</v>
@@ -7198,24 +7201,24 @@
         <v>27</v>
       </c>
       <c r="S80" s="40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A81" s="47" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C81" s="48">
         <v>5</v>
       </c>
       <c r="D81" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F81" s="48" t="s">
         <v>25</v>
@@ -7257,15 +7260,15 @@
         <v>27</v>
       </c>
       <c r="S81" s="40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C82" s="48">
         <v>5</v>
@@ -7274,7 +7277,7 @@
         <v>23</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F82" s="48" t="s">
         <v>25</v>
@@ -7316,15 +7319,15 @@
         <v>27</v>
       </c>
       <c r="S82" s="40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A83" s="50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B83" s="51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C83" s="52">
         <v>5</v>
@@ -7333,19 +7336,19 @@
         <v>23</v>
       </c>
       <c r="E83" s="51" t="s">
+        <v>277</v>
+      </c>
+      <c r="F83" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="F83" s="52" t="s">
+      <c r="G83" s="51" t="s">
         <v>279</v>
-      </c>
-      <c r="G83" s="51" t="s">
-        <v>280</v>
       </c>
       <c r="H83" s="52">
         <v>3</v>
       </c>
       <c r="I83" s="51" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J83" s="53">
         <v>600</v>
@@ -7372,18 +7375,18 @@
         <v>0</v>
       </c>
       <c r="R83" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S83" s="51" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A84" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B84" s="40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C84" s="48">
         <v>5</v>
@@ -7392,19 +7395,19 @@
         <v>23</v>
       </c>
       <c r="E84" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="F84" s="48" t="s">
         <v>284</v>
       </c>
-      <c r="F84" s="48" t="s">
+      <c r="G84" s="40" t="s">
         <v>285</v>
-      </c>
-      <c r="G84" s="40" t="s">
-        <v>286</v>
       </c>
       <c r="H84" s="48">
         <v>3</v>
       </c>
       <c r="I84" s="40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J84" s="49">
         <v>300</v>
@@ -7431,39 +7434,39 @@
         <v>0</v>
       </c>
       <c r="R84" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S84" s="40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="85" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A85" s="47" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C85" s="48">
         <v>5</v>
       </c>
       <c r="D85" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F85" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G85" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G85" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H85" s="48">
         <v>3</v>
       </c>
       <c r="I85" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J85" s="49">
         <v>10000</v>
@@ -7490,27 +7493,27 @@
         <v>40000</v>
       </c>
       <c r="R85" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S85" s="40" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="47" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C86" s="48">
         <v>5</v>
       </c>
       <c r="D86" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F86" s="48" t="s">
         <v>25</v>
@@ -7552,15 +7555,15 @@
         <v>27</v>
       </c>
       <c r="S86" s="40" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="50" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B87" s="51" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C87" s="52">
         <v>5</v>
@@ -7569,19 +7572,19 @@
         <v>23</v>
       </c>
       <c r="E87" s="51" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F87" s="52" t="s">
+        <v>98</v>
+      </c>
+      <c r="G87" s="51" t="s">
         <v>99</v>
-      </c>
-      <c r="G87" s="51" t="s">
-        <v>100</v>
       </c>
       <c r="H87" s="52">
         <v>3</v>
       </c>
       <c r="I87" s="51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J87" s="53">
         <v>0</v>
@@ -7611,24 +7614,24 @@
         <v>27</v>
       </c>
       <c r="S87" s="51" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="47" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B88" s="40" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C88" s="48">
         <v>5</v>
       </c>
       <c r="D88" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E88" s="40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F88" s="48" t="s">
         <v>25</v>
@@ -7670,24 +7673,24 @@
         <v>27</v>
       </c>
       <c r="S88" s="40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="47" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B89" s="40" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C89" s="48">
         <v>5</v>
       </c>
       <c r="D89" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F89" s="48" t="s">
         <v>25</v>
@@ -7729,15 +7732,15 @@
         <v>27</v>
       </c>
       <c r="S89" s="40" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B90" s="40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C90" s="48">
         <v>5</v>
@@ -7746,19 +7749,19 @@
         <v>23</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F90" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G90" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G90" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H90" s="48">
         <v>3</v>
       </c>
       <c r="I90" s="40" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J90" s="49">
         <v>25000</v>
@@ -7788,15 +7791,15 @@
         <v>27</v>
       </c>
       <c r="S90" s="40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="50" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B91" s="51" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C91" s="52">
         <v>5</v>
@@ -7805,7 +7808,7 @@
         <v>23</v>
       </c>
       <c r="E91" s="51" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F91" s="52" t="s">
         <v>25</v>
@@ -7847,36 +7850,36 @@
         <v>27</v>
       </c>
       <c r="S91" s="51" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A92" s="47" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B92" s="40" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C92" s="48">
         <v>5</v>
       </c>
       <c r="D92" s="41" t="s">
+        <v>312</v>
+      </c>
+      <c r="E92" s="40" t="s">
         <v>313</v>
       </c>
-      <c r="E92" s="40" t="s">
-        <v>314</v>
-      </c>
       <c r="F92" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G92" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G92" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H92" s="48">
         <v>3</v>
       </c>
       <c r="I92" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J92" s="49">
         <v>11000</v>
@@ -7897,27 +7900,27 @@
       <c r="P92" s="49"/>
       <c r="Q92" s="49"/>
       <c r="R92" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S92" s="40" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="47" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C93" s="48">
         <v>5</v>
       </c>
       <c r="D93" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F93" s="48" t="s">
         <v>25</v>
@@ -7929,7 +7932,7 @@
         <v>3</v>
       </c>
       <c r="I93" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J93" s="49">
         <v>90</v>
@@ -7953,36 +7956,36 @@
         <v>27</v>
       </c>
       <c r="S93" s="40" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A94" s="47" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B94" s="40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C94" s="48">
         <v>5</v>
       </c>
       <c r="D94" s="41" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F94" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G94" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G94" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H94" s="48">
         <v>3</v>
       </c>
       <c r="I94" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J94" s="49">
         <v>16000</v>
@@ -8003,39 +8006,39 @@
       <c r="P94" s="49"/>
       <c r="Q94" s="49"/>
       <c r="R94" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S94" s="40" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A95" s="47" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B95" s="40" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C95" s="48">
         <v>5</v>
       </c>
       <c r="D95" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F95" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G95" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G95" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H95" s="48">
         <v>3</v>
       </c>
       <c r="I95" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J95" s="49">
         <v>42000</v>
@@ -8056,39 +8059,39 @@
       <c r="P95" s="49"/>
       <c r="Q95" s="49"/>
       <c r="R95" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S95" s="40" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A96" s="47" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B96" s="40" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C96" s="48">
         <v>5</v>
       </c>
       <c r="D96" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F96" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G96" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G96" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H96" s="48">
         <v>3</v>
       </c>
       <c r="I96" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J96" s="49">
         <v>17000</v>
@@ -8109,39 +8112,39 @@
       <c r="P96" s="49"/>
       <c r="Q96" s="49"/>
       <c r="R96" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S96" s="40" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A97" s="47" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B97" s="40" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C97" s="48">
         <v>5</v>
       </c>
       <c r="D97" s="41" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E97" s="40" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F97" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G97" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G97" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H97" s="48">
         <v>3</v>
       </c>
       <c r="I97" s="40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J97" s="49">
         <v>620</v>
@@ -8165,36 +8168,36 @@
         <v>27</v>
       </c>
       <c r="S97" s="40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="98" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A98" s="47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C98" s="48">
         <v>5</v>
       </c>
       <c r="D98" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F98" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G98" s="40" t="s">
         <v>127</v>
-      </c>
-      <c r="G98" s="40" t="s">
-        <v>128</v>
       </c>
       <c r="H98" s="48">
         <v>3</v>
       </c>
       <c r="I98" s="40" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J98" s="49">
         <v>32000</v>
@@ -8215,39 +8218,39 @@
       <c r="P98" s="49"/>
       <c r="Q98" s="49"/>
       <c r="R98" s="48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S98" s="40" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="99" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A99" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="B99" s="40" t="s">
         <v>334</v>
-      </c>
-      <c r="B99" s="40" t="s">
-        <v>335</v>
       </c>
       <c r="C99" s="48">
         <v>5</v>
       </c>
       <c r="D99" s="41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E99" s="40" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F99" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G99" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G99" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H99" s="48">
         <v>2</v>
       </c>
       <c r="I99" s="40" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J99" s="49">
         <v>500</v>
@@ -8277,38 +8280,38 @@
         <v>27</v>
       </c>
       <c r="S99" s="40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="54" t="s">
-        <v>338</v>
-      </c>
-      <c r="B100" s="55"/>
-      <c r="C100" s="55"/>
-      <c r="D100" s="55"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="55"/>
-      <c r="G100" s="55"/>
-      <c r="H100" s="55"/>
-      <c r="I100" s="55"/>
-      <c r="J100" s="55"/>
-      <c r="K100" s="55"/>
-      <c r="L100" s="55"/>
-      <c r="M100" s="55"/>
-      <c r="N100" s="55"/>
-      <c r="O100" s="55"/>
-      <c r="P100" s="55"/>
-      <c r="Q100" s="55"/>
-      <c r="R100" s="55"/>
-      <c r="S100" s="56"/>
+      <c r="A100" s="56" t="s">
+        <v>337</v>
+      </c>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
+      <c r="J100" s="57"/>
+      <c r="K100" s="57"/>
+      <c r="L100" s="57"/>
+      <c r="M100" s="57"/>
+      <c r="N100" s="57"/>
+      <c r="O100" s="57"/>
+      <c r="P100" s="57"/>
+      <c r="Q100" s="57"/>
+      <c r="R100" s="57"/>
+      <c r="S100" s="58"/>
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="47" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B101" s="40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C101" s="48">
         <v>6</v>
@@ -8317,7 +8320,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="40" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F101" s="48" t="s">
         <v>25</v>
@@ -8359,24 +8362,24 @@
         <v>27</v>
       </c>
       <c r="S101" s="40" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="47" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B102" s="40" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C102" s="48">
         <v>6</v>
       </c>
       <c r="D102" s="41" t="s">
+        <v>342</v>
+      </c>
+      <c r="E102" s="40" t="s">
         <v>343</v>
-      </c>
-      <c r="E102" s="40" t="s">
-        <v>344</v>
       </c>
       <c r="F102" s="48" t="s">
         <v>25</v>
@@ -8418,36 +8421,36 @@
         <v>27</v>
       </c>
       <c r="S102" s="40" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A103" s="47" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B103" s="40" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C103" s="48">
         <v>6</v>
       </c>
       <c r="D103" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E103" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="E103" s="40" t="s">
-        <v>348</v>
-      </c>
       <c r="F103" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G103" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G103" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H103" s="48">
         <v>4</v>
       </c>
       <c r="I103" s="40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J103" s="49">
         <v>3200</v>
@@ -8471,24 +8474,24 @@
         <v>27</v>
       </c>
       <c r="S103" s="40" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A104" s="47" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C104" s="48">
         <v>6</v>
       </c>
       <c r="D104" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="E104" s="40" t="s">
         <v>351</v>
-      </c>
-      <c r="E104" s="40" t="s">
-        <v>352</v>
       </c>
       <c r="F104" s="48" t="s">
         <v>25</v>
@@ -8500,7 +8503,7 @@
         <v>4</v>
       </c>
       <c r="I104" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J104" s="49">
         <v>380</v>
@@ -8524,38 +8527,38 @@
         <v>27</v>
       </c>
       <c r="S104" s="40" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A105" s="56" t="s">
         <v>353</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="54" t="s">
-        <v>354</v>
-      </c>
-      <c r="B105" s="55"/>
-      <c r="C105" s="55"/>
-      <c r="D105" s="55"/>
-      <c r="E105" s="55"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="55"/>
-      <c r="H105" s="55"/>
-      <c r="I105" s="55"/>
-      <c r="J105" s="55"/>
-      <c r="K105" s="55"/>
-      <c r="L105" s="55"/>
-      <c r="M105" s="55"/>
-      <c r="N105" s="55"/>
-      <c r="O105" s="55"/>
-      <c r="P105" s="55"/>
-      <c r="Q105" s="55"/>
-      <c r="R105" s="55"/>
-      <c r="S105" s="56"/>
+      <c r="B105" s="57"/>
+      <c r="C105" s="57"/>
+      <c r="D105" s="57"/>
+      <c r="E105" s="57"/>
+      <c r="F105" s="57"/>
+      <c r="G105" s="57"/>
+      <c r="H105" s="57"/>
+      <c r="I105" s="57"/>
+      <c r="J105" s="57"/>
+      <c r="K105" s="57"/>
+      <c r="L105" s="57"/>
+      <c r="M105" s="57"/>
+      <c r="N105" s="57"/>
+      <c r="O105" s="57"/>
+      <c r="P105" s="57"/>
+      <c r="Q105" s="57"/>
+      <c r="R105" s="57"/>
+      <c r="S105" s="58"/>
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="47" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B106" s="40" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C106" s="48">
         <v>7</v>
@@ -8564,7 +8567,7 @@
         <v>23</v>
       </c>
       <c r="E106" s="40" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F106" s="48" t="s">
         <v>25</v>
@@ -8606,15 +8609,15 @@
         <v>27</v>
       </c>
       <c r="S106" s="40" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="50" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B107" s="51" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C107" s="52">
         <v>7</v>
@@ -8623,7 +8626,7 @@
         <v>23</v>
       </c>
       <c r="E107" s="51" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F107" s="52" t="s">
         <v>25</v>
@@ -8665,15 +8668,15 @@
         <v>27</v>
       </c>
       <c r="S107" s="51" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B108" s="40" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C108" s="48">
         <v>7</v>
@@ -8682,7 +8685,7 @@
         <v>23</v>
       </c>
       <c r="E108" s="40" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F108" s="48" t="s">
         <v>25</v>
@@ -8724,15 +8727,15 @@
         <v>27</v>
       </c>
       <c r="S108" s="40" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="50" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B109" s="51" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C109" s="52">
         <v>7</v>
@@ -8741,7 +8744,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="51" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F109" s="52" t="s">
         <v>25</v>
@@ -8783,15 +8786,15 @@
         <v>27</v>
       </c>
       <c r="S109" s="51" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="47" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C110" s="48">
         <v>7</v>
@@ -8800,7 +8803,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="40" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F110" s="48" t="s">
         <v>25</v>
@@ -8842,38 +8845,38 @@
         <v>27</v>
       </c>
       <c r="S110" s="40" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111" s="56" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="B111" s="55"/>
-      <c r="C111" s="55"/>
-      <c r="D111" s="55"/>
-      <c r="E111" s="55"/>
-      <c r="F111" s="55"/>
-      <c r="G111" s="55"/>
-      <c r="H111" s="55"/>
-      <c r="I111" s="55"/>
-      <c r="J111" s="55"/>
-      <c r="K111" s="55"/>
-      <c r="L111" s="55"/>
-      <c r="M111" s="55"/>
-      <c r="N111" s="55"/>
-      <c r="O111" s="55"/>
-      <c r="P111" s="55"/>
-      <c r="Q111" s="55"/>
-      <c r="R111" s="55"/>
-      <c r="S111" s="56"/>
+      <c r="B111" s="57"/>
+      <c r="C111" s="57"/>
+      <c r="D111" s="57"/>
+      <c r="E111" s="57"/>
+      <c r="F111" s="57"/>
+      <c r="G111" s="57"/>
+      <c r="H111" s="57"/>
+      <c r="I111" s="57"/>
+      <c r="J111" s="57"/>
+      <c r="K111" s="57"/>
+      <c r="L111" s="57"/>
+      <c r="M111" s="57"/>
+      <c r="N111" s="57"/>
+      <c r="O111" s="57"/>
+      <c r="P111" s="57"/>
+      <c r="Q111" s="57"/>
+      <c r="R111" s="57"/>
+      <c r="S111" s="58"/>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="47" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B112" s="40" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C112" s="48">
         <v>8</v>
@@ -8882,7 +8885,7 @@
         <v>23</v>
       </c>
       <c r="E112" s="40" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F112" s="48" t="s">
         <v>25</v>
@@ -8924,15 +8927,15 @@
         <v>27</v>
       </c>
       <c r="S112" s="40" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="50" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B113" s="51" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C113" s="52">
         <v>8</v>
@@ -8941,7 +8944,7 @@
         <v>23</v>
       </c>
       <c r="E113" s="51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F113" s="52" t="s">
         <v>25</v>
@@ -8983,15 +8986,15 @@
         <v>27</v>
       </c>
       <c r="S113" s="51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="114" spans="1:19" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A114" s="47" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C114" s="48">
         <v>8</v>
@@ -9000,19 +9003,19 @@
         <v>23</v>
       </c>
       <c r="E114" s="40" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F114" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G114" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G114" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H114" s="48">
         <v>1</v>
       </c>
       <c r="I114" s="40" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J114" s="49">
         <v>1000</v>
@@ -9042,15 +9045,15 @@
         <v>27</v>
       </c>
       <c r="S114" s="40" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="50" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B115" s="51" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C115" s="52">
         <v>8</v>
@@ -9059,7 +9062,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="51" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F115" s="52" t="s">
         <v>25</v>
@@ -9101,15 +9104,15 @@
         <v>27</v>
       </c>
       <c r="S115" s="51" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="47" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B116" s="40" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C116" s="48">
         <v>8</v>
@@ -9118,7 +9121,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="40" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F116" s="48" t="s">
         <v>25</v>
@@ -9160,15 +9163,15 @@
         <v>27</v>
       </c>
       <c r="S116" s="40" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B117" s="51" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C117" s="52">
         <v>8</v>
@@ -9177,7 +9180,7 @@
         <v>23</v>
       </c>
       <c r="E117" s="51" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F117" s="52" t="s">
         <v>25</v>
@@ -9219,15 +9222,15 @@
         <v>27</v>
       </c>
       <c r="S117" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="47" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C118" s="48">
         <v>8</v>
@@ -9236,7 +9239,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="40" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F118" s="48" t="s">
         <v>25</v>
@@ -9278,15 +9281,15 @@
         <v>27</v>
       </c>
       <c r="S118" s="40" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="50" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B119" s="51" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C119" s="52">
         <v>8</v>
@@ -9295,7 +9298,7 @@
         <v>23</v>
       </c>
       <c r="E119" s="51" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F119" s="52" t="s">
         <v>25</v>
@@ -9337,15 +9340,15 @@
         <v>27</v>
       </c>
       <c r="S119" s="51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="47" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B120" s="40" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C120" s="48">
         <v>8</v>
@@ -9354,13 +9357,13 @@
         <v>23</v>
       </c>
       <c r="E120" s="40" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F120" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G120" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G120" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H120" s="48">
         <v>1</v>
@@ -9396,24 +9399,24 @@
         <v>27</v>
       </c>
       <c r="S120" s="40" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A121" s="47" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C121" s="48">
         <v>8</v>
       </c>
       <c r="D121" s="41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E121" s="40" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F121" s="48" t="s">
         <v>25</v>
@@ -9425,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="I121" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J121" s="49"/>
       <c r="K121" s="49"/>
@@ -9449,15 +9452,15 @@
         <v>27</v>
       </c>
       <c r="S121" s="40" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A122" s="47" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B122" s="40" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C122" s="48">
         <v>8</v>
@@ -9466,19 +9469,19 @@
         <v>23</v>
       </c>
       <c r="E122" s="40" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F122" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G122" s="40" t="s">
         <v>99</v>
-      </c>
-      <c r="G122" s="40" t="s">
-        <v>100</v>
       </c>
       <c r="H122" s="48">
         <v>1</v>
       </c>
       <c r="I122" s="40" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J122" s="49">
         <v>210</v>
@@ -9508,15 +9511,15 @@
         <v>27</v>
       </c>
       <c r="S122" s="40" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A123" s="50" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B123" s="51" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C123" s="52">
         <v>8</v>
@@ -9525,19 +9528,19 @@
         <v>23</v>
       </c>
       <c r="E123" s="51" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F123" s="52" t="s">
+        <v>126</v>
+      </c>
+      <c r="G123" s="51" t="s">
         <v>127</v>
-      </c>
-      <c r="G123" s="51" t="s">
-        <v>128</v>
       </c>
       <c r="H123" s="52">
         <v>1</v>
       </c>
       <c r="I123" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J123" s="53">
         <v>2800</v>
@@ -9564,18 +9567,18 @@
         <v>5800</v>
       </c>
       <c r="R123" s="52" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S123" s="51" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="124" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A124" s="47" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B124" s="40" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C124" s="48">
         <v>8</v>
@@ -9584,7 +9587,7 @@
         <v>23</v>
       </c>
       <c r="E124" s="40" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F124" s="48" t="s">
         <v>25</v>
@@ -9596,7 +9599,7 @@
         <v>1</v>
       </c>
       <c r="I124" s="40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J124" s="49">
         <v>42</v>
@@ -9624,7 +9627,7 @@
         <v>27</v>
       </c>
       <c r="S124" s="40" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -9659,53 +9662,53 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>470</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
+        <v>469</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
-        <v>471</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+        <v>470</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>475</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="C5" s="7" t="s">
         <v>478</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>479</v>
       </c>
       <c r="D5" s="8">
         <v>8</v>
@@ -9714,18 +9717,18 @@
         <v>10</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="C6" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D6" s="8">
         <v>1</v>
@@ -9734,18 +9737,18 @@
         <v>10</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="C7" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D7" s="8">
         <v>0.5</v>
@@ -9754,18 +9757,18 @@
         <v>10</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="C8" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D8" s="8">
         <v>0.5</v>
@@ -9774,18 +9777,18 @@
         <v>10</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="C9" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D9" s="8">
         <v>0.5</v>
@@ -9794,18 +9797,18 @@
         <v>10</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>478</v>
-      </c>
       <c r="C10" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D10" s="8">
         <v>0.5</v>
@@ -9814,342 +9817,342 @@
         <v>10</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="D11" s="8">
         <v>11</v>
       </c>
       <c r="E11" s="8"/>
       <c r="F11" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="D12" s="8">
         <v>9.5</v>
       </c>
       <c r="E12" s="8"/>
       <c r="F12" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>489</v>
       </c>
       <c r="D13" s="8">
         <v>8.5</v>
       </c>
       <c r="E13" s="8"/>
       <c r="F13" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B14" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D14" s="12">
         <v>13.5</v>
       </c>
       <c r="E14" s="12"/>
       <c r="F14" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C15" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D15" s="12">
         <v>11.5</v>
       </c>
       <c r="E15" s="12"/>
       <c r="F15" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C16" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D16" s="12">
         <v>8.5</v>
       </c>
       <c r="E16" s="12"/>
       <c r="F16" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C17" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D17" s="12">
         <v>6</v>
       </c>
       <c r="E17" s="12"/>
       <c r="F17" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C18" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D18" s="12">
         <v>1.5</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C19" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D19" s="12">
         <v>1</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>494</v>
-      </c>
       <c r="C20" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D20" s="12">
         <v>2</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="13" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C21" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D21" s="12">
         <v>3.5</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="13" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D22" s="12">
         <v>4</v>
       </c>
       <c r="E22" s="12"/>
       <c r="F22" s="13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D23" s="12">
         <v>4</v>
       </c>
       <c r="E23" s="12"/>
       <c r="F23" s="13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D24" s="12">
         <v>2.5</v>
       </c>
       <c r="E24" s="12"/>
       <c r="F24" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B25" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C25" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D25" s="12">
         <v>2</v>
       </c>
       <c r="E25" s="12"/>
       <c r="F25" s="13" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C26" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D26" s="12">
         <v>3</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C27" s="11" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D27" s="12">
         <v>0.5</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="13" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>503</v>
-      </c>
       <c r="C28" s="11" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D28" s="12">
         <v>4</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C29" s="15" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D29" s="16">
         <v>5</v>
@@ -10158,18 +10161,18 @@
         <v>10</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C30" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D30" s="16">
         <v>2</v>
@@ -10178,18 +10181,18 @@
         <v>10</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C31" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D31" s="16">
         <v>2</v>
@@ -10198,18 +10201,18 @@
         <v>10</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B32" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C32" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D32" s="16">
         <v>1.5</v>
@@ -10218,18 +10221,18 @@
         <v>10</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C33" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D33" s="16">
         <v>1.5</v>
@@ -10238,18 +10241,18 @@
         <v>10</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B34" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C34" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D34" s="16">
         <v>1</v>
@@ -10258,18 +10261,18 @@
         <v>10</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C35" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D35" s="16">
         <v>0.5</v>
@@ -10278,18 +10281,18 @@
         <v>10</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C36" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D36" s="16">
         <v>0.5</v>
@@ -10298,18 +10301,18 @@
         <v>10</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C37" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D37" s="16">
         <v>0.5</v>
@@ -10318,18 +10321,18 @@
         <v>10</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B38" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C38" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D38" s="16">
         <v>0.5</v>
@@ -10338,18 +10341,18 @@
         <v>10</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C39" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D39" s="16">
         <v>1</v>
@@ -10358,18 +10361,18 @@
         <v>10</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
+        <v>511</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>512</v>
       </c>
-      <c r="B40" s="15" t="s">
-        <v>513</v>
-      </c>
       <c r="C40" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D40" s="16">
         <v>0.5</v>
@@ -10378,18 +10381,18 @@
         <v>10</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
+        <v>524</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>525</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="C41" s="19" t="s">
         <v>526</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>527</v>
       </c>
       <c r="D41" s="20">
         <v>5</v>
@@ -10398,18 +10401,18 @@
         <v>5</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B42" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B42" s="19" t="s">
+      <c r="C42" s="19" t="s">
         <v>530</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D42" s="20">
         <v>0</v>
@@ -10418,18 +10421,18 @@
         <v>12</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B43" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B43" s="19" t="s">
+      <c r="C43" s="19" t="s">
         <v>530</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D43" s="20">
         <v>2</v>
@@ -10438,18 +10441,18 @@
         <v>12</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B44" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B44" s="19" t="s">
+      <c r="C44" s="19" t="s">
         <v>530</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D44" s="20">
         <v>4</v>
@@ -10458,18 +10461,18 @@
         <v>12</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18" t="s">
+        <v>528</v>
+      </c>
+      <c r="B45" s="19" t="s">
         <v>529</v>
       </c>
-      <c r="B45" s="19" t="s">
+      <c r="C45" s="19" t="s">
         <v>530</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>531</v>
       </c>
       <c r="D45" s="20">
         <v>6</v>
@@ -10478,18 +10481,18 @@
         <v>12</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D46" s="20">
         <v>1</v>
@@ -10498,18 +10501,18 @@
         <v>12</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D47" s="20">
         <v>2</v>
@@ -10518,18 +10521,18 @@
         <v>12</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D48" s="20">
         <v>3</v>
@@ -10538,18 +10541,18 @@
         <v>12</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D49" s="20">
         <v>4</v>
@@ -10558,18 +10561,18 @@
         <v>12</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D50" s="20">
         <v>5</v>
@@ -10578,18 +10581,18 @@
         <v>12</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="22" t="s">
+        <v>541</v>
+      </c>
+      <c r="B51" s="23" t="s">
         <v>542</v>
       </c>
-      <c r="B51" s="23" t="s">
-        <v>543</v>
-      </c>
       <c r="C51" s="23" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D51" s="24">
         <v>20</v>
@@ -10598,20 +10601,20 @@
         <v>20</v>
       </c>
       <c r="F51" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
+      <c r="A52" s="55"/>
+      <c r="B52" s="55"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="55"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
     </row>
     <row r="53" spans="1:6" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -10638,136 +10641,136 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>546</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+        <v>545</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>549</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
+        <v>550</v>
+      </c>
+      <c r="B4" s="27" t="s">
         <v>551</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="C4" s="27" t="s">
         <v>552</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="27" t="s">
         <v>553</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
+        <v>554</v>
+      </c>
+      <c r="B5" s="27" t="s">
         <v>555</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="C5" s="27" t="s">
         <v>556</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="D5" s="27" t="s">
         <v>557</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
+        <v>558</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>559</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>556</v>
-      </c>
-      <c r="C6" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>560</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
+        <v>561</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>562</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="C7" s="27" t="s">
         <v>563</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>564</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>567</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
+        <v>568</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>569</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="C9" s="27" t="s">
         <v>570</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="D9" s="27" t="s">
         <v>571</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
+        <v>572</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>573</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="C10" s="27" t="s">
         <v>574</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="D10" s="27" t="s">
         <v>575</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
+        <v>576</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>577</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="C11" s="27" t="s">
         <v>578</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="D11" s="27" t="s">
         <v>579</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -10791,180 +10794,180 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>581</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+        <v>580</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
     </row>
     <row r="2" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="59" t="s">
-        <v>582</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
+        <v>581</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
+        <v>582</v>
+      </c>
+      <c r="B4" s="28" t="s">
         <v>583</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="C4" s="28" t="s">
         <v>584</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="D4" s="28" t="s">
         <v>585</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B5" s="27" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>588</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>591</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>13</v>
       </c>
       <c r="C7" s="27" t="s">
+        <v>593</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>594</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="35" t="s">
+        <v>595</v>
+      </c>
+      <c r="B9" s="35" t="s">
         <v>596</v>
       </c>
-      <c r="B9" s="35" t="s">
+      <c r="C9" s="35" t="s">
         <v>597</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="D9" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="E9" s="36" t="s">
         <v>599</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>600</v>
+      </c>
+      <c r="B10" t="s">
         <v>601</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>602</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>603</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>604</v>
-      </c>
-      <c r="E10" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
+        <v>605</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>606</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="C11" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>607</v>
       </c>
-      <c r="C11" s="27" t="s">
-        <v>603</v>
-      </c>
-      <c r="D11" s="27" t="s">
+      <c r="E11" t="s">
         <v>608</v>
-      </c>
-      <c r="E11" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
+        <v>609</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>610</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="C12" s="27" t="s">
+        <v>602</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>611</v>
       </c>
-      <c r="C12" s="27" t="s">
-        <v>603</v>
-      </c>
-      <c r="D12" s="27" t="s">
+      <c r="E12" t="s">
         <v>612</v>
-      </c>
-      <c r="E12" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
+        <v>613</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>614</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="C13" s="27" t="s">
         <v>615</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="D13" s="27" t="s">
         <v>616</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="E13" t="s">
         <v>617</v>
-      </c>
-      <c r="E13" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="61"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="62" t="s">
-        <v>619</v>
-      </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
+        <v>618</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
     </row>
     <row r="16" spans="1:5" ht="132" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
   </sheetData>
@@ -10991,36 +10994,36 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>621</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
+        <v>620</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>624</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
+        <v>625</v>
+      </c>
+      <c r="B4" s="31" t="s">
         <v>626</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>627</v>
       </c>
       <c r="C4" s="32">
         <v>1.2</v>
@@ -11034,10 +11037,10 @@
     </row>
     <row r="5" spans="1:5" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30" t="s">
+        <v>627</v>
+      </c>
+      <c r="B5" s="31" t="s">
         <v>628</v>
-      </c>
-      <c r="B5" s="31" t="s">
-        <v>629</v>
       </c>
       <c r="C5" s="32">
         <v>1.1000000000000001</v>
@@ -11051,10 +11054,10 @@
     </row>
     <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30" t="s">
+        <v>629</v>
+      </c>
+      <c r="B6" s="31" t="s">
         <v>630</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>631</v>
       </c>
       <c r="C6" s="32">
         <v>1.05</v>
@@ -11068,10 +11071,10 @@
     </row>
     <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>632</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>633</v>
       </c>
       <c r="C7" s="32">
         <v>1</v>
@@ -11085,10 +11088,10 @@
     </row>
     <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B8" s="33" t="s">
         <v>634</v>
-      </c>
-      <c r="B8" s="33" t="s">
-        <v>635</v>
       </c>
       <c r="C8" s="34">
         <v>0.92</v>
@@ -11102,10 +11105,10 @@
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
+        <v>635</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>636</v>
-      </c>
-      <c r="B9" s="31" t="s">
-        <v>637</v>
       </c>
       <c r="C9" s="32">
         <v>0.91</v>
@@ -11119,10 +11122,10 @@
     </row>
     <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
+        <v>637</v>
+      </c>
+      <c r="B10" s="31" t="s">
         <v>638</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>639</v>
       </c>
       <c r="C10" s="32">
         <v>0.88</v>
@@ -11136,10 +11139,10 @@
     </row>
     <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
+        <v>639</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>640</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>641</v>
       </c>
       <c r="C11" s="32">
         <v>0.9</v>
@@ -11153,10 +11156,10 @@
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30" t="s">
+        <v>641</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>642</v>
-      </c>
-      <c r="B12" s="31" t="s">
-        <v>643</v>
       </c>
       <c r="C12" s="32">
         <v>0.87</v>
@@ -11170,10 +11173,10 @@
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
+        <v>643</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>644</v>
-      </c>
-      <c r="B13" s="31" t="s">
-        <v>645</v>
       </c>
       <c r="C13" s="32">
         <v>0.87</v>
@@ -11187,10 +11190,10 @@
     </row>
     <row r="14" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30" t="s">
+        <v>645</v>
+      </c>
+      <c r="B14" s="31" t="s">
         <v>646</v>
-      </c>
-      <c r="B14" s="31" t="s">
-        <v>647</v>
       </c>
       <c r="C14" s="32">
         <v>0.93</v>
@@ -11204,10 +11207,10 @@
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
+        <v>647</v>
+      </c>
+      <c r="B15" s="31" t="s">
         <v>648</v>
-      </c>
-      <c r="B15" s="31" t="s">
-        <v>649</v>
       </c>
       <c r="C15" s="32">
         <v>0.82</v>
@@ -11221,12 +11224,12 @@
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="59" t="s">
-        <v>650</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
+        <v>649</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11250,37 +11253,37 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>652</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
+        <v>651</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
     </row>
     <row r="4" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
+        <v>652</v>
+      </c>
+      <c r="B4" s="43" t="s">
         <v>653</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="C4" s="43" t="s">
         <v>654</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="D4" s="43" t="s">
         <v>655</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C5" s="45">
         <v>600</v>
@@ -11291,10 +11294,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C6" s="45">
         <v>700</v>
@@ -11305,10 +11308,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C7" s="45">
         <v>800</v>
@@ -11319,10 +11322,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" s="45">
         <v>1000</v>
@@ -11333,10 +11336,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="45">
         <v>1500</v>
@@ -11347,10 +11350,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C10" s="45">
         <v>500</v>
@@ -11361,10 +11364,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C11" s="45">
         <v>400</v>
@@ -11375,10 +11378,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="44" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B12" s="44" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C12" s="45">
         <v>500</v>
@@ -11389,10 +11392,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="44" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B13" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C13" s="45">
         <v>900</v>
@@ -11403,10 +11406,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="44" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B14" s="44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" s="45">
         <v>500</v>
@@ -11417,10 +11420,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B15" s="44" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C15" s="45">
         <v>1800</v>
@@ -11431,10 +11434,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B16" s="44" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="45">
         <v>1600</v>
@@ -11445,10 +11448,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B17" s="44" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C17" s="45">
         <v>2000</v>
@@ -11459,10 +11462,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B18" s="44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C18" s="45">
         <v>2200</v>
@@ -11473,10 +11476,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B19" s="44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19" s="45">
         <v>3000</v>
@@ -11487,10 +11490,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="44" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B20" s="44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C20" s="45">
         <v>900</v>

--- a/NRM1_Cost_Estimate_Tool_v4_5.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v4_5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBA7215-3F23-4322-836E-C3ED81F6A740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8CB13B-2BB0-4BE9-9D19-89039DCA18AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3082,7 +3082,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="56" t="s">
         <v>21</v>
       </c>
@@ -3105,7 +3105,7 @@
       <c r="R5" s="57"/>
       <c r="S5" s="58"/>
     </row>
-    <row r="6" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="47" t="s">
         <v>22</v>
       </c>
@@ -3164,7 +3164,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="50" t="s">
         <v>30</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="47" t="s">
         <v>34</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
         <v>37</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="56" t="s">
         <v>40</v>
       </c>
@@ -3364,7 +3364,7 @@
       <c r="R10" s="57"/>
       <c r="S10" s="58"/>
     </row>
-    <row r="11" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="47" t="s">
         <v>41</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="50" t="s">
         <v>44</v>
       </c>
@@ -3482,7 +3482,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="47" t="s">
         <v>47</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="50" t="s">
         <v>50</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="56" t="s">
         <v>52</v>
       </c>
@@ -3623,7 +3623,7 @@
       <c r="R15" s="57"/>
       <c r="S15" s="58"/>
     </row>
-    <row r="16" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="47" t="s">
         <v>53</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="50" t="s">
         <v>56</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="47" t="s">
         <v>59</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="50" t="s">
         <v>62</v>
       </c>
@@ -3859,7 +3859,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="47" t="s">
         <v>65</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A21" s="50" t="s">
         <v>68</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="s">
         <v>71</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="50" t="s">
         <v>74</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="25.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A24" s="47" t="s">
         <v>77</v>
       </c>
@@ -4212,19 +4212,19 @@
         <v>55</v>
       </c>
       <c r="L26" s="49">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="M26" s="49">
         <v>55</v>
       </c>
       <c r="N26" s="49">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="O26" s="49">
         <v>55</v>
       </c>
       <c r="P26" s="49">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="Q26" s="49">
         <v>0</v>
@@ -4271,19 +4271,19 @@
         <v>75</v>
       </c>
       <c r="L27" s="53">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="M27" s="53">
         <v>75</v>
       </c>
       <c r="N27" s="53">
-        <v>280</v>
+        <v>200</v>
       </c>
       <c r="O27" s="53">
         <v>80</v>
       </c>
       <c r="P27" s="53">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="Q27" s="53">
         <v>0</v>
@@ -6475,16 +6475,16 @@
         <v>90</v>
       </c>
       <c r="M68" s="49">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N68" s="49">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="O68" s="49">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="P68" s="49">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="Q68" s="49">
         <v>0</v>
@@ -6646,10 +6646,10 @@
         <v>30</v>
       </c>
       <c r="K71" s="53">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="L71" s="53">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="M71" s="53">
         <v>150</v>

--- a/NRM1_Cost_Estimate_Tool_v4_5.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v4_5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A8CB13B-2BB0-4BE9-9D19-89039DCA18AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82D837F-D013-4F01-BB0F-9BC784B83CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="663">
   <si>
     <t>MASTER COST TABLE | v4.5 June 2026</t>
   </si>
@@ -2005,7 +2005,16 @@
     <t>Applied to basment foot print High uncertainty; specialist estimate</t>
   </si>
   <si>
-    <t>GIFA (automatic, m2)/number of stories</t>
+    <t>footprint_rate</t>
+  </si>
+  <si>
+    <t>upperfloors_rate</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Soft strip of finishes &amp; fittings</t>
   </si>
 </sst>
 </file>
@@ -2015,7 +2024,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\-#,##0;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2118,6 +2127,18 @@
       <sz val="10"/>
       <color rgb="FF1A2E4A"/>
       <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -2250,7 +2271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2394,6 +2415,16 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2976,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -3342,1148 +3373,1144 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="50" t="s">
+        <v>661</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>661</v>
+      </c>
+      <c r="C10" s="52">
+        <v>0</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="F10" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="65"/>
+      <c r="I10" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" s="52">
+        <v>15</v>
+      </c>
+      <c r="K10" s="66">
+        <v>25</v>
+      </c>
+      <c r="L10" s="66">
+        <v>35</v>
+      </c>
+      <c r="M10" s="53">
+        <v>0</v>
+      </c>
+      <c r="N10" s="53">
+        <v>0</v>
+      </c>
+      <c r="O10" s="53">
+        <v>0</v>
+      </c>
+      <c r="P10" s="53">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="53">
+        <v>0</v>
+      </c>
+      <c r="R10" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S10" s="67"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="57"/>
-      <c r="S10" s="58"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="58"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B12" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C12" s="48">
         <v>1</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D12" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="40" t="s">
+      <c r="E12" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F12" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G12" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="H12" s="48">
+        <v>4</v>
+      </c>
+      <c r="I12" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="J12" s="49">
+        <v>0</v>
+      </c>
+      <c r="K12" s="49">
+        <v>0</v>
+      </c>
+      <c r="L12" s="49">
+        <v>0</v>
+      </c>
+      <c r="M12" s="49">
+        <v>80</v>
+      </c>
+      <c r="N12" s="49">
+        <v>120</v>
+      </c>
+      <c r="O12" s="49">
+        <v>80</v>
+      </c>
+      <c r="P12" s="49">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="49">
+        <v>0</v>
+      </c>
+      <c r="R12" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="40" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A13" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="52">
+        <v>1</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="51" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G13" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="H13" s="52">
+        <v>1</v>
+      </c>
+      <c r="I13" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="J13" s="53">
+        <v>0</v>
+      </c>
+      <c r="K13" s="53">
+        <v>0</v>
+      </c>
+      <c r="L13" s="53">
+        <v>0</v>
+      </c>
+      <c r="M13" s="53">
+        <v>160</v>
+      </c>
+      <c r="N13" s="53">
+        <v>220</v>
+      </c>
+      <c r="O13" s="53">
+        <v>160</v>
+      </c>
+      <c r="P13" s="53">
+        <v>250</v>
+      </c>
+      <c r="Q13" s="53">
+        <v>0</v>
+      </c>
+      <c r="R13" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13" s="51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="48">
+        <v>1</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="H14" s="48">
+        <v>4</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="J14" s="49">
+        <v>0</v>
+      </c>
+      <c r="K14" s="49">
+        <v>0</v>
+      </c>
+      <c r="L14" s="49">
+        <v>0</v>
+      </c>
+      <c r="M14" s="49">
+        <v>90</v>
+      </c>
+      <c r="N14" s="49">
+        <v>140</v>
+      </c>
+      <c r="O14" s="49">
+        <v>90</v>
+      </c>
+      <c r="P14" s="49">
+        <v>140</v>
+      </c>
+      <c r="Q14" s="49">
+        <v>0</v>
+      </c>
+      <c r="R14" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="52">
+        <v>1</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="H15" s="52">
+        <v>1</v>
+      </c>
+      <c r="I15" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="J15" s="53">
+        <v>0</v>
+      </c>
+      <c r="K15" s="53">
+        <v>0</v>
+      </c>
+      <c r="L15" s="53">
+        <v>0</v>
+      </c>
+      <c r="M15" s="53">
+        <v>900</v>
+      </c>
+      <c r="N15" s="53">
+        <v>1600</v>
+      </c>
+      <c r="O15" s="53">
+        <v>900</v>
+      </c>
+      <c r="P15" s="53">
+        <v>1600</v>
+      </c>
+      <c r="Q15" s="53">
+        <v>0</v>
+      </c>
+      <c r="R15" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S15" s="51" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="57"/>
+      <c r="O16" s="57"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="57"/>
+      <c r="R16" s="57"/>
+      <c r="S16" s="58"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="48">
+        <v>2</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="48">
+      <c r="H17" s="48">
         <v>4</v>
       </c>
-      <c r="I11" s="40" t="s">
+      <c r="I17" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="49">
-        <v>0</v>
-      </c>
-      <c r="K11" s="49">
-        <v>0</v>
-      </c>
-      <c r="L11" s="49">
-        <v>0</v>
-      </c>
-      <c r="M11" s="49">
+      <c r="J17" s="49">
+        <v>0</v>
+      </c>
+      <c r="K17" s="49">
+        <v>20</v>
+      </c>
+      <c r="L17" s="49">
+        <v>40</v>
+      </c>
+      <c r="M17" s="49">
+        <v>350</v>
+      </c>
+      <c r="N17" s="49">
+        <v>550</v>
+      </c>
+      <c r="O17" s="49">
+        <v>130</v>
+      </c>
+      <c r="P17" s="49">
+        <v>200</v>
+      </c>
+      <c r="Q17" s="49">
+        <v>0</v>
+      </c>
+      <c r="R17" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S17" s="40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A18" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="52">
+        <v>2</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="64" t="s">
+        <v>660</v>
+      </c>
+      <c r="H18" s="52">
+        <v>4</v>
+      </c>
+      <c r="I18" s="64" t="s">
+        <v>660</v>
+      </c>
+      <c r="J18" s="53">
+        <v>0</v>
+      </c>
+      <c r="K18" s="53">
+        <v>15</v>
+      </c>
+      <c r="L18" s="53">
+        <v>30</v>
+      </c>
+      <c r="M18" s="53">
+        <v>78</v>
+      </c>
+      <c r="N18" s="53">
+        <v>110</v>
+      </c>
+      <c r="O18" s="53">
+        <v>65</v>
+      </c>
+      <c r="P18" s="53">
+        <v>95</v>
+      </c>
+      <c r="Q18" s="53">
+        <v>0</v>
+      </c>
+      <c r="R18" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="51" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="48">
+        <v>2</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F19" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="H19" s="48">
+        <v>1</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>659</v>
+      </c>
+      <c r="J19" s="49">
+        <v>35</v>
+      </c>
+      <c r="K19" s="49">
+        <v>55</v>
+      </c>
+      <c r="L19" s="49">
+        <v>90</v>
+      </c>
+      <c r="M19" s="49">
+        <v>150</v>
+      </c>
+      <c r="N19" s="49">
+        <v>250</v>
+      </c>
+      <c r="O19" s="49">
+        <v>75</v>
+      </c>
+      <c r="P19" s="49">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="49">
+        <v>0</v>
+      </c>
+      <c r="R19" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="52">
+        <v>2</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="F20" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="52">
+        <v>2</v>
+      </c>
+      <c r="I20" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="53">
+        <v>10</v>
+      </c>
+      <c r="K20" s="53">
+        <v>15</v>
+      </c>
+      <c r="L20" s="53">
+        <v>25</v>
+      </c>
+      <c r="M20" s="53">
+        <v>20</v>
+      </c>
+      <c r="N20" s="53">
+        <v>35</v>
+      </c>
+      <c r="O20" s="53">
+        <v>20</v>
+      </c>
+      <c r="P20" s="53">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="53">
+        <v>0</v>
+      </c>
+      <c r="R20" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="48">
+        <v>2</v>
+      </c>
+      <c r="D21" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="40" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H21" s="48">
+        <v>1</v>
+      </c>
+      <c r="I21" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" s="49">
+        <v>30</v>
+      </c>
+      <c r="K21" s="49">
+        <v>60</v>
+      </c>
+      <c r="L21" s="49">
+        <v>110</v>
+      </c>
+      <c r="M21" s="49">
+        <v>450</v>
+      </c>
+      <c r="N21" s="49">
+        <v>650</v>
+      </c>
+      <c r="O21" s="49">
+        <v>450</v>
+      </c>
+      <c r="P21" s="49">
+        <v>650</v>
+      </c>
+      <c r="Q21" s="49">
+        <v>0</v>
+      </c>
+      <c r="R21" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" s="40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="52">
+        <v>2</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="52">
+        <v>1</v>
+      </c>
+      <c r="I22" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="53">
+        <v>100</v>
+      </c>
+      <c r="K22" s="53">
+        <v>150</v>
+      </c>
+      <c r="L22" s="53">
+        <v>200</v>
+      </c>
+      <c r="M22" s="53">
+        <v>250</v>
+      </c>
+      <c r="N22" s="53">
+        <v>350</v>
+      </c>
+      <c r="O22" s="53">
+        <v>250</v>
+      </c>
+      <c r="P22" s="53">
+        <v>350</v>
+      </c>
+      <c r="Q22" s="53">
+        <v>0</v>
+      </c>
+      <c r="R22" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="51" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" s="40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="48">
+        <v>2</v>
+      </c>
+      <c r="D23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="48">
+        <v>4</v>
+      </c>
+      <c r="I23" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="49">
+        <v>50</v>
+      </c>
+      <c r="K23" s="49">
         <v>80</v>
       </c>
-      <c r="N11" s="49">
+      <c r="L23" s="49">
         <v>120</v>
       </c>
-      <c r="O11" s="49">
+      <c r="M23" s="49">
         <v>80</v>
       </c>
-      <c r="P11" s="49">
+      <c r="N23" s="49">
         <v>120</v>
       </c>
-      <c r="Q11" s="49">
-        <v>0</v>
-      </c>
-      <c r="R11" s="48" t="s">
+      <c r="O23" s="49">
+        <v>80</v>
+      </c>
+      <c r="P23" s="49">
+        <v>120</v>
+      </c>
+      <c r="Q23" s="49">
+        <v>0</v>
+      </c>
+      <c r="R23" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S11" s="40" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="52">
+      <c r="S23" s="40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B24" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="52">
+        <v>2</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="F24" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G24" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="52">
         <v>1</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="I24" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="53">
+        <v>15</v>
+      </c>
+      <c r="K24" s="53">
+        <v>35</v>
+      </c>
+      <c r="L24" s="53">
+        <v>60</v>
+      </c>
+      <c r="M24" s="53">
+        <v>80</v>
+      </c>
+      <c r="N24" s="53">
+        <v>120</v>
+      </c>
+      <c r="O24" s="53">
+        <v>35</v>
+      </c>
+      <c r="P24" s="53">
+        <v>60</v>
+      </c>
+      <c r="Q24" s="53">
+        <v>0</v>
+      </c>
+      <c r="R24" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="51" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="47" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="48">
+        <v>2</v>
+      </c>
+      <c r="D25" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E25" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="48">
+        <v>1</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="49">
+        <v>12</v>
+      </c>
+      <c r="K25" s="49">
+        <v>22</v>
+      </c>
+      <c r="L25" s="49">
+        <v>40</v>
+      </c>
+      <c r="M25" s="49">
+        <v>15</v>
+      </c>
+      <c r="N25" s="49">
+        <v>28</v>
+      </c>
+      <c r="O25" s="49">
+        <v>12</v>
+      </c>
+      <c r="P25" s="49">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="49">
+        <v>0</v>
+      </c>
+      <c r="R25" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="57"/>
+      <c r="K26" s="57"/>
+      <c r="L26" s="57"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="57"/>
+      <c r="O26" s="57"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="57"/>
+      <c r="R26" s="57"/>
+      <c r="S26" s="58"/>
+    </row>
+    <row r="27" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C27" s="48">
+        <v>3</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="48">
+        <v>1</v>
+      </c>
+      <c r="I27" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="49">
+        <v>30</v>
+      </c>
+      <c r="K27" s="49">
+        <v>55</v>
+      </c>
+      <c r="L27" s="49">
+        <v>140</v>
+      </c>
+      <c r="M27" s="49">
+        <v>55</v>
+      </c>
+      <c r="N27" s="49">
+        <v>140</v>
+      </c>
+      <c r="O27" s="49">
+        <v>55</v>
+      </c>
+      <c r="P27" s="49">
+        <v>120</v>
+      </c>
+      <c r="Q27" s="49">
+        <v>0</v>
+      </c>
+      <c r="R27" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S27" s="40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="52">
+        <v>3</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="52">
+        <v>1</v>
+      </c>
+      <c r="I28" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="53">
         <v>45</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="K28" s="53">
+        <v>75</v>
+      </c>
+      <c r="L28" s="53">
+        <v>200</v>
+      </c>
+      <c r="M28" s="53">
+        <v>75</v>
+      </c>
+      <c r="N28" s="53">
+        <v>200</v>
+      </c>
+      <c r="O28" s="53">
+        <v>80</v>
+      </c>
+      <c r="P28" s="53">
+        <v>140</v>
+      </c>
+      <c r="Q28" s="53">
+        <v>0</v>
+      </c>
+      <c r="R28" s="52" t="s">
+        <v>27</v>
+      </c>
+      <c r="S28" s="51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="48">
+        <v>3</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="F29" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G29" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H12" s="52">
+      <c r="H29" s="48">
         <v>1</v>
       </c>
-      <c r="I12" s="51" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="53">
-        <v>0</v>
-      </c>
-      <c r="K12" s="53">
-        <v>0</v>
-      </c>
-      <c r="L12" s="53">
-        <v>0</v>
-      </c>
-      <c r="M12" s="53">
-        <v>160</v>
-      </c>
-      <c r="N12" s="53">
-        <v>220</v>
-      </c>
-      <c r="O12" s="53">
-        <v>160</v>
-      </c>
-      <c r="P12" s="53">
-        <v>250</v>
-      </c>
-      <c r="Q12" s="53">
-        <v>0</v>
-      </c>
-      <c r="R12" s="52" t="s">
+      <c r="I29" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="49">
+        <v>30</v>
+      </c>
+      <c r="K29" s="49">
+        <v>50</v>
+      </c>
+      <c r="L29" s="49">
+        <v>140</v>
+      </c>
+      <c r="M29" s="49">
+        <v>50</v>
+      </c>
+      <c r="N29" s="49">
+        <v>140</v>
+      </c>
+      <c r="O29" s="49">
+        <v>50</v>
+      </c>
+      <c r="P29" s="49">
+        <v>100</v>
+      </c>
+      <c r="Q29" s="49">
+        <v>0</v>
+      </c>
+      <c r="R29" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S12" s="51" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="48">
-        <v>1</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="48">
-        <v>4</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="49">
-        <v>0</v>
-      </c>
-      <c r="K13" s="49">
-        <v>0</v>
-      </c>
-      <c r="L13" s="49">
-        <v>0</v>
-      </c>
-      <c r="M13" s="49">
+      <c r="S29" s="40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A30" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="N13" s="49">
-        <v>140</v>
-      </c>
-      <c r="O13" s="49">
-        <v>90</v>
-      </c>
-      <c r="P13" s="49">
-        <v>140</v>
-      </c>
-      <c r="Q13" s="49">
-        <v>0</v>
-      </c>
-      <c r="R13" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S13" s="40" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="52">
-        <v>1</v>
-      </c>
-      <c r="D14" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="52">
-        <v>1</v>
-      </c>
-      <c r="I14" s="51" t="s">
-        <v>659</v>
-      </c>
-      <c r="J14" s="53">
-        <v>0</v>
-      </c>
-      <c r="K14" s="53">
-        <v>0</v>
-      </c>
-      <c r="L14" s="53">
-        <v>0</v>
-      </c>
-      <c r="M14" s="53">
-        <v>900</v>
-      </c>
-      <c r="N14" s="53">
-        <v>1600</v>
-      </c>
-      <c r="O14" s="53">
-        <v>900</v>
-      </c>
-      <c r="P14" s="53">
-        <v>1600</v>
-      </c>
-      <c r="Q14" s="53">
-        <v>0</v>
-      </c>
-      <c r="R14" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S14" s="51" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="57"/>
-      <c r="L15" s="57"/>
-      <c r="M15" s="57"/>
-      <c r="N15" s="57"/>
-      <c r="O15" s="57"/>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="57"/>
-      <c r="R15" s="57"/>
-      <c r="S15" s="58"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="48">
-        <v>2</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G16" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="48">
-        <v>4</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="49">
-        <v>0</v>
-      </c>
-      <c r="K16" s="49">
-        <v>20</v>
-      </c>
-      <c r="L16" s="49">
-        <v>40</v>
-      </c>
-      <c r="M16" s="49">
-        <v>350</v>
-      </c>
-      <c r="N16" s="49">
-        <v>550</v>
-      </c>
-      <c r="O16" s="49">
-        <v>130</v>
-      </c>
-      <c r="P16" s="49">
-        <v>200</v>
-      </c>
-      <c r="Q16" s="49">
-        <v>0</v>
-      </c>
-      <c r="R16" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S16" s="40" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="52">
-        <v>2</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>57</v>
-      </c>
-      <c r="F17" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="52">
-        <v>4</v>
-      </c>
-      <c r="I17" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="53">
-        <v>0</v>
-      </c>
-      <c r="K17" s="53">
-        <v>15</v>
-      </c>
-      <c r="L17" s="53">
-        <v>30</v>
-      </c>
-      <c r="M17" s="53">
-        <v>78</v>
-      </c>
-      <c r="N17" s="53">
-        <v>110</v>
-      </c>
-      <c r="O17" s="53">
-        <v>65</v>
-      </c>
-      <c r="P17" s="53">
-        <v>95</v>
-      </c>
-      <c r="Q17" s="53">
-        <v>0</v>
-      </c>
-      <c r="R17" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S17" s="51" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="48">
-        <v>2</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="48">
-        <v>1</v>
-      </c>
-      <c r="I18" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="49">
-        <v>35</v>
-      </c>
-      <c r="K18" s="49">
-        <v>55</v>
-      </c>
-      <c r="L18" s="49">
-        <v>90</v>
-      </c>
-      <c r="M18" s="49">
-        <v>150</v>
-      </c>
-      <c r="N18" s="49">
-        <v>250</v>
-      </c>
-      <c r="O18" s="49">
-        <v>75</v>
-      </c>
-      <c r="P18" s="49">
-        <v>120</v>
-      </c>
-      <c r="Q18" s="49">
-        <v>0</v>
-      </c>
-      <c r="R18" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S18" s="40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="52">
-        <v>2</v>
-      </c>
-      <c r="D19" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="52">
-        <v>2</v>
-      </c>
-      <c r="I19" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="53">
-        <v>10</v>
-      </c>
-      <c r="K19" s="53">
-        <v>15</v>
-      </c>
-      <c r="L19" s="53">
-        <v>25</v>
-      </c>
-      <c r="M19" s="53">
-        <v>20</v>
-      </c>
-      <c r="N19" s="53">
-        <v>35</v>
-      </c>
-      <c r="O19" s="53">
-        <v>20</v>
-      </c>
-      <c r="P19" s="53">
-        <v>35</v>
-      </c>
-      <c r="Q19" s="53">
-        <v>0</v>
-      </c>
-      <c r="R19" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S19" s="51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="48">
-        <v>2</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="48">
-        <v>1</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="49">
-        <v>30</v>
-      </c>
-      <c r="K20" s="49">
-        <v>60</v>
-      </c>
-      <c r="L20" s="49">
-        <v>110</v>
-      </c>
-      <c r="M20" s="49">
-        <v>450</v>
-      </c>
-      <c r="N20" s="49">
-        <v>650</v>
-      </c>
-      <c r="O20" s="49">
-        <v>450</v>
-      </c>
-      <c r="P20" s="49">
-        <v>650</v>
-      </c>
-      <c r="Q20" s="49">
-        <v>0</v>
-      </c>
-      <c r="R20" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S20" s="40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="52">
-        <v>2</v>
-      </c>
-      <c r="D21" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="51" t="s">
-        <v>69</v>
-      </c>
-      <c r="F21" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G21" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="52">
-        <v>1</v>
-      </c>
-      <c r="I21" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J21" s="53">
-        <v>100</v>
-      </c>
-      <c r="K21" s="53">
-        <v>150</v>
-      </c>
-      <c r="L21" s="53">
-        <v>200</v>
-      </c>
-      <c r="M21" s="53">
-        <v>250</v>
-      </c>
-      <c r="N21" s="53">
-        <v>350</v>
-      </c>
-      <c r="O21" s="53">
-        <v>250</v>
-      </c>
-      <c r="P21" s="53">
-        <v>350</v>
-      </c>
-      <c r="Q21" s="53">
-        <v>0</v>
-      </c>
-      <c r="R21" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S21" s="51" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
-        <v>71</v>
-      </c>
-      <c r="B22" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="48">
-        <v>2</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G22" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="48">
-        <v>4</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="49">
-        <v>50</v>
-      </c>
-      <c r="K22" s="49">
-        <v>80</v>
-      </c>
-      <c r="L22" s="49">
-        <v>120</v>
-      </c>
-      <c r="M22" s="49">
-        <v>80</v>
-      </c>
-      <c r="N22" s="49">
-        <v>120</v>
-      </c>
-      <c r="O22" s="49">
-        <v>80</v>
-      </c>
-      <c r="P22" s="49">
-        <v>120</v>
-      </c>
-      <c r="Q22" s="49">
-        <v>0</v>
-      </c>
-      <c r="R22" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S22" s="40" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="52">
-        <v>2</v>
-      </c>
-      <c r="D23" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="F23" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="52">
-        <v>1</v>
-      </c>
-      <c r="I23" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="53">
-        <v>15</v>
-      </c>
-      <c r="K23" s="53">
-        <v>35</v>
-      </c>
-      <c r="L23" s="53">
-        <v>60</v>
-      </c>
-      <c r="M23" s="53">
-        <v>80</v>
-      </c>
-      <c r="N23" s="53">
-        <v>120</v>
-      </c>
-      <c r="O23" s="53">
-        <v>35</v>
-      </c>
-      <c r="P23" s="53">
-        <v>60</v>
-      </c>
-      <c r="Q23" s="53">
-        <v>0</v>
-      </c>
-      <c r="R23" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S23" s="51" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
-        <v>77</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="C24" s="48">
-        <v>2</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G24" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="48">
-        <v>1</v>
-      </c>
-      <c r="I24" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="49">
-        <v>12</v>
-      </c>
-      <c r="K24" s="49">
-        <v>22</v>
-      </c>
-      <c r="L24" s="49">
-        <v>40</v>
-      </c>
-      <c r="M24" s="49">
-        <v>15</v>
-      </c>
-      <c r="N24" s="49">
-        <v>28</v>
-      </c>
-      <c r="O24" s="49">
-        <v>12</v>
-      </c>
-      <c r="P24" s="49">
-        <v>24</v>
-      </c>
-      <c r="Q24" s="49">
-        <v>0</v>
-      </c>
-      <c r="R24" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S24" s="40" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="57"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="58"/>
-    </row>
-    <row r="26" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="48">
-        <v>3</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="48">
-        <v>1</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="49">
-        <v>30</v>
-      </c>
-      <c r="K26" s="49">
-        <v>55</v>
-      </c>
-      <c r="L26" s="49">
-        <v>140</v>
-      </c>
-      <c r="M26" s="49">
-        <v>55</v>
-      </c>
-      <c r="N26" s="49">
-        <v>140</v>
-      </c>
-      <c r="O26" s="49">
-        <v>55</v>
-      </c>
-      <c r="P26" s="49">
-        <v>120</v>
-      </c>
-      <c r="Q26" s="49">
-        <v>0</v>
-      </c>
-      <c r="R26" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S26" s="40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="52">
-        <v>3</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="52">
-        <v>1</v>
-      </c>
-      <c r="I27" s="51" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="53">
-        <v>45</v>
-      </c>
-      <c r="K27" s="53">
-        <v>75</v>
-      </c>
-      <c r="L27" s="53">
-        <v>200</v>
-      </c>
-      <c r="M27" s="53">
-        <v>75</v>
-      </c>
-      <c r="N27" s="53">
-        <v>200</v>
-      </c>
-      <c r="O27" s="53">
-        <v>80</v>
-      </c>
-      <c r="P27" s="53">
-        <v>140</v>
-      </c>
-      <c r="Q27" s="53">
-        <v>0</v>
-      </c>
-      <c r="R27" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="S27" s="51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="48">
-        <v>3</v>
-      </c>
-      <c r="D28" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G28" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="48">
-        <v>1</v>
-      </c>
-      <c r="I28" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="49">
-        <v>30</v>
-      </c>
-      <c r="K28" s="49">
-        <v>50</v>
-      </c>
-      <c r="L28" s="49">
-        <v>140</v>
-      </c>
-      <c r="M28" s="49">
-        <v>50</v>
-      </c>
-      <c r="N28" s="49">
-        <v>140</v>
-      </c>
-      <c r="O28" s="49">
-        <v>50</v>
-      </c>
-      <c r="P28" s="49">
-        <v>100</v>
-      </c>
-      <c r="Q28" s="49">
-        <v>0</v>
-      </c>
-      <c r="R28" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S28" s="40" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="57"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="57"/>
-      <c r="J29" s="57"/>
-      <c r="K29" s="57"/>
-      <c r="L29" s="57"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="57"/>
-      <c r="O29" s="57"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="57"/>
-      <c r="R29" s="57"/>
-      <c r="S29" s="58"/>
-    </row>
-    <row r="30" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="47" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="48">
-        <v>4</v>
-      </c>
-      <c r="D30" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="40" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="48">
-        <v>1</v>
-      </c>
-      <c r="I30" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="49">
-        <v>10</v>
-      </c>
-      <c r="K30" s="49">
-        <v>45</v>
-      </c>
-      <c r="L30" s="49">
-        <v>100</v>
-      </c>
-      <c r="M30" s="49">
-        <v>15</v>
-      </c>
-      <c r="N30" s="49">
-        <v>50</v>
-      </c>
-      <c r="O30" s="49">
-        <v>10</v>
-      </c>
-      <c r="P30" s="49">
-        <v>40</v>
-      </c>
-      <c r="Q30" s="49">
-        <v>0</v>
-      </c>
-      <c r="R30" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S30" s="40" t="s">
-        <v>93</v>
-      </c>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="58"/>
     </row>
     <row r="31" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A31" s="47" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C31" s="48">
         <v>4</v>
       </c>
-      <c r="D31" s="41" t="s">
-        <v>96</v>
+      <c r="D31" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E31" s="40" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G31" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H31" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I31" s="40" t="s">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="J31" s="49">
-        <v>900</v>
+        <v>10</v>
       </c>
       <c r="K31" s="49">
-        <v>2000</v>
+        <v>45</v>
       </c>
       <c r="L31" s="49">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="M31" s="49">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="N31" s="49">
-        <v>3500</v>
+        <v>50</v>
       </c>
       <c r="O31" s="49">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="P31" s="49">
-        <v>3500</v>
+        <v>40</v>
       </c>
       <c r="Q31" s="49">
         <v>0</v>
@@ -4492,12 +4519,12 @@
         <v>27</v>
       </c>
       <c r="S31" s="40" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A32" s="47" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="B32" s="40" t="s">
         <v>95</v>
@@ -4506,10 +4533,10 @@
         <v>4</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E32" s="40" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F32" s="48" t="s">
         <v>98</v>
@@ -4524,22 +4551,22 @@
         <v>101</v>
       </c>
       <c r="J32" s="49">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="K32" s="49">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="L32" s="49">
         <v>3500</v>
       </c>
       <c r="M32" s="49">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="N32" s="49">
         <v>3500</v>
       </c>
       <c r="O32" s="49">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="P32" s="49">
         <v>3500</v>
@@ -4551,12 +4578,12 @@
         <v>27</v>
       </c>
       <c r="S32" s="40" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A33" s="47" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B33" s="40" t="s">
         <v>95</v>
@@ -4565,10 +4592,10 @@
         <v>4</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F33" s="48" t="s">
         <v>98</v>
@@ -4583,25 +4610,25 @@
         <v>101</v>
       </c>
       <c r="J33" s="49">
+        <v>1200</v>
+      </c>
+      <c r="K33" s="49">
+        <v>2200</v>
+      </c>
+      <c r="L33" s="49">
         <v>3500</v>
       </c>
-      <c r="K33" s="49">
-        <v>5500</v>
-      </c>
-      <c r="L33" s="49">
-        <v>8500</v>
-      </c>
       <c r="M33" s="49">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="N33" s="49">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="O33" s="49">
-        <v>5500</v>
+        <v>2200</v>
       </c>
       <c r="P33" s="49">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="Q33" s="49">
         <v>0</v>
@@ -4610,12 +4637,12 @@
         <v>27</v>
       </c>
       <c r="S33" s="40" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A34" s="47" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B34" s="40" t="s">
         <v>95</v>
@@ -4624,10 +4651,10 @@
         <v>4</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E34" s="40" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F34" s="48" t="s">
         <v>98</v>
@@ -4642,25 +4669,25 @@
         <v>101</v>
       </c>
       <c r="J34" s="49">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="K34" s="49">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="L34" s="49">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="M34" s="49">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="N34" s="49">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="O34" s="49">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="P34" s="49">
-        <v>6000</v>
+        <v>8500</v>
       </c>
       <c r="Q34" s="49">
         <v>0</v>
@@ -4669,12 +4696,12 @@
         <v>27</v>
       </c>
       <c r="S34" s="40" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A35" s="47" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B35" s="40" t="s">
         <v>95</v>
@@ -4683,10 +4710,10 @@
         <v>4</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E35" s="40" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F35" s="48" t="s">
         <v>98</v>
@@ -4701,25 +4728,25 @@
         <v>101</v>
       </c>
       <c r="J35" s="49">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="K35" s="49">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="L35" s="49">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="M35" s="49">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="N35" s="49">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="O35" s="49">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="P35" s="49">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="Q35" s="49">
         <v>0</v>
@@ -4728,24 +4755,24 @@
         <v>27</v>
       </c>
       <c r="S35" s="40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A36" s="47" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C36" s="48">
         <v>4</v>
       </c>
-      <c r="D36" s="40" t="s">
-        <v>23</v>
+      <c r="D36" s="41" t="s">
+        <v>116</v>
       </c>
       <c r="E36" s="40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F36" s="48" t="s">
         <v>98</v>
@@ -4757,28 +4784,28 @@
         <v>2</v>
       </c>
       <c r="I36" s="40" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="J36" s="49">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="K36" s="49">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="L36" s="49">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="M36" s="49">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="N36" s="49">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="O36" s="49">
-        <v>6000</v>
+        <v>4500</v>
       </c>
       <c r="P36" s="49">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="Q36" s="49">
         <v>0</v>
@@ -4787,54 +4814,54 @@
         <v>27</v>
       </c>
       <c r="S36" s="40" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" s="47" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B37" s="40" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C37" s="48">
         <v>4</v>
       </c>
-      <c r="D37" s="41" t="s">
-        <v>124</v>
+      <c r="D37" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E37" s="40" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F37" s="48" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G37" s="40" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="H37" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I37" s="40" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="J37" s="49">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="K37" s="49">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="L37" s="49">
         <v>10000</v>
       </c>
       <c r="M37" s="49">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="N37" s="49">
         <v>10000</v>
       </c>
       <c r="O37" s="49">
-        <v>7500</v>
+        <v>6000</v>
       </c>
       <c r="P37" s="49">
         <v>10000</v>
@@ -4843,143 +4870,145 @@
         <v>0</v>
       </c>
       <c r="R37" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S37" s="40" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A38" s="47" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C38" s="48">
         <v>4</v>
       </c>
-      <c r="D38" s="40" t="s">
-        <v>23</v>
+      <c r="D38" s="41" t="s">
+        <v>124</v>
       </c>
       <c r="E38" s="40" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="G38" s="40" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="H38" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" s="40" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="J38" s="49">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="K38" s="49">
-        <v>10</v>
+        <v>7500</v>
       </c>
       <c r="L38" s="49">
-        <v>15</v>
+        <v>10000</v>
       </c>
       <c r="M38" s="49">
-        <v>3</v>
+        <v>7500</v>
       </c>
       <c r="N38" s="49">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="O38" s="49">
-        <v>2</v>
+        <v>7500</v>
       </c>
       <c r="P38" s="49">
-        <v>8</v>
+        <v>10000</v>
       </c>
       <c r="Q38" s="49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R38" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S38" s="40" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="47" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B39" s="40" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C39" s="48">
         <v>4</v>
       </c>
-      <c r="D39" s="41" t="s">
-        <v>96</v>
+      <c r="D39" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E39" s="40" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F39" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G39" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H39" s="48">
         <v>1</v>
       </c>
       <c r="I39" s="40" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="J39" s="49">
-        <v>1200</v>
+        <v>5</v>
       </c>
       <c r="K39" s="49">
-        <v>2200</v>
+        <v>10</v>
       </c>
       <c r="L39" s="49">
-        <v>4500</v>
+        <v>15</v>
       </c>
       <c r="M39" s="49">
-        <v>2200</v>
+        <v>3</v>
       </c>
       <c r="N39" s="49">
-        <v>4500</v>
+        <v>10</v>
       </c>
       <c r="O39" s="49">
-        <v>2200</v>
+        <v>2</v>
       </c>
       <c r="P39" s="49">
-        <v>4500</v>
-      </c>
-      <c r="Q39" s="49"/>
+        <v>8</v>
+      </c>
+      <c r="Q39" s="49">
+        <v>5</v>
+      </c>
       <c r="R39" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S39" s="40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A40" s="47" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C40" s="48">
         <v>4</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>138</v>
+        <v>96</v>
       </c>
       <c r="E40" s="40" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="F40" s="48" t="s">
         <v>98</v>
@@ -4994,49 +5023,49 @@
         <v>135</v>
       </c>
       <c r="J40" s="49">
-        <v>550</v>
+        <v>1200</v>
       </c>
       <c r="K40" s="49">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="L40" s="49">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="M40" s="49">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="N40" s="49">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="O40" s="49">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="P40" s="49">
-        <v>2400</v>
+        <v>4500</v>
       </c>
       <c r="Q40" s="49"/>
       <c r="R40" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S40" s="40" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" s="47" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C41" s="48">
         <v>4</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E41" s="40" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F41" s="48" t="s">
         <v>98</v>
@@ -5051,49 +5080,49 @@
         <v>135</v>
       </c>
       <c r="J41" s="49">
-        <v>2500</v>
+        <v>550</v>
       </c>
       <c r="K41" s="49">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="L41" s="49">
-        <v>14000</v>
+        <v>2400</v>
       </c>
       <c r="M41" s="49">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="N41" s="49">
-        <v>14000</v>
+        <v>2400</v>
       </c>
       <c r="O41" s="49">
-        <v>5500</v>
+        <v>1100</v>
       </c>
       <c r="P41" s="49">
-        <v>14000</v>
+        <v>2400</v>
       </c>
       <c r="Q41" s="49"/>
       <c r="R41" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S41" s="40" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" s="47" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C42" s="48">
         <v>4</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="E42" s="40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F42" s="48" t="s">
         <v>98</v>
@@ -5108,89 +5137,93 @@
         <v>135</v>
       </c>
       <c r="J42" s="49">
-        <v>750</v>
+        <v>2500</v>
       </c>
       <c r="K42" s="49">
-        <v>1300</v>
+        <v>5500</v>
       </c>
       <c r="L42" s="49">
-        <v>2400</v>
+        <v>14000</v>
       </c>
       <c r="M42" s="49">
-        <v>1300</v>
+        <v>5500</v>
       </c>
       <c r="N42" s="49">
-        <v>2400</v>
-      </c>
-      <c r="O42" s="49"/>
-      <c r="P42" s="49"/>
+        <v>14000</v>
+      </c>
+      <c r="O42" s="49">
+        <v>5500</v>
+      </c>
+      <c r="P42" s="49">
+        <v>14000</v>
+      </c>
       <c r="Q42" s="49"/>
       <c r="R42" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S42" s="40" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" s="47" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C43" s="48">
         <v>4</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="E43" s="40" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F43" s="48" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G43" s="40" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="H43" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" s="40" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="J43" s="49">
-        <v>10000</v>
+        <v>750</v>
       </c>
       <c r="K43" s="49">
-        <v>22000</v>
+        <v>1300</v>
       </c>
       <c r="L43" s="49">
-        <v>50000</v>
+        <v>2400</v>
       </c>
       <c r="M43" s="49">
-        <v>22000</v>
+        <v>1300</v>
       </c>
       <c r="N43" s="49">
-        <v>50000</v>
+        <v>2400</v>
       </c>
       <c r="O43" s="49"/>
       <c r="P43" s="49"/>
       <c r="Q43" s="49"/>
       <c r="R43" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S43" s="40" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A44" s="47" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C44" s="48">
         <v>4</v>
@@ -5199,7 +5232,7 @@
         <v>149</v>
       </c>
       <c r="E44" s="40" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F44" s="48" t="s">
         <v>126</v>
@@ -5211,22 +5244,22 @@
         <v>3</v>
       </c>
       <c r="I44" s="40" t="s">
-        <v>154</v>
+        <v>121</v>
       </c>
       <c r="J44" s="49">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="K44" s="49">
-        <v>14000</v>
+        <v>22000</v>
       </c>
       <c r="L44" s="49">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="M44" s="49">
-        <v>14000</v>
+        <v>22000</v>
       </c>
       <c r="N44" s="49">
-        <v>28000</v>
+        <v>50000</v>
       </c>
       <c r="O44" s="49"/>
       <c r="P44" s="49"/>
@@ -5235,24 +5268,24 @@
         <v>100</v>
       </c>
       <c r="S44" s="40" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A45" s="47" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C45" s="48">
         <v>4</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E45" s="40" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F45" s="48" t="s">
         <v>126</v>
@@ -5261,25 +5294,25 @@
         <v>127</v>
       </c>
       <c r="H45" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I45" s="40" t="s">
         <v>154</v>
       </c>
       <c r="J45" s="49">
-        <v>9500</v>
+        <v>7000</v>
       </c>
       <c r="K45" s="49">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="L45" s="49">
-        <v>44000</v>
+        <v>28000</v>
       </c>
       <c r="M45" s="49">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="N45" s="49">
-        <v>44000</v>
+        <v>28000</v>
       </c>
       <c r="O45" s="49"/>
       <c r="P45" s="49"/>
@@ -5288,24 +5321,24 @@
         <v>100</v>
       </c>
       <c r="S45" s="40" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A46" s="47" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C46" s="48">
         <v>4</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="E46" s="40" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F46" s="48" t="s">
         <v>126</v>
@@ -5320,19 +5353,19 @@
         <v>154</v>
       </c>
       <c r="J46" s="49">
-        <v>28000</v>
+        <v>9500</v>
       </c>
       <c r="K46" s="49">
-        <v>28000</v>
+        <v>21000</v>
       </c>
       <c r="L46" s="49">
-        <v>65000</v>
+        <v>44000</v>
       </c>
       <c r="M46" s="49">
-        <v>28000</v>
+        <v>21000</v>
       </c>
       <c r="N46" s="49">
-        <v>65000</v>
+        <v>44000</v>
       </c>
       <c r="O46" s="49"/>
       <c r="P46" s="49"/>
@@ -5341,15 +5374,15 @@
         <v>100</v>
       </c>
       <c r="S46" s="40" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A47" s="47" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B47" s="40" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C47" s="48">
         <v>4</v>
@@ -5358,51 +5391,51 @@
         <v>160</v>
       </c>
       <c r="E47" s="40" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F47" s="48" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="G47" s="40" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="H47" s="48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I47" s="40" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J47" s="49">
-        <v>5200</v>
+        <v>28000</v>
       </c>
       <c r="K47" s="49">
-        <v>5200</v>
+        <v>28000</v>
       </c>
       <c r="L47" s="49">
-        <v>8000</v>
+        <v>65000</v>
       </c>
       <c r="M47" s="49">
-        <v>5200</v>
+        <v>28000</v>
       </c>
       <c r="N47" s="49">
-        <v>8000</v>
+        <v>65000</v>
       </c>
       <c r="O47" s="49"/>
       <c r="P47" s="49"/>
       <c r="Q47" s="49"/>
       <c r="R47" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S47" s="40" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A48" s="47" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B48" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C48" s="48">
         <v>4</v>
@@ -5411,7 +5444,7 @@
         <v>160</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F48" s="48" t="s">
         <v>98</v>
@@ -5420,205 +5453,205 @@
         <v>99</v>
       </c>
       <c r="H48" s="48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I48" s="40" t="s">
         <v>135</v>
       </c>
       <c r="J48" s="49">
-        <v>2800</v>
+        <v>5200</v>
       </c>
       <c r="K48" s="49">
         <v>5200</v>
       </c>
       <c r="L48" s="49">
-        <v>10500</v>
+        <v>8000</v>
       </c>
       <c r="M48" s="49">
         <v>5200</v>
       </c>
       <c r="N48" s="49">
-        <v>10500</v>
-      </c>
-      <c r="O48" s="49">
-        <v>5200</v>
-      </c>
-      <c r="P48" s="49">
-        <v>10500</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="O48" s="49"/>
+      <c r="P48" s="49"/>
       <c r="Q48" s="49"/>
       <c r="R48" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S48" s="40" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A49" s="47" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B49" s="40" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C49" s="48">
         <v>4</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E49" s="40" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F49" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G49" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H49" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I49" s="40" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="J49" s="49">
-        <v>440</v>
+        <v>2800</v>
       </c>
       <c r="K49" s="49">
-        <v>440</v>
+        <v>5200</v>
       </c>
       <c r="L49" s="49">
-        <v>720</v>
+        <v>10500</v>
       </c>
       <c r="M49" s="49">
-        <v>440</v>
+        <v>5200</v>
       </c>
       <c r="N49" s="49">
-        <v>720</v>
-      </c>
-      <c r="O49" s="49"/>
-      <c r="P49" s="49"/>
+        <v>10500</v>
+      </c>
+      <c r="O49" s="49">
+        <v>5200</v>
+      </c>
+      <c r="P49" s="49">
+        <v>10500</v>
+      </c>
       <c r="Q49" s="49"/>
       <c r="R49" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S49" s="40" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="47" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B50" s="40" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C50" s="48">
         <v>4</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="E50" s="40" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F50" s="48" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="G50" s="40" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="H50" s="48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I50" s="40" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J50" s="49">
-        <v>34000</v>
+        <v>440</v>
       </c>
       <c r="K50" s="49">
-        <v>34000</v>
+        <v>440</v>
       </c>
       <c r="L50" s="49">
-        <v>78000</v>
+        <v>720</v>
       </c>
       <c r="M50" s="49">
-        <v>34000</v>
+        <v>440</v>
       </c>
       <c r="N50" s="49">
-        <v>78000</v>
+        <v>720</v>
       </c>
       <c r="O50" s="49"/>
       <c r="P50" s="49"/>
       <c r="Q50" s="49"/>
       <c r="R50" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S50" s="40" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A51" s="47" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B51" s="40" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C51" s="48">
         <v>4</v>
       </c>
       <c r="D51" s="41" t="s">
-        <v>116</v>
+        <v>160</v>
       </c>
       <c r="E51" s="40" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F51" s="48" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="G51" s="40" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="H51" s="48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="40" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J51" s="49">
-        <v>1000</v>
+        <v>34000</v>
       </c>
       <c r="K51" s="49">
-        <v>1000</v>
+        <v>34000</v>
       </c>
       <c r="L51" s="49">
-        <v>1650</v>
+        <v>78000</v>
       </c>
       <c r="M51" s="49">
-        <v>1000</v>
+        <v>34000</v>
       </c>
       <c r="N51" s="49">
-        <v>1650</v>
+        <v>78000</v>
       </c>
       <c r="O51" s="49"/>
       <c r="P51" s="49"/>
       <c r="Q51" s="49"/>
       <c r="R51" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S51" s="40" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B52" s="40" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C52" s="48">
         <v>4</v>
@@ -5627,34 +5660,34 @@
         <v>116</v>
       </c>
       <c r="E52" s="40" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F52" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G52" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H52" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52" s="40" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="J52" s="49">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="K52" s="49">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="L52" s="49">
-        <v>130</v>
+        <v>1650</v>
       </c>
       <c r="M52" s="49">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="N52" s="49">
-        <v>130</v>
+        <v>1650</v>
       </c>
       <c r="O52" s="49"/>
       <c r="P52" s="49"/>
@@ -5663,24 +5696,24 @@
         <v>27</v>
       </c>
       <c r="S52" s="40" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A53" s="47" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B53" s="40" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C53" s="48">
         <v>4</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>184</v>
+        <v>116</v>
       </c>
       <c r="E53" s="40" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="F53" s="48" t="s">
         <v>25</v>
@@ -5695,19 +5728,19 @@
         <v>172</v>
       </c>
       <c r="J53" s="49">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="K53" s="49">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="L53" s="49">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="M53" s="49">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="N53" s="49">
-        <v>390</v>
+        <v>130</v>
       </c>
       <c r="O53" s="49"/>
       <c r="P53" s="49"/>
@@ -5716,15 +5749,15 @@
         <v>27</v>
       </c>
       <c r="S53" s="40" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A54" s="47" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B54" s="40" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C54" s="48">
         <v>4</v>
@@ -5733,34 +5766,34 @@
         <v>184</v>
       </c>
       <c r="E54" s="40" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F54" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G54" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H54" s="48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54" s="40" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="J54" s="49">
-        <v>5500</v>
+        <v>200</v>
       </c>
       <c r="K54" s="49">
-        <v>5500</v>
+        <v>200</v>
       </c>
       <c r="L54" s="49">
-        <v>10500</v>
+        <v>390</v>
       </c>
       <c r="M54" s="49">
-        <v>5500</v>
+        <v>200</v>
       </c>
       <c r="N54" s="49">
-        <v>10500</v>
+        <v>390</v>
       </c>
       <c r="O54" s="49"/>
       <c r="P54" s="49"/>
@@ -5769,24 +5802,24 @@
         <v>27</v>
       </c>
       <c r="S54" s="40" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B55" s="40" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C55" s="48">
         <v>4</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="E55" s="40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F55" s="48" t="s">
         <v>98</v>
@@ -5795,25 +5828,25 @@
         <v>99</v>
       </c>
       <c r="H55" s="48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I55" s="40" t="s">
         <v>135</v>
       </c>
       <c r="J55" s="49">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="K55" s="49">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="L55" s="49">
-        <v>16500</v>
+        <v>10500</v>
       </c>
       <c r="M55" s="49">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="N55" s="49">
-        <v>16500</v>
+        <v>10500</v>
       </c>
       <c r="O55" s="49"/>
       <c r="P55" s="49"/>
@@ -5822,51 +5855,51 @@
         <v>27</v>
       </c>
       <c r="S55" s="40" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B56" s="40" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C56" s="48">
         <v>4</v>
       </c>
       <c r="D56" s="41" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="E56" s="40" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F56" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G56" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H56" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="40" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="J56" s="49">
-        <v>110</v>
+        <v>6000</v>
       </c>
       <c r="K56" s="49">
-        <v>110</v>
+        <v>6000</v>
       </c>
       <c r="L56" s="49">
-        <v>200</v>
+        <v>16500</v>
       </c>
       <c r="M56" s="49">
-        <v>110</v>
+        <v>6000</v>
       </c>
       <c r="N56" s="49">
-        <v>200</v>
+        <v>16500</v>
       </c>
       <c r="O56" s="49"/>
       <c r="P56" s="49"/>
@@ -5875,15 +5908,15 @@
         <v>27</v>
       </c>
       <c r="S56" s="40" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A57" s="47" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B57" s="40" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C57" s="48">
         <v>4</v>
@@ -5892,34 +5925,34 @@
         <v>194</v>
       </c>
       <c r="E57" s="40" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F57" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G57" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H57" s="48">
         <v>1</v>
       </c>
       <c r="I57" s="40" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="J57" s="49">
-        <v>3500</v>
+        <v>110</v>
       </c>
       <c r="K57" s="49">
-        <v>3500</v>
+        <v>110</v>
       </c>
       <c r="L57" s="49">
-        <v>6800</v>
+        <v>200</v>
       </c>
       <c r="M57" s="49">
-        <v>3500</v>
+        <v>110</v>
       </c>
       <c r="N57" s="49">
-        <v>6800</v>
+        <v>200</v>
       </c>
       <c r="O57" s="49"/>
       <c r="P57" s="49"/>
@@ -5928,15 +5961,15 @@
         <v>27</v>
       </c>
       <c r="S57" s="40" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A58" s="47" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B58" s="40" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C58" s="48">
         <v>4</v>
@@ -5945,7 +5978,7 @@
         <v>194</v>
       </c>
       <c r="E58" s="40" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F58" s="48" t="s">
         <v>98</v>
@@ -5954,25 +5987,25 @@
         <v>99</v>
       </c>
       <c r="H58" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I58" s="40" t="s">
         <v>135</v>
       </c>
       <c r="J58" s="49">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="K58" s="49">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="L58" s="49">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="M58" s="49">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="N58" s="49">
-        <v>6500</v>
+        <v>6800</v>
       </c>
       <c r="O58" s="49"/>
       <c r="P58" s="49"/>
@@ -5981,15 +6014,15 @@
         <v>27</v>
       </c>
       <c r="S58" s="40" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A59" s="47" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B59" s="40" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C59" s="48">
         <v>4</v>
@@ -5998,104 +6031,104 @@
         <v>194</v>
       </c>
       <c r="E59" s="40" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F59" s="48" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G59" s="40" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="H59" s="48">
         <v>2</v>
       </c>
       <c r="I59" s="40" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="J59" s="49">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="K59" s="49">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="L59" s="49">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="M59" s="49">
-        <v>5500</v>
+        <v>3200</v>
       </c>
       <c r="N59" s="49">
-        <v>11000</v>
+        <v>6500</v>
       </c>
       <c r="O59" s="49"/>
       <c r="P59" s="49"/>
       <c r="Q59" s="49"/>
       <c r="R59" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S59" s="40" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A60" s="47" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B60" s="40" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C60" s="48">
         <v>4</v>
       </c>
       <c r="D60" s="41" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E60" s="40" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F60" s="48" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="G60" s="40" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="H60" s="48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="40" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="J60" s="49">
-        <v>120</v>
+        <v>5500</v>
       </c>
       <c r="K60" s="49">
-        <v>120</v>
+        <v>5500</v>
       </c>
       <c r="L60" s="49">
-        <v>290</v>
+        <v>11000</v>
       </c>
       <c r="M60" s="49">
-        <v>120</v>
+        <v>5500</v>
       </c>
       <c r="N60" s="49">
-        <v>290</v>
+        <v>11000</v>
       </c>
       <c r="O60" s="49"/>
       <c r="P60" s="49"/>
       <c r="Q60" s="49"/>
       <c r="R60" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S60" s="40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A61" s="47" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B61" s="40" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C61" s="48">
         <v>4</v>
@@ -6104,34 +6137,34 @@
         <v>207</v>
       </c>
       <c r="E61" s="40" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F61" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G61" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H61" s="48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I61" s="40" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="J61" s="49">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="K61" s="49">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="L61" s="49">
-        <v>560</v>
+        <v>290</v>
       </c>
       <c r="M61" s="49">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="N61" s="49">
-        <v>560</v>
+        <v>290</v>
       </c>
       <c r="O61" s="49"/>
       <c r="P61" s="49"/>
@@ -6140,15 +6173,15 @@
         <v>27</v>
       </c>
       <c r="S61" s="40" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A62" s="47" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B62" s="40" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C62" s="48">
         <v>4</v>
@@ -6157,34 +6190,34 @@
         <v>207</v>
       </c>
       <c r="E62" s="40" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F62" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G62" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H62" s="48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I62" s="40" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="J62" s="49">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="K62" s="49">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="L62" s="49">
-        <v>310</v>
+        <v>560</v>
       </c>
       <c r="M62" s="49">
-        <v>160</v>
+        <v>280</v>
       </c>
       <c r="N62" s="49">
-        <v>310</v>
+        <v>560</v>
       </c>
       <c r="O62" s="49"/>
       <c r="P62" s="49"/>
@@ -6193,678 +6226,672 @@
         <v>27</v>
       </c>
       <c r="S62" s="40" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B63" s="40" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C63" s="48">
         <v>4</v>
       </c>
       <c r="D63" s="41" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="E63" s="40" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F63" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G63" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H63" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="40" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="J63" s="49">
-        <v>600</v>
+        <v>160</v>
       </c>
       <c r="K63" s="49">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="L63" s="49">
-        <v>1800</v>
+        <v>310</v>
       </c>
       <c r="M63" s="49">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="N63" s="49">
-        <v>1800</v>
-      </c>
-      <c r="O63" s="49">
-        <v>900</v>
-      </c>
-      <c r="P63" s="49">
-        <v>1800</v>
-      </c>
-      <c r="Q63" s="49">
-        <v>0</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="O63" s="49"/>
+      <c r="P63" s="49"/>
+      <c r="Q63" s="49"/>
       <c r="R63" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S63" s="40" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B64" s="40" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C64" s="48">
         <v>4</v>
       </c>
       <c r="D64" s="41" t="s">
-        <v>222</v>
+        <v>124</v>
       </c>
       <c r="E64" s="40" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F64" s="48" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G64" s="40" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="H64" s="48">
         <v>2</v>
       </c>
       <c r="I64" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="J64" s="49">
+        <v>600</v>
+      </c>
+      <c r="K64" s="49">
+        <v>900</v>
+      </c>
+      <c r="L64" s="49">
+        <v>1800</v>
+      </c>
+      <c r="M64" s="49">
+        <v>900</v>
+      </c>
+      <c r="N64" s="49">
+        <v>1800</v>
+      </c>
+      <c r="O64" s="49">
+        <v>900</v>
+      </c>
+      <c r="P64" s="49">
+        <v>1800</v>
+      </c>
+      <c r="Q64" s="49">
+        <v>0</v>
+      </c>
+      <c r="R64" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S64" s="40" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A65" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="B65" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="C65" s="48">
+        <v>4</v>
+      </c>
+      <c r="D65" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="E65" s="40" t="s">
+        <v>223</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G65" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H65" s="48">
+        <v>2</v>
+      </c>
+      <c r="I65" s="40" t="s">
         <v>154</v>
       </c>
-      <c r="J64" s="49">
+      <c r="J65" s="49">
         <v>3000</v>
       </c>
-      <c r="K64" s="49">
+      <c r="K65" s="49">
         <v>6000</v>
       </c>
-      <c r="L64" s="49">
+      <c r="L65" s="49">
         <v>14000</v>
       </c>
-      <c r="M64" s="49">
+      <c r="M65" s="49">
         <v>6000</v>
       </c>
-      <c r="N64" s="49">
+      <c r="N65" s="49">
         <v>14000</v>
       </c>
-      <c r="O64" s="49">
+      <c r="O65" s="49">
         <v>6000</v>
       </c>
-      <c r="P64" s="49">
+      <c r="P65" s="49">
         <v>14000</v>
       </c>
-      <c r="Q64" s="49">
-        <v>0</v>
-      </c>
-      <c r="R64" s="48" t="s">
+      <c r="Q65" s="49">
+        <v>0</v>
+      </c>
+      <c r="R65" s="48" t="s">
         <v>100</v>
       </c>
-      <c r="S64" s="40" t="s">
+      <c r="S65" s="40" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A65" s="56" t="s">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="B65" s="57"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="57"/>
-      <c r="E65" s="57"/>
-      <c r="F65" s="57"/>
-      <c r="G65" s="57"/>
-      <c r="H65" s="57"/>
-      <c r="I65" s="57"/>
-      <c r="J65" s="57"/>
-      <c r="K65" s="57"/>
-      <c r="L65" s="57"/>
-      <c r="M65" s="57"/>
-      <c r="N65" s="57"/>
-      <c r="O65" s="57"/>
-      <c r="P65" s="57"/>
-      <c r="Q65" s="57"/>
-      <c r="R65" s="57"/>
-      <c r="S65" s="58"/>
-    </row>
-    <row r="66" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="47" t="s">
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
+      <c r="J66" s="57"/>
+      <c r="K66" s="57"/>
+      <c r="L66" s="57"/>
+      <c r="M66" s="57"/>
+      <c r="N66" s="57"/>
+      <c r="O66" s="57"/>
+      <c r="P66" s="57"/>
+      <c r="Q66" s="57"/>
+      <c r="R66" s="57"/>
+      <c r="S66" s="58"/>
+    </row>
+    <row r="67" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="B66" s="40" t="s">
+      <c r="B67" s="40" t="s">
         <v>226</v>
       </c>
-      <c r="C66" s="48">
+      <c r="C67" s="48">
         <v>5</v>
       </c>
-      <c r="D66" s="40" t="s">
+      <c r="D67" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E66" s="40" t="s">
+      <c r="E67" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="F66" s="48" t="s">
+      <c r="F67" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G66" s="40" t="s">
+      <c r="G67" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H66" s="48">
+      <c r="H67" s="48">
         <v>2</v>
       </c>
-      <c r="I66" s="40" t="s">
+      <c r="I67" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="J66" s="49">
+      <c r="J67" s="49">
         <v>30</v>
       </c>
-      <c r="K66" s="49">
+      <c r="K67" s="49">
         <v>65</v>
       </c>
-      <c r="L66" s="49">
+      <c r="L67" s="49">
         <v>110</v>
       </c>
-      <c r="M66" s="49">
+      <c r="M67" s="49">
         <v>30</v>
       </c>
-      <c r="N66" s="49">
+      <c r="N67" s="49">
         <v>45</v>
       </c>
-      <c r="O66" s="49">
+      <c r="O67" s="49">
         <v>20</v>
       </c>
-      <c r="P66" s="49">
+      <c r="P67" s="49">
         <v>45</v>
       </c>
-      <c r="Q66" s="49">
-        <v>0</v>
-      </c>
-      <c r="R66" s="48" t="s">
+      <c r="Q67" s="49">
+        <v>0</v>
+      </c>
+      <c r="R67" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S66" s="40" t="s">
+      <c r="S67" s="40" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A67" s="50" t="s">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A68" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="B67" s="51" t="s">
+      <c r="B68" s="51" t="s">
         <v>229</v>
       </c>
-      <c r="C67" s="52">
+      <c r="C68" s="52">
         <v>5</v>
       </c>
-      <c r="D67" s="51" t="s">
+      <c r="D68" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E67" s="51" t="s">
+      <c r="E68" s="51" t="s">
         <v>230</v>
       </c>
-      <c r="F67" s="52" t="s">
+      <c r="F68" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G67" s="51" t="s">
+      <c r="G68" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H67" s="52">
+      <c r="H68" s="52">
         <v>1</v>
       </c>
-      <c r="I67" s="51" t="s">
+      <c r="I68" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J67" s="53"/>
-      <c r="K67" s="53"/>
-      <c r="L67" s="53"/>
-      <c r="M67" s="53"/>
-      <c r="N67" s="53"/>
-      <c r="O67" s="53"/>
-      <c r="P67" s="53"/>
-      <c r="Q67" s="53"/>
-      <c r="R67" s="52" t="s">
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+      <c r="L68" s="53"/>
+      <c r="M68" s="53"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="53"/>
+      <c r="P68" s="53"/>
+      <c r="Q68" s="53"/>
+      <c r="R68" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S67" s="51"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="47" t="s">
+      <c r="S68" s="51"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A69" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="B68" s="40" t="s">
+      <c r="B69" s="40" t="s">
         <v>231</v>
       </c>
-      <c r="C68" s="48">
+      <c r="C69" s="48">
         <v>5</v>
       </c>
-      <c r="D68" s="40" t="s">
+      <c r="D69" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E68" s="40" t="s">
+      <c r="E69" s="40" t="s">
         <v>232</v>
       </c>
-      <c r="F68" s="48" t="s">
+      <c r="F69" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G68" s="40" t="s">
+      <c r="G69" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H68" s="48">
+      <c r="H69" s="48">
         <v>3</v>
       </c>
-      <c r="I68" s="40" t="s">
+      <c r="I69" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J68" s="49">
+      <c r="J69" s="49">
         <v>25</v>
       </c>
-      <c r="K68" s="49">
+      <c r="K69" s="49">
         <v>50</v>
       </c>
-      <c r="L68" s="49">
+      <c r="L69" s="49">
         <v>90</v>
       </c>
-      <c r="M68" s="49">
+      <c r="M69" s="49">
         <v>50</v>
       </c>
-      <c r="N68" s="49">
+      <c r="N69" s="49">
         <v>90</v>
       </c>
-      <c r="O68" s="49">
+      <c r="O69" s="49">
         <v>50</v>
       </c>
-      <c r="P68" s="49">
+      <c r="P69" s="49">
         <v>90</v>
       </c>
-      <c r="Q68" s="49">
-        <v>0</v>
-      </c>
-      <c r="R68" s="48" t="s">
+      <c r="Q69" s="49">
+        <v>0</v>
+      </c>
+      <c r="R69" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S68" s="40" t="s">
+      <c r="S69" s="40" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A69" s="50" t="s">
+    <row r="70" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A70" s="50" t="s">
         <v>234</v>
       </c>
-      <c r="B69" s="51" t="s">
+      <c r="B70" s="51" t="s">
         <v>234</v>
       </c>
-      <c r="C69" s="52">
+      <c r="C70" s="52">
         <v>5</v>
       </c>
-      <c r="D69" s="51" t="s">
+      <c r="D70" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="51" t="s">
+      <c r="E70" s="51" t="s">
         <v>235</v>
       </c>
-      <c r="F69" s="52" t="s">
+      <c r="F70" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="G69" s="51" t="s">
+      <c r="G70" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="H69" s="52">
+      <c r="H70" s="52">
         <v>2</v>
       </c>
-      <c r="I69" s="51" t="s">
+      <c r="I70" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="J69" s="53">
+      <c r="J70" s="53">
         <v>2500</v>
       </c>
-      <c r="K69" s="53">
+      <c r="K70" s="53">
         <v>3500</v>
       </c>
-      <c r="L69" s="53">
+      <c r="L70" s="53">
         <v>6000</v>
       </c>
-      <c r="M69" s="53">
-        <v>0</v>
-      </c>
-      <c r="N69" s="53">
-        <v>0</v>
-      </c>
-      <c r="O69" s="53">
-        <v>0</v>
-      </c>
-      <c r="P69" s="53">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="53">
-        <v>0</v>
-      </c>
-      <c r="R69" s="52" t="s">
+      <c r="M70" s="53">
+        <v>0</v>
+      </c>
+      <c r="N70" s="53">
+        <v>0</v>
+      </c>
+      <c r="O70" s="53">
+        <v>0</v>
+      </c>
+      <c r="P70" s="53">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="53">
+        <v>0</v>
+      </c>
+      <c r="R70" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="S69" s="51" t="s">
+      <c r="S70" s="51" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A70" s="47" t="s">
+    <row r="71" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A71" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="B70" s="40" t="s">
+      <c r="B71" s="40" t="s">
         <v>237</v>
       </c>
-      <c r="C70" s="48">
+      <c r="C71" s="48">
         <v>5</v>
       </c>
-      <c r="D70" s="40" t="s">
+      <c r="D71" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="40" t="s">
+      <c r="E71" s="40" t="s">
         <v>238</v>
       </c>
-      <c r="F70" s="48" t="s">
+      <c r="F71" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G70" s="40" t="s">
+      <c r="G71" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H70" s="48">
+      <c r="H71" s="48">
         <v>3</v>
       </c>
-      <c r="I70" s="40" t="s">
+      <c r="I71" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="J70" s="49">
+      <c r="J71" s="49">
         <v>20</v>
       </c>
-      <c r="K70" s="49">
+      <c r="K71" s="49">
         <v>45</v>
       </c>
-      <c r="L70" s="49">
+      <c r="L71" s="49">
         <v>90</v>
       </c>
-      <c r="M70" s="49">
+      <c r="M71" s="49">
         <v>40</v>
       </c>
-      <c r="N70" s="49">
+      <c r="N71" s="49">
         <v>70</v>
       </c>
-      <c r="O70" s="49">
+      <c r="O71" s="49">
         <v>25</v>
       </c>
-      <c r="P70" s="49">
+      <c r="P71" s="49">
         <v>60</v>
       </c>
-      <c r="Q70" s="49">
-        <v>0</v>
-      </c>
-      <c r="R70" s="48" t="s">
+      <c r="Q71" s="49">
+        <v>0</v>
+      </c>
+      <c r="R71" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S70" s="40" t="s">
+      <c r="S71" s="40" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="50" t="s">
+    <row r="72" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A72" s="50" t="s">
         <v>240</v>
       </c>
-      <c r="B71" s="51" t="s">
+      <c r="B72" s="51" t="s">
         <v>240</v>
       </c>
-      <c r="C71" s="52">
+      <c r="C72" s="52">
         <v>5</v>
       </c>
-      <c r="D71" s="51" t="s">
+      <c r="D72" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E71" s="51" t="s">
+      <c r="E72" s="51" t="s">
         <v>241</v>
       </c>
-      <c r="F71" s="52" t="s">
+      <c r="F72" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G71" s="51" t="s">
+      <c r="G72" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H71" s="52">
+      <c r="H72" s="52">
         <v>3</v>
       </c>
-      <c r="I71" s="51" t="s">
+      <c r="I72" s="51" t="s">
         <v>128</v>
       </c>
-      <c r="J71" s="53">
+      <c r="J72" s="53">
         <v>30</v>
       </c>
-      <c r="K71" s="53">
+      <c r="K72" s="53">
         <v>90</v>
       </c>
-      <c r="L71" s="53">
+      <c r="L72" s="53">
         <v>180</v>
       </c>
-      <c r="M71" s="53">
+      <c r="M72" s="53">
         <v>150</v>
       </c>
-      <c r="N71" s="53">
+      <c r="N72" s="53">
         <v>250</v>
       </c>
-      <c r="O71" s="53">
+      <c r="O72" s="53">
         <v>10</v>
       </c>
-      <c r="P71" s="53">
+      <c r="P72" s="53">
         <v>45</v>
       </c>
-      <c r="Q71" s="53">
-        <v>0</v>
-      </c>
-      <c r="R71" s="52" t="s">
+      <c r="Q72" s="53">
+        <v>0</v>
+      </c>
+      <c r="R72" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S71" s="51" t="s">
+      <c r="S72" s="51" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="51" x14ac:dyDescent="0.25">
-      <c r="A72" s="47" t="s">
+    <row r="73" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+      <c r="A73" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="B72" s="40" t="s">
+      <c r="B73" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="C72" s="48">
+      <c r="C73" s="48">
         <v>5</v>
       </c>
-      <c r="D72" s="40" t="s">
+      <c r="D73" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="40" t="s">
+      <c r="E73" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="F72" s="48" t="s">
+      <c r="F73" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G72" s="40" t="s">
+      <c r="G73" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H72" s="48">
+      <c r="H73" s="48">
         <v>3</v>
       </c>
-      <c r="I72" s="40" t="s">
+      <c r="I73" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J72" s="49">
+      <c r="J73" s="49">
         <v>5</v>
       </c>
-      <c r="K72" s="49">
+      <c r="K73" s="49">
         <v>10</v>
       </c>
-      <c r="L72" s="49">
+      <c r="L73" s="49">
         <v>15</v>
       </c>
-      <c r="M72" s="49">
+      <c r="M73" s="49">
         <v>8</v>
       </c>
-      <c r="N72" s="49">
+      <c r="N73" s="49">
         <v>15</v>
       </c>
-      <c r="O72" s="49">
+      <c r="O73" s="49">
         <v>5</v>
       </c>
-      <c r="P72" s="49">
+      <c r="P73" s="49">
         <v>10</v>
       </c>
-      <c r="Q72" s="49">
-        <v>0</v>
-      </c>
-      <c r="R72" s="48" t="s">
+      <c r="Q73" s="49">
+        <v>0</v>
+      </c>
+      <c r="R73" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S72" s="40" t="s">
+      <c r="S73" s="40" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="50" t="s">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A74" s="50" t="s">
         <v>246</v>
       </c>
-      <c r="B73" s="51" t="s">
+      <c r="B74" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="C73" s="52">
+      <c r="C74" s="52">
         <v>5</v>
       </c>
-      <c r="D73" s="51" t="s">
+      <c r="D74" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E73" s="51" t="s">
+      <c r="E74" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="F73" s="52" t="s">
+      <c r="F74" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G73" s="51" t="s">
+      <c r="G74" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H73" s="52">
+      <c r="H74" s="52">
         <v>3</v>
       </c>
-      <c r="I73" s="51" t="s">
+      <c r="I74" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="J73" s="53">
-        <v>0</v>
-      </c>
-      <c r="K73" s="53">
+      <c r="J74" s="53">
+        <v>0</v>
+      </c>
+      <c r="K74" s="53">
         <v>15</v>
       </c>
-      <c r="L73" s="53">
+      <c r="L74" s="53">
         <v>30</v>
       </c>
-      <c r="M73" s="53">
+      <c r="M74" s="53">
         <v>10</v>
       </c>
-      <c r="N73" s="53">
+      <c r="N74" s="53">
         <v>25</v>
       </c>
-      <c r="O73" s="53">
+      <c r="O74" s="53">
         <v>5</v>
       </c>
-      <c r="P73" s="53">
+      <c r="P74" s="53">
         <v>20</v>
       </c>
-      <c r="Q73" s="53">
-        <v>0</v>
-      </c>
-      <c r="R73" s="52" t="s">
+      <c r="Q74" s="53">
+        <v>0</v>
+      </c>
+      <c r="R74" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S73" s="51" t="s">
+      <c r="S74" s="51" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="47" t="s">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A75" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="B74" s="40" t="s">
+      <c r="B75" s="40" t="s">
         <v>249</v>
-      </c>
-      <c r="C74" s="48">
-        <v>5</v>
-      </c>
-      <c r="D74" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E74" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="F74" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G74" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" s="48">
-        <v>3</v>
-      </c>
-      <c r="I74" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J74" s="49">
-        <v>20</v>
-      </c>
-      <c r="K74" s="49">
-        <v>38</v>
-      </c>
-      <c r="L74" s="49">
-        <v>70</v>
-      </c>
-      <c r="M74" s="49">
-        <v>38</v>
-      </c>
-      <c r="N74" s="49">
-        <v>58</v>
-      </c>
-      <c r="O74" s="49">
-        <v>15</v>
-      </c>
-      <c r="P74" s="49">
-        <v>40</v>
-      </c>
-      <c r="Q74" s="49">
-        <v>0</v>
-      </c>
-      <c r="R74" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S74" s="40" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A75" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="B75" s="40" t="s">
-        <v>252</v>
       </c>
       <c r="C75" s="48">
         <v>5</v>
       </c>
-      <c r="D75" s="41" t="s">
-        <v>124</v>
+      <c r="D75" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E75" s="40" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F75" s="48" t="s">
         <v>25</v>
@@ -6879,25 +6906,25 @@
         <v>32</v>
       </c>
       <c r="J75" s="49">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K75" s="49">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L75" s="49">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="M75" s="49">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="N75" s="49">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="O75" s="49">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="P75" s="49">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="Q75" s="49">
         <v>0</v>
@@ -6906,24 +6933,24 @@
         <v>27</v>
       </c>
       <c r="S75" s="40" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A76" s="47" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B76" s="40" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C76" s="48">
         <v>5</v>
       </c>
-      <c r="D76" s="40" t="s">
-        <v>23</v>
+      <c r="D76" s="41" t="s">
+        <v>124</v>
       </c>
       <c r="E76" s="40" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F76" s="48" t="s">
         <v>25</v>
@@ -6932,31 +6959,31 @@
         <v>26</v>
       </c>
       <c r="H76" s="48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I76" s="40" t="s">
         <v>32</v>
       </c>
       <c r="J76" s="49">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K76" s="49">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="L76" s="49">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="M76" s="49">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="N76" s="49">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="O76" s="49">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="P76" s="49">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="Q76" s="49">
         <v>0</v>
@@ -6965,260 +6992,260 @@
         <v>27</v>
       </c>
       <c r="S76" s="40" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A77" s="47" t="s">
+        <v>255</v>
+      </c>
+      <c r="B77" s="40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C77" s="48">
+        <v>5</v>
+      </c>
+      <c r="D77" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="40" t="s">
+        <v>256</v>
+      </c>
+      <c r="F77" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="48">
+        <v>2</v>
+      </c>
+      <c r="I77" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J77" s="49">
+        <v>50</v>
+      </c>
+      <c r="K77" s="49">
+        <v>70</v>
+      </c>
+      <c r="L77" s="49">
+        <v>115</v>
+      </c>
+      <c r="M77" s="49">
+        <v>55</v>
+      </c>
+      <c r="N77" s="49">
+        <v>90</v>
+      </c>
+      <c r="O77" s="49">
+        <v>25</v>
+      </c>
+      <c r="P77" s="49">
+        <v>55</v>
+      </c>
+      <c r="Q77" s="49">
+        <v>0</v>
+      </c>
+      <c r="R77" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S77" s="40" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="50" t="s">
+    <row r="78" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A78" s="50" t="s">
         <v>258</v>
       </c>
-      <c r="B77" s="51" t="s">
+      <c r="B78" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="C77" s="52">
+      <c r="C78" s="52">
         <v>5</v>
       </c>
-      <c r="D77" s="51" t="s">
+      <c r="D78" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E77" s="51" t="s">
+      <c r="E78" s="51" t="s">
         <v>259</v>
       </c>
-      <c r="F77" s="52" t="s">
+      <c r="F78" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G77" s="51" t="s">
+      <c r="G78" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H77" s="52">
+      <c r="H78" s="52">
         <v>3</v>
       </c>
-      <c r="I77" s="51" t="s">
+      <c r="I78" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="J77" s="53">
+      <c r="J78" s="53">
         <v>22</v>
       </c>
-      <c r="K77" s="53">
+      <c r="K78" s="53">
         <v>32</v>
       </c>
-      <c r="L77" s="53">
+      <c r="L78" s="53">
         <v>50</v>
       </c>
-      <c r="M77" s="53">
-        <v>0</v>
-      </c>
-      <c r="N77" s="53">
-        <v>0</v>
-      </c>
-      <c r="O77" s="53">
-        <v>0</v>
-      </c>
-      <c r="P77" s="53">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="53">
-        <v>0</v>
-      </c>
-      <c r="R77" s="52" t="s">
+      <c r="M78" s="53">
+        <v>0</v>
+      </c>
+      <c r="N78" s="53">
+        <v>0</v>
+      </c>
+      <c r="O78" s="53">
+        <v>0</v>
+      </c>
+      <c r="P78" s="53">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="53">
+        <v>0</v>
+      </c>
+      <c r="R78" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S77" s="51" t="s">
+      <c r="S78" s="51" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A78" s="47" t="s">
+    <row r="79" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="47" t="s">
         <v>261</v>
       </c>
-      <c r="B78" s="40" t="s">
+      <c r="B79" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="C78" s="48">
+      <c r="C79" s="48">
         <v>5</v>
       </c>
-      <c r="D78" s="40" t="s">
+      <c r="D79" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E78" s="40" t="s">
+      <c r="E79" s="40" t="s">
         <v>262</v>
       </c>
-      <c r="F78" s="48" t="s">
+      <c r="F79" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G78" s="40" t="s">
+      <c r="G79" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H78" s="48">
+      <c r="H79" s="48">
         <v>2</v>
       </c>
-      <c r="I78" s="40" t="s">
+      <c r="I79" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J78" s="49">
+      <c r="J79" s="49">
         <v>13</v>
       </c>
-      <c r="K78" s="49">
+      <c r="K79" s="49">
         <v>15</v>
       </c>
-      <c r="L78" s="49">
+      <c r="L79" s="49">
         <v>30</v>
       </c>
-      <c r="M78" s="49">
-        <v>0</v>
-      </c>
-      <c r="N78" s="49">
-        <v>0</v>
-      </c>
-      <c r="O78" s="49">
-        <v>0</v>
-      </c>
-      <c r="P78" s="49">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="49">
-        <v>0</v>
-      </c>
-      <c r="R78" s="48" t="s">
+      <c r="M79" s="49">
+        <v>0</v>
+      </c>
+      <c r="N79" s="49">
+        <v>0</v>
+      </c>
+      <c r="O79" s="49">
+        <v>0</v>
+      </c>
+      <c r="P79" s="49">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="49">
+        <v>0</v>
+      </c>
+      <c r="R79" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S78" s="40" t="s">
+      <c r="S79" s="40" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A79" s="50" t="s">
+    <row r="80" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A80" s="50" t="s">
         <v>264</v>
       </c>
-      <c r="B79" s="51" t="s">
+      <c r="B80" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="C79" s="52">
+      <c r="C80" s="52">
         <v>5</v>
       </c>
-      <c r="D79" s="51" t="s">
+      <c r="D80" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="51" t="s">
+      <c r="E80" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="F79" s="52" t="s">
+      <c r="F80" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G79" s="51" t="s">
+      <c r="G80" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H79" s="52">
+      <c r="H80" s="52">
         <v>2</v>
       </c>
-      <c r="I79" s="51" t="s">
+      <c r="I80" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="J79" s="53">
+      <c r="J80" s="53">
         <v>15</v>
       </c>
-      <c r="K79" s="53">
+      <c r="K80" s="53">
         <v>23</v>
       </c>
-      <c r="L79" s="53">
+      <c r="L80" s="53">
         <v>37</v>
       </c>
-      <c r="M79" s="53">
+      <c r="M80" s="53">
         <v>12</v>
       </c>
-      <c r="N79" s="53">
+      <c r="N80" s="53">
         <v>22</v>
       </c>
-      <c r="O79" s="53">
+      <c r="O80" s="53">
         <v>8</v>
       </c>
-      <c r="P79" s="53">
+      <c r="P80" s="53">
         <v>15</v>
       </c>
-      <c r="Q79" s="53">
-        <v>0</v>
-      </c>
-      <c r="R79" s="52" t="s">
+      <c r="Q80" s="53">
+        <v>0</v>
+      </c>
+      <c r="R80" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S79" s="51" t="s">
+      <c r="S80" s="51" t="s">
         <v>266</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A80" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="B80" s="40" t="s">
-        <v>267</v>
-      </c>
-      <c r="C80" s="48">
-        <v>5</v>
-      </c>
-      <c r="D80" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E80" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="F80" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G80" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="48">
-        <v>3</v>
-      </c>
-      <c r="I80" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J80" s="49">
-        <v>10</v>
-      </c>
-      <c r="K80" s="49">
-        <v>18</v>
-      </c>
-      <c r="L80" s="49">
-        <v>30</v>
-      </c>
-      <c r="M80" s="49">
-        <v>14</v>
-      </c>
-      <c r="N80" s="49">
-        <v>20</v>
-      </c>
-      <c r="O80" s="49">
-        <v>8</v>
-      </c>
-      <c r="P80" s="49">
-        <v>15</v>
-      </c>
-      <c r="Q80" s="49">
-        <v>0</v>
-      </c>
-      <c r="R80" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S80" s="40" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A81" s="47" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B81" s="40" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C81" s="48">
         <v>5</v>
       </c>
-      <c r="D81" s="41" t="s">
-        <v>124</v>
+      <c r="D81" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E81" s="40" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F81" s="48" t="s">
         <v>25</v>
@@ -7233,25 +7260,25 @@
         <v>32</v>
       </c>
       <c r="J81" s="49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K81" s="49">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L81" s="49">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="M81" s="49">
+        <v>14</v>
+      </c>
+      <c r="N81" s="49">
+        <v>20</v>
+      </c>
+      <c r="O81" s="49">
         <v>8</v>
       </c>
-      <c r="N81" s="49">
-        <v>12</v>
-      </c>
-      <c r="O81" s="49">
-        <v>4</v>
-      </c>
       <c r="P81" s="49">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q81" s="49">
         <v>0</v>
@@ -7260,24 +7287,24 @@
         <v>27</v>
       </c>
       <c r="S81" s="40" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A82" s="47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B82" s="40" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C82" s="48">
         <v>5</v>
       </c>
-      <c r="D82" s="40" t="s">
-        <v>23</v>
+      <c r="D82" s="41" t="s">
+        <v>124</v>
       </c>
       <c r="E82" s="40" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F82" s="48" t="s">
         <v>25</v>
@@ -7286,7 +7313,7 @@
         <v>26</v>
       </c>
       <c r="H82" s="48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I82" s="40" t="s">
         <v>32</v>
@@ -7298,213 +7325,213 @@
         <v>10</v>
       </c>
       <c r="L82" s="49">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M82" s="49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N82" s="49">
         <v>12</v>
       </c>
       <c r="O82" s="49">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P82" s="49">
         <v>8</v>
       </c>
       <c r="Q82" s="49">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R82" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S82" s="40" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A83" s="47" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="C83" s="48">
+        <v>5</v>
+      </c>
+      <c r="D83" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="F83" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="48">
+        <v>1</v>
+      </c>
+      <c r="I83" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="J83" s="49">
+        <v>5</v>
+      </c>
+      <c r="K83" s="49">
+        <v>10</v>
+      </c>
+      <c r="L83" s="49">
+        <v>15</v>
+      </c>
+      <c r="M83" s="49">
+        <v>5</v>
+      </c>
+      <c r="N83" s="49">
+        <v>12</v>
+      </c>
+      <c r="O83" s="49">
+        <v>3</v>
+      </c>
+      <c r="P83" s="49">
+        <v>8</v>
+      </c>
+      <c r="Q83" s="49">
+        <v>10</v>
+      </c>
+      <c r="R83" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S83" s="40" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="50" t="s">
+    <row r="84" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A84" s="50" t="s">
         <v>276</v>
       </c>
-      <c r="B83" s="51" t="s">
+      <c r="B84" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="C83" s="52">
+      <c r="C84" s="52">
         <v>5</v>
       </c>
-      <c r="D83" s="51" t="s">
+      <c r="D84" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E83" s="51" t="s">
+      <c r="E84" s="51" t="s">
         <v>277</v>
       </c>
-      <c r="F83" s="52" t="s">
+      <c r="F84" s="52" t="s">
         <v>278</v>
       </c>
-      <c r="G83" s="51" t="s">
+      <c r="G84" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="H83" s="52">
+      <c r="H84" s="52">
         <v>3</v>
       </c>
-      <c r="I83" s="51" t="s">
+      <c r="I84" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="J83" s="53">
+      <c r="J84" s="53">
         <v>600</v>
       </c>
-      <c r="K83" s="53">
+      <c r="K84" s="53">
         <v>800</v>
       </c>
-      <c r="L83" s="53">
+      <c r="L84" s="53">
         <v>1200</v>
       </c>
-      <c r="M83" s="53">
+      <c r="M84" s="53">
         <v>800</v>
       </c>
-      <c r="N83" s="53">
+      <c r="N84" s="53">
         <v>1200</v>
       </c>
-      <c r="O83" s="53">
+      <c r="O84" s="53">
         <v>800</v>
       </c>
-      <c r="P83" s="53">
+      <c r="P84" s="53">
         <v>1200</v>
       </c>
-      <c r="Q83" s="53">
-        <v>0</v>
-      </c>
-      <c r="R83" s="52" t="s">
+      <c r="Q84" s="53">
+        <v>0</v>
+      </c>
+      <c r="R84" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="S83" s="51" t="s">
+      <c r="S84" s="51" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="47" t="s">
+    <row r="85" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="B84" s="40" t="s">
+      <c r="B85" s="40" t="s">
         <v>282</v>
-      </c>
-      <c r="C84" s="48">
-        <v>5</v>
-      </c>
-      <c r="D84" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E84" s="40" t="s">
-        <v>283</v>
-      </c>
-      <c r="F84" s="48" t="s">
-        <v>284</v>
-      </c>
-      <c r="G84" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="H84" s="48">
-        <v>3</v>
-      </c>
-      <c r="I84" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="J84" s="49">
-        <v>300</v>
-      </c>
-      <c r="K84" s="49">
-        <v>400</v>
-      </c>
-      <c r="L84" s="49">
-        <v>650</v>
-      </c>
-      <c r="M84" s="49">
-        <v>400</v>
-      </c>
-      <c r="N84" s="49">
-        <v>650</v>
-      </c>
-      <c r="O84" s="49">
-        <v>400</v>
-      </c>
-      <c r="P84" s="49">
-        <v>650</v>
-      </c>
-      <c r="Q84" s="49">
-        <v>0</v>
-      </c>
-      <c r="R84" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="S84" s="40" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A85" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="B85" s="40" t="s">
-        <v>288</v>
       </c>
       <c r="C85" s="48">
         <v>5</v>
       </c>
-      <c r="D85" s="41" t="s">
-        <v>124</v>
+      <c r="D85" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E85" s="40" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="F85" s="48" t="s">
-        <v>126</v>
+        <v>284</v>
       </c>
       <c r="G85" s="40" t="s">
-        <v>127</v>
+        <v>285</v>
       </c>
       <c r="H85" s="48">
         <v>3</v>
       </c>
       <c r="I85" s="40" t="s">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="J85" s="49">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="K85" s="49">
-        <v>40000</v>
+        <v>400</v>
       </c>
       <c r="L85" s="49">
-        <v>250000</v>
+        <v>650</v>
       </c>
       <c r="M85" s="49">
-        <v>40000</v>
+        <v>400</v>
       </c>
       <c r="N85" s="49">
-        <v>250000</v>
+        <v>650</v>
       </c>
       <c r="O85" s="49">
-        <v>40000</v>
+        <v>400</v>
       </c>
       <c r="P85" s="49">
-        <v>250000</v>
+        <v>650</v>
       </c>
       <c r="Q85" s="49">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="R85" s="48" t="s">
         <v>100</v>
       </c>
       <c r="S85" s="40" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A86" s="47" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C86" s="48">
         <v>5</v>
@@ -7513,175 +7540,175 @@
         <v>124</v>
       </c>
       <c r="E86" s="40" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F86" s="48" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="G86" s="40" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="H86" s="48">
         <v>3</v>
       </c>
       <c r="I86" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="J86" s="49">
+        <v>10000</v>
+      </c>
+      <c r="K86" s="49">
+        <v>40000</v>
+      </c>
+      <c r="L86" s="49">
+        <v>250000</v>
+      </c>
+      <c r="M86" s="49">
+        <v>40000</v>
+      </c>
+      <c r="N86" s="49">
+        <v>250000</v>
+      </c>
+      <c r="O86" s="49">
+        <v>40000</v>
+      </c>
+      <c r="P86" s="49">
+        <v>250000</v>
+      </c>
+      <c r="Q86" s="49">
+        <v>40000</v>
+      </c>
+      <c r="R86" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="S86" s="40" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A87" s="47" t="s">
+        <v>291</v>
+      </c>
+      <c r="B87" s="40" t="s">
+        <v>291</v>
+      </c>
+      <c r="C87" s="48">
+        <v>5</v>
+      </c>
+      <c r="D87" s="41" t="s">
+        <v>124</v>
+      </c>
+      <c r="E87" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="F87" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G87" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="48">
+        <v>3</v>
+      </c>
+      <c r="I87" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J86" s="49">
+      <c r="J87" s="49">
         <v>8</v>
       </c>
-      <c r="K86" s="49">
+      <c r="K87" s="49">
         <v>15</v>
       </c>
-      <c r="L86" s="49">
+      <c r="L87" s="49">
         <v>30</v>
       </c>
-      <c r="M86" s="49">
+      <c r="M87" s="49">
         <v>12</v>
       </c>
-      <c r="N86" s="49">
+      <c r="N87" s="49">
         <v>30</v>
       </c>
-      <c r="O86" s="49">
+      <c r="O87" s="49">
         <v>5</v>
       </c>
-      <c r="P86" s="49">
+      <c r="P87" s="49">
         <v>12</v>
       </c>
-      <c r="Q86" s="49">
-        <v>0</v>
-      </c>
-      <c r="R86" s="48" t="s">
+      <c r="Q87" s="49">
+        <v>0</v>
+      </c>
+      <c r="R87" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S86" s="40" t="s">
+      <c r="S87" s="40" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="50" t="s">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A88" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="B87" s="51" t="s">
+      <c r="B88" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="C87" s="52">
+      <c r="C88" s="52">
         <v>5</v>
       </c>
-      <c r="D87" s="51" t="s">
+      <c r="D88" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E87" s="51" t="s">
+      <c r="E88" s="51" t="s">
         <v>295</v>
       </c>
-      <c r="F87" s="52" t="s">
+      <c r="F88" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="G87" s="51" t="s">
+      <c r="G88" s="51" t="s">
         <v>99</v>
       </c>
-      <c r="H87" s="52">
+      <c r="H88" s="52">
         <v>3</v>
       </c>
-      <c r="I87" s="51" t="s">
+      <c r="I88" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="J87" s="53">
-        <v>0</v>
-      </c>
-      <c r="K87" s="53">
+      <c r="J88" s="53">
+        <v>0</v>
+      </c>
+      <c r="K88" s="53">
         <v>1500</v>
       </c>
-      <c r="L87" s="53">
+      <c r="L88" s="53">
         <v>2500</v>
       </c>
-      <c r="M87" s="53">
+      <c r="M88" s="53">
         <v>1500</v>
       </c>
-      <c r="N87" s="53">
+      <c r="N88" s="53">
         <v>2500</v>
       </c>
-      <c r="O87" s="53">
+      <c r="O88" s="53">
         <v>1500</v>
       </c>
-      <c r="P87" s="53">
+      <c r="P88" s="53">
         <v>2500</v>
       </c>
-      <c r="Q87" s="53">
+      <c r="Q88" s="53">
         <v>2000</v>
       </c>
-      <c r="R87" s="52" t="s">
+      <c r="R88" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S87" s="51" t="s">
+      <c r="S88" s="51" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="47" t="s">
-        <v>298</v>
-      </c>
-      <c r="B88" s="40" t="s">
-        <v>298</v>
-      </c>
-      <c r="C88" s="48">
-        <v>5</v>
-      </c>
-      <c r="D88" s="41" t="s">
-        <v>124</v>
-      </c>
-      <c r="E88" s="40" t="s">
-        <v>299</v>
-      </c>
-      <c r="F88" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G88" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="48">
-        <v>2</v>
-      </c>
-      <c r="I88" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J88" s="49">
-        <v>8</v>
-      </c>
-      <c r="K88" s="49">
-        <v>18</v>
-      </c>
-      <c r="L88" s="49">
-        <v>35</v>
-      </c>
-      <c r="M88" s="49">
-        <v>15</v>
-      </c>
-      <c r="N88" s="49">
-        <v>30</v>
-      </c>
-      <c r="O88" s="49">
-        <v>8</v>
-      </c>
-      <c r="P88" s="49">
-        <v>20</v>
-      </c>
-      <c r="Q88" s="49">
-        <v>0</v>
-      </c>
-      <c r="R88" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S88" s="40" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="47" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B89" s="40" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C89" s="48">
         <v>5</v>
@@ -7690,7 +7717,7 @@
         <v>124</v>
       </c>
       <c r="E89" s="40" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F89" s="48" t="s">
         <v>25</v>
@@ -7699,31 +7726,31 @@
         <v>26</v>
       </c>
       <c r="H89" s="48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I89" s="40" t="s">
         <v>32</v>
       </c>
       <c r="J89" s="49">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K89" s="49">
+        <v>18</v>
+      </c>
+      <c r="L89" s="49">
+        <v>35</v>
+      </c>
+      <c r="M89" s="49">
         <v>15</v>
       </c>
-      <c r="L89" s="49">
+      <c r="N89" s="49">
         <v>30</v>
       </c>
-      <c r="M89" s="49">
+      <c r="O89" s="49">
         <v>8</v>
       </c>
-      <c r="N89" s="49">
+      <c r="P89" s="49">
         <v>20</v>
-      </c>
-      <c r="O89" s="49">
-        <v>5</v>
-      </c>
-      <c r="P89" s="49">
-        <v>15</v>
       </c>
       <c r="Q89" s="49">
         <v>0</v>
@@ -7732,57 +7759,57 @@
         <v>27</v>
       </c>
       <c r="S89" s="40" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="47" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B90" s="40" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C90" s="48">
         <v>5</v>
       </c>
-      <c r="D90" s="40" t="s">
-        <v>23</v>
+      <c r="D90" s="41" t="s">
+        <v>124</v>
       </c>
       <c r="E90" s="40" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="F90" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G90" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H90" s="48">
         <v>3</v>
       </c>
       <c r="I90" s="40" t="s">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="J90" s="49">
-        <v>25000</v>
+        <v>5</v>
       </c>
       <c r="K90" s="49">
-        <v>40000</v>
+        <v>15</v>
       </c>
       <c r="L90" s="49">
-        <v>60000</v>
+        <v>30</v>
       </c>
       <c r="M90" s="49">
-        <v>40000</v>
+        <v>8</v>
       </c>
       <c r="N90" s="49">
-        <v>60000</v>
+        <v>20</v>
       </c>
       <c r="O90" s="49">
-        <v>40000</v>
+        <v>5</v>
       </c>
       <c r="P90" s="49">
-        <v>60000</v>
+        <v>15</v>
       </c>
       <c r="Q90" s="49">
         <v>0</v>
@@ -7791,242 +7818,248 @@
         <v>27</v>
       </c>
       <c r="S90" s="40" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A91" s="47" t="s">
+        <v>304</v>
+      </c>
+      <c r="B91" s="40" t="s">
+        <v>304</v>
+      </c>
+      <c r="C91" s="48">
+        <v>5</v>
+      </c>
+      <c r="D91" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="F91" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G91" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="H91" s="48">
+        <v>3</v>
+      </c>
+      <c r="I91" s="40" t="s">
+        <v>306</v>
+      </c>
+      <c r="J91" s="49">
+        <v>25000</v>
+      </c>
+      <c r="K91" s="49">
+        <v>40000</v>
+      </c>
+      <c r="L91" s="49">
+        <v>60000</v>
+      </c>
+      <c r="M91" s="49">
+        <v>40000</v>
+      </c>
+      <c r="N91" s="49">
+        <v>60000</v>
+      </c>
+      <c r="O91" s="49">
+        <v>40000</v>
+      </c>
+      <c r="P91" s="49">
+        <v>60000</v>
+      </c>
+      <c r="Q91" s="49">
+        <v>0</v>
+      </c>
+      <c r="R91" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S91" s="40" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="50" t="s">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A92" s="50" t="s">
         <v>308</v>
       </c>
-      <c r="B91" s="51" t="s">
+      <c r="B92" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="C91" s="52">
+      <c r="C92" s="52">
         <v>5</v>
       </c>
-      <c r="D91" s="51" t="s">
+      <c r="D92" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E91" s="51" t="s">
+      <c r="E92" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="F91" s="52" t="s">
+      <c r="F92" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G91" s="51" t="s">
+      <c r="G92" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H91" s="52">
+      <c r="H92" s="52">
         <v>3</v>
       </c>
-      <c r="I91" s="51" t="s">
+      <c r="I92" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="J91" s="53">
+      <c r="J92" s="53">
         <v>8</v>
       </c>
-      <c r="K91" s="53">
+      <c r="K92" s="53">
         <v>18</v>
       </c>
-      <c r="L91" s="53">
+      <c r="L92" s="53">
         <v>30</v>
       </c>
-      <c r="M91" s="53">
+      <c r="M92" s="53">
         <v>12</v>
       </c>
-      <c r="N91" s="53">
+      <c r="N92" s="53">
         <v>24</v>
       </c>
-      <c r="O91" s="53">
+      <c r="O92" s="53">
         <v>6</v>
       </c>
-      <c r="P91" s="53">
+      <c r="P92" s="53">
         <v>15</v>
       </c>
-      <c r="Q91" s="53">
-        <v>0</v>
-      </c>
-      <c r="R91" s="52" t="s">
+      <c r="Q92" s="53">
+        <v>0</v>
+      </c>
+      <c r="R92" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S91" s="51" t="s">
+      <c r="S92" s="51" t="s">
         <v>310</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A92" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="B92" s="40" t="s">
-        <v>311</v>
-      </c>
-      <c r="C92" s="48">
-        <v>5</v>
-      </c>
-      <c r="D92" s="41" t="s">
-        <v>312</v>
-      </c>
-      <c r="E92" s="40" t="s">
-        <v>313</v>
-      </c>
-      <c r="F92" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="G92" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="H92" s="48">
-        <v>3</v>
-      </c>
-      <c r="I92" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="J92" s="49">
-        <v>11000</v>
-      </c>
-      <c r="K92" s="49">
-        <v>11000</v>
-      </c>
-      <c r="L92" s="49">
-        <v>21000</v>
-      </c>
-      <c r="M92" s="49">
-        <v>11000</v>
-      </c>
-      <c r="N92" s="49">
-        <v>21000</v>
-      </c>
-      <c r="O92" s="49"/>
-      <c r="P92" s="49"/>
-      <c r="Q92" s="49"/>
-      <c r="R92" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="S92" s="40" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="47" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B93" s="40" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C93" s="48">
         <v>5</v>
       </c>
       <c r="D93" s="41" t="s">
-        <v>170</v>
+        <v>312</v>
       </c>
       <c r="E93" s="40" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="F93" s="48" t="s">
-        <v>25</v>
+        <v>126</v>
       </c>
       <c r="G93" s="40" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="H93" s="48">
         <v>3</v>
       </c>
       <c r="I93" s="40" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="J93" s="49">
-        <v>90</v>
+        <v>11000</v>
       </c>
       <c r="K93" s="49">
-        <v>90</v>
+        <v>11000</v>
       </c>
       <c r="L93" s="49">
-        <v>155</v>
+        <v>21000</v>
       </c>
       <c r="M93" s="49">
-        <v>90</v>
+        <v>11000</v>
       </c>
       <c r="N93" s="49">
-        <v>155</v>
+        <v>21000</v>
       </c>
       <c r="O93" s="49"/>
       <c r="P93" s="49"/>
       <c r="Q93" s="49"/>
       <c r="R93" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S93" s="40" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A94" s="47" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B94" s="40" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C94" s="48">
         <v>5</v>
       </c>
       <c r="D94" s="41" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
       <c r="E94" s="40" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F94" s="48" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="G94" s="40" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="H94" s="48">
         <v>3</v>
       </c>
       <c r="I94" s="40" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="J94" s="49">
-        <v>16000</v>
+        <v>90</v>
       </c>
       <c r="K94" s="49">
-        <v>16000</v>
+        <v>90</v>
       </c>
       <c r="L94" s="49">
-        <v>38000</v>
+        <v>155</v>
       </c>
       <c r="M94" s="49">
-        <v>16000</v>
+        <v>90</v>
       </c>
       <c r="N94" s="49">
-        <v>38000</v>
+        <v>155</v>
       </c>
       <c r="O94" s="49"/>
       <c r="P94" s="49"/>
       <c r="Q94" s="49"/>
       <c r="R94" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S94" s="40" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A95" s="47" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B95" s="40" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C95" s="48">
         <v>5</v>
       </c>
       <c r="D95" s="41" t="s">
-        <v>124</v>
+        <v>312</v>
       </c>
       <c r="E95" s="40" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F95" s="48" t="s">
         <v>126</v>
@@ -8041,19 +8074,19 @@
         <v>154</v>
       </c>
       <c r="J95" s="49">
-        <v>42000</v>
+        <v>16000</v>
       </c>
       <c r="K95" s="49">
-        <v>42000</v>
+        <v>16000</v>
       </c>
       <c r="L95" s="49">
-        <v>115000</v>
+        <v>38000</v>
       </c>
       <c r="M95" s="49">
-        <v>42000</v>
+        <v>16000</v>
       </c>
       <c r="N95" s="49">
-        <v>115000</v>
+        <v>38000</v>
       </c>
       <c r="O95" s="49"/>
       <c r="P95" s="49"/>
@@ -8062,15 +8095,15 @@
         <v>100</v>
       </c>
       <c r="S95" s="40" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A96" s="47" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B96" s="40" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C96" s="48">
         <v>5</v>
@@ -8079,7 +8112,7 @@
         <v>124</v>
       </c>
       <c r="E96" s="40" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F96" s="48" t="s">
         <v>126</v>
@@ -8094,19 +8127,19 @@
         <v>154</v>
       </c>
       <c r="J96" s="49">
-        <v>17000</v>
+        <v>42000</v>
       </c>
       <c r="K96" s="49">
-        <v>17000</v>
+        <v>42000</v>
       </c>
       <c r="L96" s="49">
-        <v>52000</v>
+        <v>115000</v>
       </c>
       <c r="M96" s="49">
-        <v>17000</v>
+        <v>42000</v>
       </c>
       <c r="N96" s="49">
-        <v>52000</v>
+        <v>115000</v>
       </c>
       <c r="O96" s="49"/>
       <c r="P96" s="49"/>
@@ -8115,271 +8148,265 @@
         <v>100</v>
       </c>
       <c r="S96" s="40" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A97" s="47" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B97" s="40" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C97" s="48">
         <v>5</v>
       </c>
       <c r="D97" s="41" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E97" s="40" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F97" s="48" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="G97" s="40" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="H97" s="48">
         <v>3</v>
       </c>
       <c r="I97" s="40" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="J97" s="49">
-        <v>620</v>
+        <v>17000</v>
       </c>
       <c r="K97" s="49">
-        <v>620</v>
+        <v>17000</v>
       </c>
       <c r="L97" s="49">
-        <v>1050</v>
+        <v>52000</v>
       </c>
       <c r="M97" s="49">
-        <v>620</v>
+        <v>17000</v>
       </c>
       <c r="N97" s="49">
-        <v>1050</v>
+        <v>52000</v>
       </c>
       <c r="O97" s="49"/>
       <c r="P97" s="49"/>
       <c r="Q97" s="49"/>
       <c r="R97" s="48" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="S97" s="40" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="98" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A98" s="47" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B98" s="40" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C98" s="48">
         <v>5</v>
       </c>
       <c r="D98" s="41" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="E98" s="40" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F98" s="48" t="s">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="G98" s="40" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="H98" s="48">
         <v>3</v>
       </c>
       <c r="I98" s="40" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="J98" s="49">
-        <v>32000</v>
+        <v>620</v>
       </c>
       <c r="K98" s="49">
-        <v>32000</v>
+        <v>620</v>
       </c>
       <c r="L98" s="49">
-        <v>88000</v>
+        <v>1050</v>
       </c>
       <c r="M98" s="49">
-        <v>32000</v>
+        <v>620</v>
       </c>
       <c r="N98" s="49">
-        <v>88000</v>
+        <v>1050</v>
       </c>
       <c r="O98" s="49"/>
       <c r="P98" s="49"/>
       <c r="Q98" s="49"/>
       <c r="R98" s="48" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="S98" s="40" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="99" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A99" s="47" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B99" s="40" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C99" s="48">
         <v>5</v>
       </c>
       <c r="D99" s="41" t="s">
+        <v>160</v>
+      </c>
+      <c r="E99" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="F99" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="G99" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="H99" s="48">
+        <v>3</v>
+      </c>
+      <c r="I99" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="J99" s="49">
+        <v>32000</v>
+      </c>
+      <c r="K99" s="49">
+        <v>32000</v>
+      </c>
+      <c r="L99" s="49">
+        <v>88000</v>
+      </c>
+      <c r="M99" s="49">
+        <v>32000</v>
+      </c>
+      <c r="N99" s="49">
+        <v>88000</v>
+      </c>
+      <c r="O99" s="49"/>
+      <c r="P99" s="49"/>
+      <c r="Q99" s="49"/>
+      <c r="R99" s="48" t="s">
+        <v>100</v>
+      </c>
+      <c r="S99" s="40" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="47" t="s">
+        <v>333</v>
+      </c>
+      <c r="B100" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C100" s="48">
+        <v>5</v>
+      </c>
+      <c r="D100" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="E99" s="40" t="s">
+      <c r="E100" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="F99" s="48" t="s">
+      <c r="F100" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="G99" s="40" t="s">
+      <c r="G100" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="H99" s="48">
+      <c r="H100" s="48">
         <v>2</v>
       </c>
-      <c r="I99" s="40" t="s">
+      <c r="I100" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="J99" s="49">
+      <c r="J100" s="49">
         <v>500</v>
       </c>
-      <c r="K99" s="49">
+      <c r="K100" s="49">
         <v>700</v>
       </c>
-      <c r="L99" s="49">
+      <c r="L100" s="49">
         <v>1200</v>
       </c>
-      <c r="M99" s="49">
+      <c r="M100" s="49">
         <v>700</v>
       </c>
-      <c r="N99" s="49">
+      <c r="N100" s="49">
         <v>1200</v>
       </c>
-      <c r="O99" s="49">
+      <c r="O100" s="49">
         <v>700</v>
       </c>
-      <c r="P99" s="49">
+      <c r="P100" s="49">
         <v>1200</v>
       </c>
-      <c r="Q99" s="49">
-        <v>0</v>
-      </c>
-      <c r="R99" s="48" t="s">
+      <c r="Q100" s="49">
+        <v>0</v>
+      </c>
+      <c r="R100" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S99" s="40" t="s">
+      <c r="S100" s="40" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A100" s="56" t="s">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" s="56" t="s">
         <v>337</v>
       </c>
-      <c r="B100" s="57"/>
-      <c r="C100" s="57"/>
-      <c r="D100" s="57"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="57"/>
-      <c r="G100" s="57"/>
-      <c r="H100" s="57"/>
-      <c r="I100" s="57"/>
-      <c r="J100" s="57"/>
-      <c r="K100" s="57"/>
-      <c r="L100" s="57"/>
-      <c r="M100" s="57"/>
-      <c r="N100" s="57"/>
-      <c r="O100" s="57"/>
-      <c r="P100" s="57"/>
-      <c r="Q100" s="57"/>
-      <c r="R100" s="57"/>
-      <c r="S100" s="58"/>
-    </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A101" s="47" t="s">
-        <v>338</v>
-      </c>
-      <c r="B101" s="40" t="s">
-        <v>338</v>
-      </c>
-      <c r="C101" s="48">
-        <v>6</v>
-      </c>
-      <c r="D101" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E101" s="40" t="s">
-        <v>339</v>
-      </c>
-      <c r="F101" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="G101" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="48">
-        <v>1</v>
-      </c>
-      <c r="I101" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="J101" s="49">
-        <v>0</v>
-      </c>
-      <c r="K101" s="49">
-        <v>0</v>
-      </c>
-      <c r="L101" s="49">
-        <v>200</v>
-      </c>
-      <c r="M101" s="49">
-        <v>0</v>
-      </c>
-      <c r="N101" s="49">
-        <v>150</v>
-      </c>
-      <c r="O101" s="49">
-        <v>0</v>
-      </c>
-      <c r="P101" s="49">
-        <v>100</v>
-      </c>
-      <c r="Q101" s="49">
-        <v>0</v>
-      </c>
-      <c r="R101" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S101" s="40" t="s">
-        <v>340</v>
-      </c>
+      <c r="B101" s="57"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="57"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="57"/>
+      <c r="G101" s="57"/>
+      <c r="H101" s="57"/>
+      <c r="I101" s="57"/>
+      <c r="J101" s="57"/>
+      <c r="K101" s="57"/>
+      <c r="L101" s="57"/>
+      <c r="M101" s="57"/>
+      <c r="N101" s="57"/>
+      <c r="O101" s="57"/>
+      <c r="P101" s="57"/>
+      <c r="Q101" s="57"/>
+      <c r="R101" s="57"/>
+      <c r="S101" s="58"/>
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B102" s="40" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C102" s="48">
         <v>6</v>
       </c>
-      <c r="D102" s="41" t="s">
-        <v>342</v>
+      <c r="D102" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E102" s="40" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F102" s="48" t="s">
         <v>25</v>
@@ -8394,25 +8421,25 @@
         <v>28</v>
       </c>
       <c r="J102" s="49">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K102" s="49">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L102" s="49">
+        <v>200</v>
+      </c>
+      <c r="M102" s="49">
+        <v>0</v>
+      </c>
+      <c r="N102" s="49">
+        <v>150</v>
+      </c>
+      <c r="O102" s="49">
+        <v>0</v>
+      </c>
+      <c r="P102" s="49">
         <v>100</v>
-      </c>
-      <c r="M102" s="49">
-        <v>60</v>
-      </c>
-      <c r="N102" s="49">
-        <v>80</v>
-      </c>
-      <c r="O102" s="49">
-        <v>0</v>
-      </c>
-      <c r="P102" s="49">
-        <v>60</v>
       </c>
       <c r="Q102" s="49">
         <v>0</v>
@@ -8421,104 +8448,110 @@
         <v>27</v>
       </c>
       <c r="S102" s="40" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="103" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="47" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B103" s="40" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C103" s="48">
         <v>6</v>
       </c>
       <c r="D103" s="41" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E103" s="40" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F103" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G103" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H103" s="48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I103" s="40" t="s">
-        <v>101</v>
+        <v>28</v>
       </c>
       <c r="J103" s="49">
-        <v>3200</v>
+        <v>25</v>
       </c>
       <c r="K103" s="49">
-        <v>5800</v>
+        <v>50</v>
       </c>
       <c r="L103" s="49">
-        <v>10500</v>
+        <v>100</v>
       </c>
       <c r="M103" s="49">
-        <v>5800</v>
+        <v>60</v>
       </c>
       <c r="N103" s="49">
-        <v>10500</v>
-      </c>
-      <c r="O103" s="49"/>
-      <c r="P103" s="49"/>
-      <c r="Q103" s="49"/>
+        <v>80</v>
+      </c>
+      <c r="O103" s="49">
+        <v>0</v>
+      </c>
+      <c r="P103" s="49">
+        <v>60</v>
+      </c>
+      <c r="Q103" s="49">
+        <v>0</v>
+      </c>
       <c r="R103" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S103" s="40" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A104" s="47" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C104" s="48">
         <v>6</v>
       </c>
       <c r="D104" s="41" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E104" s="40" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F104" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G104" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H104" s="48">
         <v>4</v>
       </c>
       <c r="I104" s="40" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="J104" s="49">
-        <v>380</v>
+        <v>3200</v>
       </c>
       <c r="K104" s="49">
-        <v>380</v>
+        <v>5800</v>
       </c>
       <c r="L104" s="49">
-        <v>860</v>
+        <v>10500</v>
       </c>
       <c r="M104" s="49">
-        <v>380</v>
+        <v>5800</v>
       </c>
       <c r="N104" s="49">
-        <v>860</v>
+        <v>10500</v>
       </c>
       <c r="O104" s="49"/>
       <c r="P104" s="49"/>
@@ -8527,1122 +8560,1176 @@
         <v>27</v>
       </c>
       <c r="S104" s="40" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+      <c r="A105" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="B105" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C105" s="48">
+        <v>6</v>
+      </c>
+      <c r="D105" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="E105" s="40" t="s">
+        <v>351</v>
+      </c>
+      <c r="F105" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H105" s="48">
+        <v>4</v>
+      </c>
+      <c r="I105" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="J105" s="49">
+        <v>380</v>
+      </c>
+      <c r="K105" s="49">
+        <v>380</v>
+      </c>
+      <c r="L105" s="49">
+        <v>860</v>
+      </c>
+      <c r="M105" s="49">
+        <v>380</v>
+      </c>
+      <c r="N105" s="49">
+        <v>860</v>
+      </c>
+      <c r="O105" s="49"/>
+      <c r="P105" s="49"/>
+      <c r="Q105" s="49"/>
+      <c r="R105" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S105" s="40" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A105" s="56" t="s">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A106" s="56" t="s">
         <v>353</v>
       </c>
-      <c r="B105" s="57"/>
-      <c r="C105" s="57"/>
-      <c r="D105" s="57"/>
-      <c r="E105" s="57"/>
-      <c r="F105" s="57"/>
-      <c r="G105" s="57"/>
-      <c r="H105" s="57"/>
-      <c r="I105" s="57"/>
-      <c r="J105" s="57"/>
-      <c r="K105" s="57"/>
-      <c r="L105" s="57"/>
-      <c r="M105" s="57"/>
-      <c r="N105" s="57"/>
-      <c r="O105" s="57"/>
-      <c r="P105" s="57"/>
-      <c r="Q105" s="57"/>
-      <c r="R105" s="57"/>
-      <c r="S105" s="58"/>
-    </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A106" s="47" t="s">
+      <c r="B106" s="57"/>
+      <c r="C106" s="57"/>
+      <c r="D106" s="57"/>
+      <c r="E106" s="57"/>
+      <c r="F106" s="57"/>
+      <c r="G106" s="57"/>
+      <c r="H106" s="57"/>
+      <c r="I106" s="57"/>
+      <c r="J106" s="57"/>
+      <c r="K106" s="57"/>
+      <c r="L106" s="57"/>
+      <c r="M106" s="57"/>
+      <c r="N106" s="57"/>
+      <c r="O106" s="57"/>
+      <c r="P106" s="57"/>
+      <c r="Q106" s="57"/>
+      <c r="R106" s="57"/>
+      <c r="S106" s="58"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A107" s="47" t="s">
         <v>354</v>
       </c>
-      <c r="B106" s="40" t="s">
+      <c r="B107" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="C106" s="48">
+      <c r="C107" s="48">
         <v>7</v>
       </c>
-      <c r="D106" s="40" t="s">
+      <c r="D107" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E106" s="40" t="s">
+      <c r="E107" s="40" t="s">
         <v>355</v>
       </c>
-      <c r="F106" s="48" t="s">
+      <c r="F107" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G106" s="40" t="s">
+      <c r="G107" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H106" s="48">
+      <c r="H107" s="48">
         <v>1</v>
       </c>
-      <c r="I106" s="40" t="s">
+      <c r="I107" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J106" s="49">
+      <c r="J107" s="49">
         <v>10</v>
       </c>
-      <c r="K106" s="49">
+      <c r="K107" s="49">
         <v>25</v>
       </c>
-      <c r="L106" s="49">
+      <c r="L107" s="49">
         <v>55</v>
       </c>
-      <c r="M106" s="49">
-        <v>0</v>
-      </c>
-      <c r="N106" s="49">
-        <v>0</v>
-      </c>
-      <c r="O106" s="49">
+      <c r="M107" s="49">
+        <v>0</v>
+      </c>
+      <c r="N107" s="49">
+        <v>0</v>
+      </c>
+      <c r="O107" s="49">
         <v>15</v>
       </c>
-      <c r="P106" s="49">
+      <c r="P107" s="49">
         <v>35</v>
       </c>
-      <c r="Q106" s="49">
-        <v>0</v>
-      </c>
-      <c r="R106" s="48" t="s">
+      <c r="Q107" s="49">
+        <v>0</v>
+      </c>
+      <c r="R107" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S106" s="40" t="s">
+      <c r="S107" s="40" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A107" s="50" t="s">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A108" s="50" t="s">
         <v>357</v>
       </c>
-      <c r="B107" s="51" t="s">
+      <c r="B108" s="51" t="s">
         <v>357</v>
       </c>
-      <c r="C107" s="52">
+      <c r="C108" s="52">
         <v>7</v>
       </c>
-      <c r="D107" s="51" t="s">
+      <c r="D108" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E107" s="51" t="s">
+      <c r="E108" s="51" t="s">
         <v>358</v>
       </c>
-      <c r="F107" s="52" t="s">
+      <c r="F108" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G107" s="51" t="s">
+      <c r="G108" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H107" s="52">
+      <c r="H108" s="52">
         <v>1</v>
       </c>
-      <c r="I107" s="51" t="s">
+      <c r="I108" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J107" s="53">
+      <c r="J108" s="53">
         <v>10</v>
       </c>
-      <c r="K107" s="53">
+      <c r="K108" s="53">
         <v>20</v>
       </c>
-      <c r="L107" s="53">
+      <c r="L108" s="53">
         <v>45</v>
       </c>
-      <c r="M107" s="53">
-        <v>0</v>
-      </c>
-      <c r="N107" s="53">
-        <v>0</v>
-      </c>
-      <c r="O107" s="53">
+      <c r="M108" s="53">
+        <v>0</v>
+      </c>
+      <c r="N108" s="53">
+        <v>0</v>
+      </c>
+      <c r="O108" s="53">
         <v>12</v>
       </c>
-      <c r="P107" s="53">
+      <c r="P108" s="53">
         <v>28</v>
       </c>
-      <c r="Q107" s="53">
-        <v>0</v>
-      </c>
-      <c r="R107" s="52" t="s">
+      <c r="Q108" s="53">
+        <v>0</v>
+      </c>
+      <c r="R108" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S107" s="51" t="s">
+      <c r="S108" s="51" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A108" s="47" t="s">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A109" s="47" t="s">
         <v>360</v>
       </c>
-      <c r="B108" s="40" t="s">
+      <c r="B109" s="40" t="s">
         <v>360</v>
       </c>
-      <c r="C108" s="48">
+      <c r="C109" s="48">
         <v>7</v>
       </c>
-      <c r="D108" s="40" t="s">
+      <c r="D109" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E108" s="40" t="s">
+      <c r="E109" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="F108" s="48" t="s">
+      <c r="F109" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G108" s="40" t="s">
+      <c r="G109" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H108" s="48">
+      <c r="H109" s="48">
         <v>1</v>
       </c>
-      <c r="I108" s="40" t="s">
+      <c r="I109" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J108" s="49">
+      <c r="J109" s="49">
         <v>5</v>
       </c>
-      <c r="K108" s="49">
+      <c r="K109" s="49">
         <v>10</v>
       </c>
-      <c r="L108" s="49">
+      <c r="L109" s="49">
         <v>20</v>
       </c>
-      <c r="M108" s="49">
-        <v>0</v>
-      </c>
-      <c r="N108" s="49">
-        <v>0</v>
-      </c>
-      <c r="O108" s="49">
+      <c r="M109" s="49">
+        <v>0</v>
+      </c>
+      <c r="N109" s="49">
+        <v>0</v>
+      </c>
+      <c r="O109" s="49">
         <v>5</v>
       </c>
-      <c r="P108" s="49">
+      <c r="P109" s="49">
         <v>15</v>
       </c>
-      <c r="Q108" s="49">
-        <v>0</v>
-      </c>
-      <c r="R108" s="48" t="s">
+      <c r="Q109" s="49">
+        <v>0</v>
+      </c>
+      <c r="R109" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S108" s="40" t="s">
+      <c r="S109" s="40" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A109" s="50" t="s">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A110" s="50" t="s">
         <v>363</v>
       </c>
-      <c r="B109" s="51" t="s">
+      <c r="B110" s="51" t="s">
         <v>363</v>
       </c>
-      <c r="C109" s="52">
+      <c r="C110" s="52">
         <v>7</v>
       </c>
-      <c r="D109" s="51" t="s">
+      <c r="D110" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E109" s="51" t="s">
+      <c r="E110" s="51" t="s">
         <v>364</v>
       </c>
-      <c r="F109" s="52" t="s">
+      <c r="F110" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G109" s="51" t="s">
+      <c r="G110" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H109" s="52">
+      <c r="H110" s="52">
         <v>1</v>
       </c>
-      <c r="I109" s="51" t="s">
+      <c r="I110" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J109" s="53">
+      <c r="J110" s="53">
         <v>30</v>
       </c>
-      <c r="K109" s="53">
+      <c r="K110" s="53">
         <v>50</v>
       </c>
-      <c r="L109" s="53">
+      <c r="L110" s="53">
         <v>90</v>
       </c>
-      <c r="M109" s="53">
-        <v>0</v>
-      </c>
-      <c r="N109" s="53">
-        <v>0</v>
-      </c>
-      <c r="O109" s="53">
+      <c r="M110" s="53">
+        <v>0</v>
+      </c>
+      <c r="N110" s="53">
+        <v>0</v>
+      </c>
+      <c r="O110" s="53">
         <v>20</v>
       </c>
-      <c r="P109" s="53">
+      <c r="P110" s="53">
         <v>55</v>
       </c>
-      <c r="Q109" s="53">
-        <v>0</v>
-      </c>
-      <c r="R109" s="52" t="s">
+      <c r="Q110" s="53">
+        <v>0</v>
+      </c>
+      <c r="R110" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S109" s="51" t="s">
+      <c r="S110" s="51" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A110" s="47" t="s">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A111" s="47" t="s">
         <v>366</v>
       </c>
-      <c r="B110" s="40" t="s">
+      <c r="B111" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="C110" s="48">
+      <c r="C111" s="48">
         <v>7</v>
       </c>
-      <c r="D110" s="40" t="s">
+      <c r="D111" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E110" s="40" t="s">
+      <c r="E111" s="40" t="s">
         <v>367</v>
       </c>
-      <c r="F110" s="48" t="s">
+      <c r="F111" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G110" s="40" t="s">
+      <c r="G111" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H110" s="48">
+      <c r="H111" s="48">
         <v>1</v>
       </c>
-      <c r="I110" s="40" t="s">
+      <c r="I111" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J110" s="49">
+      <c r="J111" s="49">
         <v>5</v>
       </c>
-      <c r="K110" s="49">
+      <c r="K111" s="49">
         <v>10</v>
       </c>
-      <c r="L110" s="49">
+      <c r="L111" s="49">
         <v>20</v>
       </c>
-      <c r="M110" s="49">
-        <v>0</v>
-      </c>
-      <c r="N110" s="49">
-        <v>0</v>
-      </c>
-      <c r="O110" s="49">
+      <c r="M111" s="49">
+        <v>0</v>
+      </c>
+      <c r="N111" s="49">
+        <v>0</v>
+      </c>
+      <c r="O111" s="49">
         <v>5</v>
       </c>
-      <c r="P110" s="49">
+      <c r="P111" s="49">
         <v>12</v>
       </c>
-      <c r="Q110" s="49">
-        <v>0</v>
-      </c>
-      <c r="R110" s="48" t="s">
+      <c r="Q111" s="49">
+        <v>0</v>
+      </c>
+      <c r="R111" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S110" s="40" t="s">
+      <c r="S111" s="40" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A111" s="56" t="s">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="s">
         <v>369</v>
       </c>
-      <c r="B111" s="57"/>
-      <c r="C111" s="57"/>
-      <c r="D111" s="57"/>
-      <c r="E111" s="57"/>
-      <c r="F111" s="57"/>
-      <c r="G111" s="57"/>
-      <c r="H111" s="57"/>
-      <c r="I111" s="57"/>
-      <c r="J111" s="57"/>
-      <c r="K111" s="57"/>
-      <c r="L111" s="57"/>
-      <c r="M111" s="57"/>
-      <c r="N111" s="57"/>
-      <c r="O111" s="57"/>
-      <c r="P111" s="57"/>
-      <c r="Q111" s="57"/>
-      <c r="R111" s="57"/>
-      <c r="S111" s="58"/>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A112" s="47" t="s">
+      <c r="B112" s="57"/>
+      <c r="C112" s="57"/>
+      <c r="D112" s="57"/>
+      <c r="E112" s="57"/>
+      <c r="F112" s="57"/>
+      <c r="G112" s="57"/>
+      <c r="H112" s="57"/>
+      <c r="I112" s="57"/>
+      <c r="J112" s="57"/>
+      <c r="K112" s="57"/>
+      <c r="L112" s="57"/>
+      <c r="M112" s="57"/>
+      <c r="N112" s="57"/>
+      <c r="O112" s="57"/>
+      <c r="P112" s="57"/>
+      <c r="Q112" s="57"/>
+      <c r="R112" s="57"/>
+      <c r="S112" s="58"/>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A113" s="47" t="s">
         <v>370</v>
       </c>
-      <c r="B112" s="40" t="s">
+      <c r="B113" s="40" t="s">
         <v>370</v>
       </c>
-      <c r="C112" s="48">
+      <c r="C113" s="48">
         <v>8</v>
       </c>
-      <c r="D112" s="40" t="s">
+      <c r="D113" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E112" s="40" t="s">
+      <c r="E113" s="40" t="s">
         <v>371</v>
       </c>
-      <c r="F112" s="48" t="s">
+      <c r="F113" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G112" s="40" t="s">
+      <c r="G113" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H112" s="48">
+      <c r="H113" s="48">
         <v>1</v>
       </c>
-      <c r="I112" s="40" t="s">
+      <c r="I113" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J112" s="49">
+      <c r="J113" s="49">
         <v>3</v>
       </c>
-      <c r="K112" s="49">
+      <c r="K113" s="49">
         <v>8</v>
       </c>
-      <c r="L112" s="49">
+      <c r="L113" s="49">
         <v>15</v>
       </c>
-      <c r="M112" s="49">
+      <c r="M113" s="49">
         <v>8</v>
       </c>
-      <c r="N112" s="49">
+      <c r="N113" s="49">
         <v>18</v>
       </c>
-      <c r="O112" s="49">
+      <c r="O113" s="49">
         <v>5</v>
       </c>
-      <c r="P112" s="49">
+      <c r="P113" s="49">
         <v>12</v>
       </c>
-      <c r="Q112" s="49">
+      <c r="Q113" s="49">
         <v>10</v>
       </c>
-      <c r="R112" s="48" t="s">
+      <c r="R113" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S112" s="40" t="s">
+      <c r="S113" s="40" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A113" s="50" t="s">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A114" s="50" t="s">
         <v>373</v>
       </c>
-      <c r="B113" s="51" t="s">
+      <c r="B114" s="51" t="s">
         <v>373</v>
       </c>
-      <c r="C113" s="52">
+      <c r="C114" s="52">
         <v>8</v>
       </c>
-      <c r="D113" s="51" t="s">
+      <c r="D114" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E113" s="51" t="s">
+      <c r="E114" s="51" t="s">
         <v>374</v>
       </c>
-      <c r="F113" s="52" t="s">
+      <c r="F114" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G113" s="51" t="s">
+      <c r="G114" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H113" s="52">
+      <c r="H114" s="52">
         <v>1</v>
       </c>
-      <c r="I113" s="51" t="s">
+      <c r="I114" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="J113" s="53">
+      <c r="J114" s="53">
         <v>25</v>
       </c>
-      <c r="K113" s="53">
+      <c r="K114" s="53">
         <v>50</v>
       </c>
-      <c r="L113" s="53">
+      <c r="L114" s="53">
         <v>90</v>
       </c>
-      <c r="M113" s="53">
+      <c r="M114" s="53">
         <v>50</v>
       </c>
-      <c r="N113" s="53">
+      <c r="N114" s="53">
         <v>90</v>
       </c>
-      <c r="O113" s="53">
+      <c r="O114" s="53">
         <v>50</v>
       </c>
-      <c r="P113" s="53">
+      <c r="P114" s="53">
         <v>90</v>
       </c>
-      <c r="Q113" s="53">
+      <c r="Q114" s="53">
         <v>50</v>
       </c>
-      <c r="R113" s="52" t="s">
+      <c r="R114" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S113" s="51" t="s">
+      <c r="S114" s="51" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A114" s="47" t="s">
+    <row r="115" spans="1:19" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A115" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="B114" s="40" t="s">
+      <c r="B115" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="C114" s="48">
+      <c r="C115" s="48">
         <v>8</v>
       </c>
-      <c r="D114" s="40" t="s">
+      <c r="D115" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E114" s="40" t="s">
+      <c r="E115" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="F114" s="48" t="s">
+      <c r="F115" s="48" t="s">
         <v>98</v>
       </c>
-      <c r="G114" s="40" t="s">
+      <c r="G115" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="H114" s="48">
+      <c r="H115" s="48">
         <v>1</v>
       </c>
-      <c r="I114" s="40" t="s">
+      <c r="I115" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="J114" s="49">
+      <c r="J115" s="49">
         <v>1000</v>
       </c>
-      <c r="K114" s="49">
+      <c r="K115" s="49">
         <v>1800</v>
       </c>
-      <c r="L114" s="49">
+      <c r="L115" s="49">
         <v>2800</v>
       </c>
-      <c r="M114" s="49">
+      <c r="M115" s="49">
         <v>1000</v>
       </c>
-      <c r="N114" s="49">
+      <c r="N115" s="49">
         <v>1800</v>
       </c>
-      <c r="O114" s="49">
+      <c r="O115" s="49">
         <v>1000</v>
       </c>
-      <c r="P114" s="49">
+      <c r="P115" s="49">
         <v>1800</v>
       </c>
-      <c r="Q114" s="49">
+      <c r="Q115" s="49">
         <v>1800</v>
       </c>
-      <c r="R114" s="48" t="s">
+      <c r="R115" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S114" s="40" t="s">
+      <c r="S115" s="40" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A115" s="50" t="s">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A116" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="B115" s="51" t="s">
+      <c r="B116" s="51" t="s">
         <v>380</v>
       </c>
-      <c r="C115" s="52">
+      <c r="C116" s="52">
         <v>8</v>
       </c>
-      <c r="D115" s="51" t="s">
+      <c r="D116" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E115" s="51" t="s">
+      <c r="E116" s="51" t="s">
         <v>381</v>
       </c>
-      <c r="F115" s="52" t="s">
+      <c r="F116" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G115" s="51" t="s">
+      <c r="G116" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H115" s="52">
+      <c r="H116" s="52">
         <v>1</v>
       </c>
-      <c r="I115" s="51" t="s">
+      <c r="I116" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J115" s="53">
+      <c r="J116" s="53">
         <v>3</v>
       </c>
-      <c r="K115" s="53">
+      <c r="K116" s="53">
         <v>8</v>
       </c>
-      <c r="L115" s="53">
+      <c r="L116" s="53">
         <v>15</v>
       </c>
-      <c r="M115" s="53">
+      <c r="M116" s="53">
         <v>10</v>
       </c>
-      <c r="N115" s="53">
+      <c r="N116" s="53">
         <v>20</v>
       </c>
-      <c r="O115" s="53">
+      <c r="O116" s="53">
         <v>5</v>
       </c>
-      <c r="P115" s="53">
+      <c r="P116" s="53">
         <v>15</v>
       </c>
-      <c r="Q115" s="53">
+      <c r="Q116" s="53">
         <v>25</v>
       </c>
-      <c r="R115" s="52" t="s">
+      <c r="R116" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S115" s="51" t="s">
+      <c r="S116" s="51" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A116" s="47" t="s">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A117" s="47" t="s">
         <v>383</v>
       </c>
-      <c r="B116" s="40" t="s">
+      <c r="B117" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="C116" s="48">
+      <c r="C117" s="48">
         <v>8</v>
       </c>
-      <c r="D116" s="40" t="s">
+      <c r="D117" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E116" s="40" t="s">
+      <c r="E117" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="F116" s="48" t="s">
+      <c r="F117" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G116" s="40" t="s">
+      <c r="G117" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H116" s="48">
+      <c r="H117" s="48">
         <v>1</v>
       </c>
-      <c r="I116" s="40" t="s">
+      <c r="I117" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="J116" s="49">
+      <c r="J117" s="49">
         <v>3</v>
       </c>
-      <c r="K116" s="49">
+      <c r="K117" s="49">
         <v>6</v>
       </c>
-      <c r="L116" s="49">
+      <c r="L117" s="49">
         <v>12</v>
       </c>
-      <c r="M116" s="49">
+      <c r="M117" s="49">
         <v>8</v>
       </c>
-      <c r="N116" s="49">
+      <c r="N117" s="49">
         <v>15</v>
       </c>
-      <c r="O116" s="49">
+      <c r="O117" s="49">
         <v>5</v>
       </c>
-      <c r="P116" s="49">
+      <c r="P117" s="49">
         <v>10</v>
       </c>
-      <c r="Q116" s="49">
+      <c r="Q117" s="49">
         <v>15</v>
       </c>
-      <c r="R116" s="48" t="s">
+      <c r="R117" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S116" s="40" t="s">
+      <c r="S117" s="40" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A117" s="50" t="s">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A118" s="50" t="s">
         <v>386</v>
       </c>
-      <c r="B117" s="51" t="s">
+      <c r="B118" s="51" t="s">
         <v>386</v>
       </c>
-      <c r="C117" s="52">
+      <c r="C118" s="52">
         <v>8</v>
       </c>
-      <c r="D117" s="51" t="s">
+      <c r="D118" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E117" s="51" t="s">
+      <c r="E118" s="51" t="s">
         <v>387</v>
       </c>
-      <c r="F117" s="52" t="s">
+      <c r="F118" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G117" s="51" t="s">
+      <c r="G118" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H117" s="52">
+      <c r="H118" s="52">
         <v>1</v>
       </c>
-      <c r="I117" s="51" t="s">
+      <c r="I118" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J117" s="53">
+      <c r="J118" s="53">
         <v>8</v>
       </c>
-      <c r="K117" s="53">
+      <c r="K118" s="53">
         <v>10</v>
       </c>
-      <c r="L117" s="53">
+      <c r="L118" s="53">
         <v>20</v>
       </c>
-      <c r="M117" s="53">
+      <c r="M118" s="53">
         <v>10</v>
       </c>
-      <c r="N117" s="53">
+      <c r="N118" s="53">
         <v>20</v>
       </c>
-      <c r="O117" s="53">
+      <c r="O118" s="53">
         <v>5</v>
       </c>
-      <c r="P117" s="53">
+      <c r="P118" s="53">
         <v>15</v>
       </c>
-      <c r="Q117" s="53">
+      <c r="Q118" s="53">
         <v>20</v>
       </c>
-      <c r="R117" s="52" t="s">
+      <c r="R118" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S117" s="51" t="s">
+      <c r="S118" s="51" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A118" s="47" t="s">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A119" s="47" t="s">
         <v>389</v>
       </c>
-      <c r="B118" s="40" t="s">
+      <c r="B119" s="40" t="s">
         <v>389</v>
       </c>
-      <c r="C118" s="48">
+      <c r="C119" s="48">
         <v>8</v>
       </c>
-      <c r="D118" s="40" t="s">
+      <c r="D119" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E118" s="40" t="s">
+      <c r="E119" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="F118" s="48" t="s">
+      <c r="F119" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G118" s="40" t="s">
+      <c r="G119" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H118" s="48">
+      <c r="H119" s="48">
         <v>1</v>
       </c>
-      <c r="I118" s="40" t="s">
+      <c r="I119" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="J118" s="49">
+      <c r="J119" s="49">
         <v>30</v>
       </c>
-      <c r="K118" s="49">
+      <c r="K119" s="49">
         <v>75</v>
       </c>
-      <c r="L118" s="49">
+      <c r="L119" s="49">
         <v>150</v>
       </c>
-      <c r="M118" s="49">
+      <c r="M119" s="49">
         <v>75</v>
       </c>
-      <c r="N118" s="49">
+      <c r="N119" s="49">
         <v>150</v>
       </c>
-      <c r="O118" s="49">
+      <c r="O119" s="49">
         <v>75</v>
       </c>
-      <c r="P118" s="49">
+      <c r="P119" s="49">
         <v>150</v>
       </c>
-      <c r="Q118" s="49">
+      <c r="Q119" s="49">
         <v>30</v>
       </c>
-      <c r="R118" s="48" t="s">
+      <c r="R119" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S118" s="40" t="s">
+      <c r="S119" s="40" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A119" s="50" t="s">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A120" s="50" t="s">
         <v>392</v>
       </c>
-      <c r="B119" s="51" t="s">
+      <c r="B120" s="51" t="s">
         <v>392</v>
       </c>
-      <c r="C119" s="52">
+      <c r="C120" s="52">
         <v>8</v>
       </c>
-      <c r="D119" s="51" t="s">
+      <c r="D120" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E119" s="51" t="s">
+      <c r="E120" s="51" t="s">
         <v>393</v>
       </c>
-      <c r="F119" s="52" t="s">
+      <c r="F120" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="G119" s="51" t="s">
+      <c r="G120" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="H119" s="52">
+      <c r="H120" s="52">
         <v>1</v>
       </c>
-      <c r="I119" s="51" t="s">
+      <c r="I120" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="J119" s="53">
-        <v>0</v>
-      </c>
-      <c r="K119" s="53">
+      <c r="J120" s="53">
+        <v>0</v>
+      </c>
+      <c r="K120" s="53">
         <v>3</v>
       </c>
-      <c r="L119" s="53">
+      <c r="L120" s="53">
         <v>8</v>
       </c>
-      <c r="M119" s="53">
+      <c r="M120" s="53">
         <v>3</v>
       </c>
-      <c r="N119" s="53">
+      <c r="N120" s="53">
         <v>10</v>
       </c>
-      <c r="O119" s="53">
+      <c r="O120" s="53">
         <v>2</v>
       </c>
-      <c r="P119" s="53">
+      <c r="P120" s="53">
         <v>8</v>
       </c>
-      <c r="Q119" s="53">
+      <c r="Q120" s="53">
         <v>12</v>
       </c>
-      <c r="R119" s="52" t="s">
+      <c r="R120" s="52" t="s">
         <v>27</v>
       </c>
-      <c r="S119" s="51" t="s">
+      <c r="S120" s="51" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A120" s="47" t="s">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A121" s="47" t="s">
         <v>395</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B121" s="40" t="s">
         <v>395</v>
-      </c>
-      <c r="C120" s="48">
-        <v>8</v>
-      </c>
-      <c r="D120" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="E120" s="40" t="s">
-        <v>396</v>
-      </c>
-      <c r="F120" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="G120" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="H120" s="48">
-        <v>1</v>
-      </c>
-      <c r="I120" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="J120" s="49">
-        <v>75</v>
-      </c>
-      <c r="K120" s="49">
-        <v>150</v>
-      </c>
-      <c r="L120" s="49">
-        <v>250</v>
-      </c>
-      <c r="M120" s="49">
-        <v>150</v>
-      </c>
-      <c r="N120" s="49">
-        <v>250</v>
-      </c>
-      <c r="O120" s="49">
-        <v>150</v>
-      </c>
-      <c r="P120" s="49">
-        <v>250</v>
-      </c>
-      <c r="Q120" s="49">
-        <v>10</v>
-      </c>
-      <c r="R120" s="48" t="s">
-        <v>27</v>
-      </c>
-      <c r="S120" s="40" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="51" x14ac:dyDescent="0.25">
-      <c r="A121" s="47" t="s">
-        <v>398</v>
-      </c>
-      <c r="B121" s="40" t="s">
-        <v>398</v>
       </c>
       <c r="C121" s="48">
         <v>8</v>
       </c>
-      <c r="D121" s="41" t="s">
-        <v>160</v>
+      <c r="D121" s="40" t="s">
+        <v>23</v>
       </c>
       <c r="E121" s="40" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F121" s="48" t="s">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="G121" s="40" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="H121" s="48">
         <v>1</v>
       </c>
       <c r="I121" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="J121" s="49"/>
-      <c r="K121" s="49"/>
-      <c r="L121" s="49"/>
+        <v>32</v>
+      </c>
+      <c r="J121" s="49">
+        <v>75</v>
+      </c>
+      <c r="K121" s="49">
+        <v>150</v>
+      </c>
+      <c r="L121" s="49">
+        <v>250</v>
+      </c>
       <c r="M121" s="49">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N121" s="49">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="O121" s="49">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="P121" s="49">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="Q121" s="49">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="R121" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S121" s="40" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="51" x14ac:dyDescent="0.25">
       <c r="A122" s="47" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B122" s="40" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C122" s="48">
         <v>8</v>
       </c>
-      <c r="D122" s="40" t="s">
-        <v>23</v>
+      <c r="D122" s="41" t="s">
+        <v>160</v>
       </c>
       <c r="E122" s="40" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F122" s="48" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="G122" s="40" t="s">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="H122" s="48">
         <v>1</v>
       </c>
       <c r="I122" s="40" t="s">
-        <v>403</v>
-      </c>
-      <c r="J122" s="49">
-        <v>210</v>
-      </c>
-      <c r="K122" s="49">
-        <v>240</v>
-      </c>
-      <c r="L122" s="49">
-        <v>480</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="J122" s="49"/>
+      <c r="K122" s="49"/>
+      <c r="L122" s="49"/>
       <c r="M122" s="49">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="N122" s="49">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="O122" s="49">
-        <v>240</v>
+        <v>90</v>
       </c>
       <c r="P122" s="49">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="Q122" s="49">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="R122" s="48" t="s">
         <v>27</v>
       </c>
       <c r="S122" s="40" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+      <c r="A123" s="47" t="s">
+        <v>401</v>
+      </c>
+      <c r="B123" s="40" t="s">
+        <v>401</v>
+      </c>
+      <c r="C123" s="48">
+        <v>8</v>
+      </c>
+      <c r="D123" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" s="40" t="s">
+        <v>402</v>
+      </c>
+      <c r="F123" s="48" t="s">
+        <v>98</v>
+      </c>
+      <c r="G123" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="H123" s="48">
+        <v>1</v>
+      </c>
+      <c r="I123" s="40" t="s">
+        <v>403</v>
+      </c>
+      <c r="J123" s="49">
+        <v>210</v>
+      </c>
+      <c r="K123" s="49">
+        <v>240</v>
+      </c>
+      <c r="L123" s="49">
+        <v>480</v>
+      </c>
+      <c r="M123" s="49">
+        <v>240</v>
+      </c>
+      <c r="N123" s="49">
+        <v>480</v>
+      </c>
+      <c r="O123" s="49">
+        <v>240</v>
+      </c>
+      <c r="P123" s="49">
+        <v>480</v>
+      </c>
+      <c r="Q123" s="49">
+        <v>330</v>
+      </c>
+      <c r="R123" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="S123" s="40" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="51" x14ac:dyDescent="0.25">
-      <c r="A123" s="50" t="s">
+    <row r="124" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+      <c r="A124" s="50" t="s">
         <v>405</v>
       </c>
-      <c r="B123" s="51" t="s">
+      <c r="B124" s="51" t="s">
         <v>405</v>
       </c>
-      <c r="C123" s="52">
+      <c r="C124" s="52">
         <v>8</v>
       </c>
-      <c r="D123" s="51" t="s">
+      <c r="D124" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E123" s="51" t="s">
+      <c r="E124" s="51" t="s">
         <v>406</v>
       </c>
-      <c r="F123" s="52" t="s">
+      <c r="F124" s="52" t="s">
         <v>126</v>
       </c>
-      <c r="G123" s="51" t="s">
+      <c r="G124" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="H123" s="52">
+      <c r="H124" s="52">
         <v>1</v>
       </c>
-      <c r="I123" s="51" t="s">
+      <c r="I124" s="51" t="s">
         <v>154</v>
       </c>
-      <c r="J123" s="53">
+      <c r="J124" s="53">
         <v>2800</v>
       </c>
-      <c r="K123" s="53">
+      <c r="K124" s="53">
         <v>5000</v>
       </c>
-      <c r="L123" s="53">
+      <c r="L124" s="53">
         <v>9500</v>
       </c>
-      <c r="M123" s="53">
+      <c r="M124" s="53">
         <v>5000</v>
       </c>
-      <c r="N123" s="53">
+      <c r="N124" s="53">
         <v>9500</v>
       </c>
-      <c r="O123" s="53">
+      <c r="O124" s="53">
         <v>5000</v>
       </c>
-      <c r="P123" s="53">
+      <c r="P124" s="53">
         <v>9500</v>
       </c>
-      <c r="Q123" s="53">
+      <c r="Q124" s="53">
         <v>5800</v>
       </c>
-      <c r="R123" s="52" t="s">
+      <c r="R124" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="S123" s="51" t="s">
+      <c r="S124" s="51" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="124" spans="1:19" ht="51" x14ac:dyDescent="0.25">
-      <c r="A124" s="47" t="s">
+    <row r="125" spans="1:19" ht="51" x14ac:dyDescent="0.25">
+      <c r="A125" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="B124" s="40" t="s">
+      <c r="B125" s="40" t="s">
         <v>408</v>
       </c>
-      <c r="C124" s="48">
+      <c r="C125" s="48">
         <v>8</v>
       </c>
-      <c r="D124" s="40" t="s">
+      <c r="D125" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E124" s="40" t="s">
+      <c r="E125" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="F124" s="48" t="s">
+      <c r="F125" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="G124" s="40" t="s">
+      <c r="G125" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="H124" s="48">
+      <c r="H125" s="48">
         <v>1</v>
       </c>
-      <c r="I124" s="40" t="s">
+      <c r="I125" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="J124" s="49">
+      <c r="J125" s="49">
         <v>42</v>
       </c>
-      <c r="K124" s="49">
+      <c r="K125" s="49">
         <v>95</v>
       </c>
-      <c r="L124" s="49">
+      <c r="L125" s="49">
         <v>200</v>
       </c>
-      <c r="M124" s="49">
+      <c r="M125" s="49">
         <v>95</v>
       </c>
-      <c r="N124" s="49">
+      <c r="N125" s="49">
         <v>200</v>
       </c>
-      <c r="O124" s="49">
+      <c r="O125" s="49">
         <v>95</v>
       </c>
-      <c r="P124" s="49">
+      <c r="P125" s="49">
         <v>200</v>
       </c>
-      <c r="Q124" s="49"/>
-      <c r="R124" s="48" t="s">
+      <c r="Q125" s="49"/>
+      <c r="R125" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="S124" s="40" t="s">
+      <c r="S125" s="40" t="s">
         <v>410</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A10:S10"/>
+    <mergeCell ref="A11:S11"/>
     <mergeCell ref="A5:S5"/>
-    <mergeCell ref="A111:S111"/>
-    <mergeCell ref="A100:S100"/>
-    <mergeCell ref="A105:S105"/>
-    <mergeCell ref="A15:S15"/>
-    <mergeCell ref="A29:S29"/>
-    <mergeCell ref="A25:S25"/>
-    <mergeCell ref="A65:S65"/>
+    <mergeCell ref="A112:S112"/>
+    <mergeCell ref="A101:S101"/>
+    <mergeCell ref="A106:S106"/>
+    <mergeCell ref="A16:S16"/>
+    <mergeCell ref="A30:S30"/>
+    <mergeCell ref="A26:S26"/>
+    <mergeCell ref="A66:S66"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9731,10 +9818,10 @@
         <v>480</v>
       </c>
       <c r="D6" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>481</v>
@@ -9751,10 +9838,10 @@
         <v>480</v>
       </c>
       <c r="D7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E7" s="8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>482</v>
